--- a/LISTA_COMPRA_CAMPAMENTO.xlsx
+++ b/LISTA_COMPRA_CAMPAMENTO.xlsx
@@ -19,7 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REPARTO CAJAS" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LISTA DE LA COMPRA'!$A$1:$L$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LISTA DE LA COMPRA'!$A$1:$L$315</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L313"/>
+  <dimension ref="A1:L315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1</v>
@@ -2168,7 +2168,8 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Alambre»</t>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Alambre»
+EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Alambre»</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr"/>
@@ -2639,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>0</v>
@@ -2660,6 +2661,7 @@
           <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Aros»
 LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Un palo/algo para meter aros»
 LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Aros»
+LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «5 aros pequeños para prender»
 RUTAS ICARO - Actividad para Lobatos (Charlie y David) (J-23/07): «Un palo para meter aros»
 RUTAS ICARO - Actividad para Lobatos (Charlie y David) (J-23/07): «Aros»</t>
         </is>
@@ -7018,7 +7020,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>Globos de agua (hinchados en barreño)</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7034,13 +7036,13 @@
         <v>0</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="10" t="n">
         <v>0</v>
@@ -7052,7 +7054,7 @@
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Globos de agua (hinchados en barreño)»</t>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Gasolina»</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr"/>
@@ -7061,7 +7063,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Globos de agua 100</t>
+          <t>Globos de agua (hinchados en barreño)</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -7077,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="3" t="n">
         <v>0</v>
@@ -7095,7 +7097,7 @@
       </c>
       <c r="J142" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Globos de agua 100»</t>
+          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Globos de agua (hinchados en barreño)»</t>
         </is>
       </c>
       <c r="K142" s="8" t="inlineStr"/>
@@ -7104,12 +7106,12 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>Goma eva de colores</t>
+          <t>Globos de agua 100</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C143" s="11">
@@ -7117,26 +7119,69 @@
         <v/>
       </c>
       <c r="D143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Globos de agua 100»</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr"/>
+      <c r="L143" s="13" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Goma eva de colores</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C144" s="6">
+        <f>SUM(D144:H144)</f>
+        <v/>
+      </c>
+      <c r="D144" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E143" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="10" t="inlineStr">
+      <c r="E144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J143" s="12" t="inlineStr">
+      <c r="J144" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Taller insignias (V-17/07 tarde): «Goma eva de colores»
 CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Goma eva de colores (vale con recortes)»
@@ -7144,61 +7189,18 @@
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Goma eva de colores (recortes)»</t>
         </is>
       </c>
-      <c r="K143" s="13" t="inlineStr"/>
-      <c r="L143" s="13" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Goma eva de muchos colores (bastante)</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C144" s="6">
-        <f>SUM(D144:H144)</f>
-        <v/>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J144" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Goma eva de muchos colores (bastante)»</t>
-        </is>
-      </c>
       <c r="K144" s="8" t="inlineStr"/>
       <c r="L144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>Goma eva dorada brillantina A4</t>
+          <t>Goma eva de muchos colores (bastante)</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C145" s="11">
@@ -7209,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" s="10" t="n">
         <v>0</v>
@@ -7218,16 +7220,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Lámina goma eva dorada brillantina A4»</t>
+          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Goma eva de muchos colores (bastante)»</t>
         </is>
       </c>
       <c r="K145" s="13" t="inlineStr"/>
@@ -7236,12 +7238,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Gomas de plástico</t>
+          <t>Goma eva dorada brillantina A4</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C146" s="6">
@@ -7249,10 +7251,10 @@
         <v/>
       </c>
       <c r="D146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="3" t="n">
         <v>0</v>
@@ -7265,12 +7267,12 @@
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Gomas de plástico»</t>
+          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Lámina goma eva dorada brillantina A4»</t>
         </is>
       </c>
       <c r="K146" s="8" t="inlineStr"/>
@@ -7279,12 +7281,12 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>Gomas elásticas</t>
+          <t>Gomas de plástico</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C147" s="11">
@@ -7308,12 +7310,12 @@
       </c>
       <c r="I147" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Gomas elásticas (paquete)»</t>
+          <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Gomas de plástico»</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr"/>
@@ -7322,12 +7324,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Gomets o pegatinas de las bases</t>
+          <t>Gomas elásticas</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C148" s="6">
@@ -7351,12 +7353,12 @@
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Gomets o pegatinas de las bases»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Gomas elásticas (paquete)»</t>
         </is>
       </c>
       <c r="K148" s="8" t="inlineStr"/>
@@ -7365,7 +7367,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>Gomitas de colores para pulseras</t>
+          <t>Gomets o pegatinas de las bases</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -7378,7 +7380,7 @@
         <v/>
       </c>
       <c r="D149" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="10" t="n">
         <v>0</v>
@@ -7387,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="10" t="n">
         <v>0</v>
@@ -7399,7 +7401,7 @@
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Pulseras (L-20/07 noche): «Gomitas de colores para pulseras»</t>
+          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Gomets o pegatinas de las bases»</t>
         </is>
       </c>
       <c r="K149" s="13" t="inlineStr"/>
@@ -7408,7 +7410,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Gorro castor</t>
+          <t>Gomitas de colores para pulseras</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -7421,7 +7423,7 @@
         <v/>
       </c>
       <c r="D150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
@@ -7430,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
         <v>0</v>
@@ -7442,7 +7444,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Gorro castor»</t>
+          <t>PIONEROS - Pulseras (L-20/07 noche): «Gomitas de colores para pulseras»</t>
         </is>
       </c>
       <c r="K150" s="8" t="inlineStr"/>
@@ -7451,12 +7453,12 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>Grapadora</t>
+          <t>Gorro castor</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C151" s="11">
@@ -7464,70 +7466,113 @@
         <v/>
       </c>
       <c r="D151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Gorro castor»</t>
+        </is>
+      </c>
+      <c r="K151" s="13" t="inlineStr"/>
+      <c r="L151" s="13" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Grapadora</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C152" s="6">
+        <f>SUM(D152:H152)</f>
+        <v/>
+      </c>
+      <c r="D152" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E151" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J151" s="12" t="inlineStr">
+      <c r="E152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J152" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Lluvia: Flipbook (D-26/07 (lluvia)): «Grapadora»
 CASTORES - Cuento de imágenes (Bolsa de juegos): «Grapadora»</t>
         </is>
       </c>
-      <c r="K151" s="13" t="inlineStr"/>
-      <c r="L151" s="13" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="K152" s="8" t="inlineStr"/>
+      <c r="L152" s="8" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
         <is>
           <t>Guantes de trabajo (protección)</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B153" s="10" t="inlineStr">
         <is>
           <t>Higiene/limpieza</t>
         </is>
       </c>
-      <c r="C152" s="6">
-        <f>SUM(D152:H152)</f>
-        <v/>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="C153" s="11">
+        <f>SUM(D153:H153)</f>
+        <v/>
+      </c>
+      <c r="D153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
         <is>
           <t>LO TRAE EL NINO</t>
         </is>
       </c>
-      <c r="J152" s="7" t="inlineStr">
+      <c r="J153" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - Voluntariado conjunto Lobatos-Pioneros (J-23/07 mañana): «Guantes»
 EXPLORADORES - Servicio en el pueblo (J-23/07 mañana): «Pendiente del voluntariado, se suelen necesitar: Guantes»
@@ -7535,100 +7580,57 @@
 RUTAS ICARO - Voluntariado Manuela (J-23/07): «Guantes»</t>
         </is>
       </c>
-      <c r="K152" s="8" t="inlineStr"/>
-      <c r="L152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="K153" s="13" t="inlineStr"/>
+      <c r="L153" s="13" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Hierros de tienda</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>Construccion/herramientas</t>
         </is>
       </c>
-      <c r="C153" s="11">
-        <f>SUM(D153:H153)</f>
-        <v/>
-      </c>
-      <c r="D153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J153" s="12" t="inlineStr">
+      <c r="C154" s="6">
+        <f>SUM(D154:H154)</f>
+        <v/>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J154" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Montaje (J-16/07 mañana): «Hierros»
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Hierros de tiendas de 3-4 tamaños»</t>
         </is>
       </c>
-      <c r="K153" s="13" t="inlineStr"/>
-      <c r="L153" s="13" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Hierros y listones para tendedero</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C154" s="6">
-        <f>SUM(D154:H154)</f>
-        <v/>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J154" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Hierros y listones para tendedero»</t>
-        </is>
-      </c>
       <c r="K154" s="8" t="inlineStr"/>
       <c r="L154" s="8" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>Hilo coreano de diferentes colores (3 m x niño)</t>
+          <t>Hierros y listones para tendedero</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -7643,9 +7645,8 @@
       <c r="D155" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E155" s="10">
-        <f>CONFIG!$B$3*3</f>
-        <v/>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="10" t="n">
         <v>0</v>
@@ -7654,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155" s="10" t="inlineStr">
         <is>
@@ -7663,7 +7664,7 @@
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Taller de pulseras (D-19/07 tarde): «Hilo coreano de diferentes colores (3 m x niño)»</t>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Hierros y listones para tendedero»</t>
         </is>
       </c>
       <c r="K155" s="13" t="inlineStr"/>
@@ -7672,7 +7673,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Hilo de colores (fino, no lana)</t>
+          <t>Hilo coreano de diferentes colores (3 m x niño)</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -7687,14 +7688,15 @@
       <c r="D156" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E156" s="3" t="n">
-        <v>0</v>
+      <c r="E156" s="3">
+        <f>CONFIG!$B$3*3</f>
+        <v/>
       </c>
       <c r="F156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>0</v>
@@ -7706,7 +7708,7 @@
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Decorar fotos (Lluvia): «Hilo de colores (fino, no lana)»</t>
+          <t>LOBATOS - Taller de pulseras (D-19/07 tarde): «Hilo coreano de diferentes colores (3 m x niño)»</t>
         </is>
       </c>
       <c r="K156" s="8" t="inlineStr"/>
@@ -7715,7 +7717,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>Hilo de colores para atar (gordito, no lana ni de pulseras fino)</t>
+          <t>Hilo de colores (fino, no lana)</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -7749,7 +7751,7 @@
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Hilo de colores para atar (gordito, no lana ni de pulseras fino)»</t>
+          <t>PIONEROS - Decorar fotos (Lluvia): «Hilo de colores (fino, no lana)»</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr"/>
@@ -7758,7 +7760,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Hilo de pulsera, 7-8 colores</t>
+          <t>Hilo de colores para atar (gordito, no lana ni de pulseras fino)</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -7792,7 +7794,7 @@
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Pulseras (Lluvia): «Hilo de pulsera, 7-8 colores»</t>
+          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Hilo de colores para atar (gordito, no lana ni de pulseras fino)»</t>
         </is>
       </c>
       <c r="K158" s="8" t="inlineStr"/>
@@ -7801,12 +7803,12 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>Imperdibles</t>
+          <t>Hilo de pulsera, 7-8 colores</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C159" s="11">
@@ -7814,26 +7816,69 @@
         <v/>
       </c>
       <c r="D159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J159" s="12" t="inlineStr">
+        <is>
+          <t>PIONEROS - Pulseras (Lluvia): «Hilo de pulsera, 7-8 colores»</t>
+        </is>
+      </c>
+      <c r="K159" s="13" t="inlineStr"/>
+      <c r="L159" s="13" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Imperdibles</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C160" s="6">
+        <f>SUM(D160:H160)</f>
+        <v/>
+      </c>
+      <c r="D160" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E159" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H159" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I159" s="10" t="inlineStr">
+      <c r="E160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J159" s="12" t="inlineStr">
+      <c r="J160" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Imperdibles x4»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Imperdibles x4»
@@ -7842,56 +7887,13 @@
 RUTAS ICARO - Construcciones (J-16/07): «Imperdibles»</t>
         </is>
       </c>
-      <c r="K159" s="13" t="inlineStr"/>
-      <c r="L159" s="13" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Incienso</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C160" s="6">
-        <f>SUM(D160:H160)</f>
-        <v/>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J160" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Juegos India (V-17/07 mañana): «Incienso»</t>
-        </is>
-      </c>
       <c r="K160" s="8" t="inlineStr"/>
       <c r="L160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>Insignia de arat</t>
+          <t>Incienso</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -7904,10 +7906,10 @@
         <v/>
       </c>
       <c r="D161" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="10" t="n">
         <v>0</v>
@@ -7925,7 +7927,7 @@
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia de arat»</t>
+          <t>LOBATOS - Juegos India (V-17/07 mañana): «Incienso»</t>
         </is>
       </c>
       <c r="K161" s="13" t="inlineStr"/>
@@ -7934,7 +7936,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Insignia del tronco (promesa)</t>
+          <t>Insignia de arat</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -7968,7 +7970,7 @@
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia del tronco (promesa)»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia de arat»</t>
         </is>
       </c>
       <c r="K162" s="8" t="inlineStr"/>
@@ -7977,7 +7979,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>Insignias territorios</t>
+          <t>Insignia del tronco (promesa)</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -7990,10 +7992,10 @@
         <v/>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" s="10" t="n">
         <v>0</v>
@@ -8011,7 +8013,7 @@
       </c>
       <c r="J163" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Promesas + progresión personal (S-25/07 mañana): «Insignias territorios»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia del tronco (promesa)»</t>
         </is>
       </c>
       <c r="K163" s="13" t="inlineStr"/>
@@ -8020,7 +8022,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Jarras de cocina</t>
+          <t>Insignias territorios</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -8036,13 +8038,13 @@
         <v>0</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
         <v>0</v>
@@ -8054,7 +8056,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Jarras de cocina»</t>
+          <t>LOBATOS - Promesas + progresión personal (S-25/07 mañana): «Insignias territorios»</t>
         </is>
       </c>
       <c r="K164" s="8" t="inlineStr"/>
@@ -8063,7 +8065,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>Juegos de la caja</t>
+          <t>Jarras de cocina</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -8097,7 +8099,7 @@
       </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Velada teleclub (X-22/07 noche): «Juegos de la caja»</t>
+          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Jarras de cocina»</t>
         </is>
       </c>
       <c r="K165" s="13" t="inlineStr"/>
@@ -8106,12 +8108,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Juegos de mesa y barajas de cartas</t>
+          <t>Juegos de la caja</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Juegos/deporte</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C166" s="6">
@@ -8119,26 +8121,69 @@
         <v/>
       </c>
       <c r="D166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>PIONEROS - Velada teleclub (X-22/07 noche): «Juegos de la caja»</t>
+        </is>
+      </c>
+      <c r="K166" s="8" t="inlineStr"/>
+      <c r="L166" s="8" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Juegos de mesa y barajas de cartas</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Juegos/deporte</t>
+        </is>
+      </c>
+      <c r="C167" s="11">
+        <f>SUM(D167:H167)</f>
+        <v/>
+      </c>
+      <c r="D167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F166" s="3" t="n">
+      <c r="F167" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G166" s="3" t="n">
+      <c r="G167" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H166" s="3" t="n">
+      <c r="H167" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J166" s="7" t="inlineStr">
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J167" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Juegos de mesa (X-22/07 noche): «Juegos de mesa de las bases»
 LOBATOS - Juegos India (V-17/07 mañana): «Parchís y fichas x3»
@@ -8164,56 +8209,13 @@
 RUTAS ICARO - Actividad para Tropa: Trivial (X-22/07): «Fichas»</t>
         </is>
       </c>
-      <c r="K166" s="8" t="inlineStr"/>
-      <c r="L166" s="8" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>Lana de colores</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C167" s="11">
-        <f>SUM(D167:H167)</f>
-        <v/>
-      </c>
-      <c r="D167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J167" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Taller de tejer (Lluvia): «Lana de colores»</t>
-        </is>
-      </c>
       <c r="K167" s="13" t="inlineStr"/>
       <c r="L167" s="13" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Lanzadoras tipo Nerf (unidad, solo monitores)</t>
+          <t>Lana de colores</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -8232,10 +8234,10 @@
         <v>0</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="3" t="n">
         <v>0</v>
@@ -8247,7 +8249,7 @@
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lanzadoras tipo Nerf (unidad, solo monitores)»</t>
+          <t>PIONEROS - Taller de tejer (Lluvia): «Lana de colores»</t>
         </is>
       </c>
       <c r="K168" s="8" t="inlineStr"/>
@@ -8256,7 +8258,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>Lata de aluminio 2 por niño</t>
+          <t>Lanzadoras tipo Nerf (unidad, solo monitores)</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
@@ -8290,7 +8292,7 @@
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Lata de aluminio 2 por niño»</t>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lanzadoras tipo Nerf (unidad, solo monitores)»</t>
         </is>
       </c>
       <c r="K169" s="13" t="inlineStr"/>
@@ -8299,7 +8301,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Lentejas x300</t>
+          <t>Lata de aluminio 2 por niño</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -8318,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
         <v>0</v>
@@ -8333,7 +8335,7 @@
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Lentejas x300»</t>
+          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Lata de aluminio 2 por niño»</t>
         </is>
       </c>
       <c r="K170" s="8" t="inlineStr"/>
@@ -8342,7 +8344,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>Libro con muchas páginas</t>
+          <t>Lentejas x300</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
@@ -8361,7 +8363,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G171" s="10" t="n">
         <v>0</v>
@@ -8376,7 +8378,7 @@
       </c>
       <c r="J171" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Libro con muchas páginas»</t>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Lentejas x300»</t>
         </is>
       </c>
       <c r="K171" s="13" t="inlineStr"/>
@@ -8385,12 +8387,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Lija de grano fino</t>
+          <t>Libro con muchas páginas</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C172" s="6">
@@ -8414,12 +8416,12 @@
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lija de grano fino»</t>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Libro con muchas páginas»</t>
         </is>
       </c>
       <c r="K172" s="8" t="inlineStr"/>
@@ -8428,12 +8430,12 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>Linternas / Frontales</t>
+          <t>Lija de grano fino</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Iluminacion/electronica</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C173" s="11">
@@ -8441,26 +8443,69 @@
         <v/>
       </c>
       <c r="D173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lija de grano fino»</t>
+        </is>
+      </c>
+      <c r="K173" s="13" t="inlineStr"/>
+      <c r="L173" s="13" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Linternas / Frontales</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Iluminacion/electronica</t>
+        </is>
+      </c>
+      <c r="C174" s="6">
+        <f>SUM(D174:H174)</f>
+        <v/>
+      </c>
+      <c r="D174" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="10" t="n">
+      <c r="E174" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F173" s="10" t="n">
+      <c r="F174" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G173" s="10" t="n">
+      <c r="G174" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H173" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" s="10" t="inlineStr">
+      <c r="H174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
         <is>
           <t>LO TRAE EL NINO</t>
         </is>
       </c>
-      <c r="J173" s="12" t="inlineStr">
+      <c r="J174" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Taller constelaciones (S-18/07 noche): «Frontal o linterna del móvil»
 CASTORES - Caza Gamusino (M-21/07 noche): «Frontales»
@@ -8476,56 +8521,13 @@
 RUTAS PANDORA - Stalking con el Clan Ícaro (D-26/07 noche): «Frontales»</t>
         </is>
       </c>
-      <c r="K173" s="13" t="inlineStr"/>
-      <c r="L173" s="13" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Lista de preguntas impresa (Eva y Vali)</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C174" s="6">
-        <f>SUM(D174:H174)</f>
-        <v/>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J174" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Taller feminismo (actividad país) (X-22/07 noche): «Lista de preguntas impresa (Eva y Vali)»</t>
-        </is>
-      </c>
       <c r="K174" s="8" t="inlineStr"/>
       <c r="L174" s="8" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>Listones circulares</t>
+          <t>Lista de preguntas impresa (Eva y Vali)</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
@@ -8544,13 +8546,13 @@
         <v>0</v>
       </c>
       <c r="F175" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G175" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H175" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" s="10" t="inlineStr">
         <is>
@@ -8559,7 +8561,7 @@
       </c>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Listones circulares»</t>
+          <t>RUTAS ICARO - Taller feminismo (actividad país) (X-22/07 noche): «Lista de preguntas impresa (Eva y Vali)»</t>
         </is>
       </c>
       <c r="K175" s="13" t="inlineStr"/>
@@ -8568,7 +8570,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Listones para portada</t>
+          <t>Listones circulares</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -8602,7 +8604,7 @@
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listones para portada»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Listones circulares»</t>
         </is>
       </c>
       <c r="K176" s="8" t="inlineStr"/>
@@ -8611,7 +8613,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>Listones sobrantes</t>
+          <t>Listones para portada</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -8630,13 +8632,13 @@
         <v>0</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H177" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="10" t="inlineStr">
         <is>
@@ -8645,7 +8647,7 @@
       </c>
       <c r="J177" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Listones sobrantes»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listones para portada»</t>
         </is>
       </c>
       <c r="K177" s="13" t="inlineStr"/>
@@ -8654,12 +8656,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Listones y tablas de madera</t>
+          <t>Listones sobrantes</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C178" s="6">
@@ -8667,26 +8669,69 @@
         <v/>
       </c>
       <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Listones sobrantes»</t>
+        </is>
+      </c>
+      <c r="K178" s="8" t="inlineStr"/>
+      <c r="L178" s="8" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>Listones y tablas de madera</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C179" s="11">
+        <f>SUM(D179:H179)</f>
+        <v/>
+      </c>
+      <c r="D179" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="E178" s="3" t="n">
+      <c r="E179" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J178" s="7" t="inlineStr">
+      <c r="F179" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J179" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Listones»
 CASTORES - Montaje de tiendas (J-16/07 mañana): «Tablas de madera»
@@ -8697,56 +8742,13 @@
 LOBATOS - Construcción de parcela (J-16/07 tarde 1): «Listones»</t>
         </is>
       </c>
-      <c r="K178" s="8" t="inlineStr"/>
-      <c r="L178" s="8" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t>Listón para potero</t>
-        </is>
-      </c>
-      <c r="B179" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C179" s="11">
-        <f>SUM(D179:H179)</f>
-        <v/>
-      </c>
-      <c r="D179" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J179" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listón para potero»</t>
-        </is>
-      </c>
       <c r="K179" s="13" t="inlineStr"/>
       <c r="L179" s="13" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Lo que nos pidan</t>
+          <t>Listón para potero</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -8765,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
         <v>0</v>
@@ -8780,7 +8782,7 @@
       </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Voluntariado con Lobatos (J-23/07 mañana): «Lo que nos pidan»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listón para potero»</t>
         </is>
       </c>
       <c r="K180" s="8" t="inlineStr"/>
@@ -8789,12 +8791,12 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>Lonas</t>
+          <t>Lo que nos pidan</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C181" s="11">
@@ -8802,26 +8804,69 @@
         <v/>
       </c>
       <c r="D181" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>PIONEROS - Voluntariado con Lobatos (J-23/07 mañana): «Lo que nos pidan»</t>
+        </is>
+      </c>
+      <c r="K181" s="13" t="inlineStr"/>
+      <c r="L181" s="13" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Lonas</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C182" s="6">
+        <f>SUM(D182:H182)</f>
+        <v/>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F181" s="10" t="n">
+      <c r="F182" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G181" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I181" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J181" s="12" t="inlineStr">
+      <c r="G182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J182" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Lona + segunda estructura de tienda (mochilero)»
 LOBATOS - Gymkana de agua (V-24/07 mañana): «Lona grande o plástico resistente»
@@ -8833,105 +8878,62 @@
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Lona»</t>
         </is>
       </c>
-      <c r="K181" s="13" t="inlineStr"/>
-      <c r="L181" s="13" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="K182" s="8" t="inlineStr"/>
+      <c r="L182" s="8" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
         <is>
           <t>Lumi gas</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B183" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C182" s="6">
-        <f>SUM(D182:H182)</f>
-        <v/>
-      </c>
-      <c r="D182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J182" s="7" t="inlineStr">
+      <c r="C183" s="11">
+        <f>SUM(D183:H183)</f>
+        <v/>
+      </c>
+      <c r="D183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J183" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Lumi gas»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Lumi gas»</t>
         </is>
       </c>
-      <c r="K182" s="8" t="inlineStr"/>
-      <c r="L182" s="8" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Lumis para el centro</t>
-        </is>
-      </c>
-      <c r="B183" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C183" s="11">
-        <f>SUM(D183:H183)</f>
-        <v/>
-      </c>
-      <c r="D183" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H183" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J183" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Lumis para el centro»</t>
-        </is>
-      </c>
       <c r="K183" s="13" t="inlineStr"/>
       <c r="L183" s="13" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Lápices de colores / ceras / pinturas de palo</t>
+          <t>Lumis para el centro</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C184" s="6">
@@ -8948,78 +8950,78 @@
         <v>0</v>
       </c>
       <c r="G184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Lumis para el centro»</t>
+        </is>
+      </c>
+      <c r="K184" s="8" t="inlineStr"/>
+      <c r="L184" s="8" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Lápices de colores / ceras / pinturas de palo</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C185" s="11">
+        <f>SUM(D185:H185)</f>
+        <v/>
+      </c>
+      <c r="D185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
+      <c r="H185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J184" s="7" t="inlineStr">
+      <c r="J185" s="12" t="inlineStr">
         <is>
           <t>PIONEROS - Fe (V-24/07 tarde 2): «Pinturas de palo»
 PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Pinturas de palo»
 PIONEROS - Pintar mandalas (Lluvia): «Pinturas de palo»</t>
         </is>
       </c>
-      <c r="K184" s="8" t="inlineStr"/>
-      <c r="L184" s="8" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>Lápices de colores o ceras</t>
-        </is>
-      </c>
-      <c r="B185" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C185" s="11">
-        <f>SUM(D185:H185)</f>
-        <v/>
-      </c>
-      <c r="D185" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J185" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Progresión Personal (mandalas) (J-23/07 tarde 1): «Lápices de colores o ceras»</t>
-        </is>
-      </c>
       <c r="K185" s="13" t="inlineStr"/>
       <c r="L185" s="13" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Lápices y gomas</t>
+          <t>Lápices de colores o ceras</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C186" s="6">
@@ -9048,7 +9050,7 @@
       </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Lápices y gomas»</t>
+          <t>CASTORES - Progresión Personal (mandalas) (J-23/07 tarde 1): «Lápices de colores o ceras»</t>
         </is>
       </c>
       <c r="K186" s="8" t="inlineStr"/>
@@ -9057,12 +9059,12 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>Maderas varias para parcela y FELSA</t>
+          <t>Lápices y gomas</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C187" s="11">
@@ -9070,13 +9072,13 @@
         <v/>
       </c>
       <c r="D187" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" s="10" t="n">
         <v>0</v>
@@ -9091,7 +9093,7 @@
       </c>
       <c r="J187" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Maderas varias para parcela y FELSA»</t>
+          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Lápices y gomas»</t>
         </is>
       </c>
       <c r="K187" s="13" t="inlineStr"/>
@@ -9100,12 +9102,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Malla de alambre 1m x 30cm</t>
+          <t>Maderas varias para parcela y FELSA</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C188" s="6">
@@ -9116,10 +9118,10 @@
         <v>0</v>
       </c>
       <c r="E188" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
@@ -9129,12 +9131,12 @@
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Malla de alambre 1m x 30cm aprox (ref Temu en el doc)»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Maderas varias para parcela y FELSA»</t>
         </is>
       </c>
       <c r="K188" s="8" t="inlineStr"/>
@@ -9143,12 +9145,12 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>Mandalas (20)</t>
+          <t>Malla de alambre 1m x 30cm</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C189" s="11">
@@ -9172,12 +9174,12 @@
       </c>
       <c r="I189" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Mandalas (20)»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Malla de alambre 1m x 30cm aprox (ref Temu en el doc)»</t>
         </is>
       </c>
       <c r="K189" s="13" t="inlineStr"/>
@@ -9186,7 +9188,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Manojo de llaves</t>
+          <t>Mandalas (20)</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -9220,7 +9222,7 @@
       </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - GRUPAL: Velada inicial (J-16/07 noche): «Manojo de llaves»</t>
+          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Mandalas (20)»</t>
         </is>
       </c>
       <c r="K190" s="8" t="inlineStr"/>
@@ -9229,7 +9231,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>Manojo de llaves o cascabel</t>
+          <t>Manojo de llaves</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
@@ -9245,10 +9247,10 @@
         <v>0</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" s="10" t="n">
         <v>0</v>
@@ -9263,7 +9265,7 @@
       </c>
       <c r="J191" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Manojo de llaves o cascabel»</t>
+          <t>LOBATOS - GRUPAL: Velada inicial (J-16/07 noche): «Manojo de llaves»</t>
         </is>
       </c>
       <c r="K191" s="13" t="inlineStr"/>
@@ -9272,7 +9274,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Mantas</t>
+          <t>Manojo de llaves o cascabel</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -9291,64 +9293,107 @@
         <v>0</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Manojo de llaves o cascabel»</t>
+        </is>
+      </c>
+      <c r="K192" s="8" t="inlineStr"/>
+      <c r="L192" s="8" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>Mantas</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C193" s="11">
+        <f>SUM(D193:H193)</f>
+        <v/>
+      </c>
+      <c r="D193" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J192" s="7" t="inlineStr">
+      <c r="I193" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J193" s="12" t="inlineStr">
         <is>
           <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mantas»
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Mantas»</t>
         </is>
       </c>
-      <c r="K192" s="8" t="inlineStr"/>
-      <c r="L192" s="8" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="9" t="inlineStr">
+      <c r="K193" s="13" t="inlineStr"/>
+      <c r="L193" s="13" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>Mapas de la zona y Brújulas</t>
         </is>
       </c>
-      <c r="B193" s="10" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>Impresiones/documentacion</t>
         </is>
       </c>
-      <c r="C193" s="11">
-        <f>SUM(D193:H193)</f>
-        <v/>
-      </c>
-      <c r="D193" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" s="10" t="n">
+      <c r="C194" s="6">
+        <f>SUM(D194:H194)</f>
+        <v/>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F193" s="10" t="n">
+      <c r="F194" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G193" s="10" t="n">
+      <c r="G194" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H193" s="10" t="n">
+      <c r="H194" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I193" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J193" s="12" t="inlineStr">
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J194" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Mapas 312-I, 315-II, 315-IV, 316-III»
 LOBATOS - El amuleto del elefante sagrado (orientación) (X-22/07 tarde): «5 brújulas»
@@ -9374,61 +9419,18 @@
 RUTAS ICARO - Preparación de raids (L-27/07): «Mapas»</t>
         </is>
       </c>
-      <c r="K193" s="13" t="inlineStr"/>
-      <c r="L193" s="13" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Martillos</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C194" s="6">
-        <f>SUM(D194:H194)</f>
-        <v/>
-      </c>
-      <c r="D194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J194" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Martillos o maza»</t>
-        </is>
-      </c>
       <c r="K194" s="8" t="inlineStr"/>
       <c r="L194" s="8" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>Material de juegos especiales (Jugger, frisbee, combas, sogatira)</t>
+          <t>Martillos</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Juegos/deporte</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C195" s="11">
@@ -9439,23 +9441,66 @@
         <v>0</v>
       </c>
       <c r="E195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J195" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Martillos o maza»</t>
+        </is>
+      </c>
+      <c r="K195" s="13" t="inlineStr"/>
+      <c r="L195" s="13" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Material de juegos especiales (Jugger, frisbee, combas, sogatira)</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Juegos/deporte</t>
+        </is>
+      </c>
+      <c r="C196" s="6">
+        <f>SUM(D196:H196)</f>
+        <v/>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F195" s="10" t="n">
+      <c r="F196" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G195" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" s="10" t="n">
+      <c r="G196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I195" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J195" s="12" t="inlineStr">
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J196" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Comba»
 LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Discos para lanzar»
@@ -9469,61 +9514,18 @@
 RUTAS ICARO - Jugger con Pandora (S-25/07): «Armas de jugger»</t>
         </is>
       </c>
-      <c r="K195" s="13" t="inlineStr"/>
-      <c r="L195" s="13" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Material dejado por la empresa</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C196" s="6">
-        <f>SUM(D196:H196)</f>
-        <v/>
-      </c>
-      <c r="D196" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J196" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - Rapel (D-26/07): «Material dejado por la empresa»</t>
-        </is>
-      </c>
       <c r="K196" s="8" t="inlineStr"/>
       <c r="L196" s="8" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>Mazas / martillo de goma</t>
+          <t>Material dejado por la empresa</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C197" s="11">
@@ -9531,26 +9533,69 @@
         <v/>
       </c>
       <c r="D197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J197" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Rapel (D-26/07): «Material dejado por la empresa»</t>
+        </is>
+      </c>
+      <c r="K197" s="13" t="inlineStr"/>
+      <c r="L197" s="13" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Mazas / martillo de goma</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C198" s="6">
+        <f>SUM(D198:H198)</f>
+        <v/>
+      </c>
+      <c r="D198" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E197" s="10" t="n">
+      <c r="E198" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F197" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J197" s="12" t="inlineStr">
+      <c r="F198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J198" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Martillo de goma»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Martillo de goma»
@@ -9559,49 +9604,50 @@
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Martillo»</t>
         </is>
       </c>
-      <c r="K197" s="13" t="inlineStr"/>
-      <c r="L197" s="13" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="K198" s="8" t="inlineStr"/>
+      <c r="L198" s="8" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
         <is>
           <t>Mechero</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C198" s="6">
-        <f>SUM(D198:H198)</f>
-        <v/>
-      </c>
-      <c r="D198" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="3" t="n">
+      <c r="C199" s="11">
+        <f>SUM(D199:H199)</f>
+        <v/>
+      </c>
+      <c r="D199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F198" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H198" s="3" t="n">
+      <c r="H199" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J198" s="7" t="inlineStr">
+      <c r="I199" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J199" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Mechero»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Mechero»
 LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Mechero»
+LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Mechero»
 EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Mechero»
 PIONEROS - Actividad Clan Ícaro - Drogas (S-18/07 tarde 1): «Mechero»
 PIONEROS - Pulseras (Lluvia): «Mechero»
@@ -9611,56 +9657,13 @@
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Mechero»</t>
         </is>
       </c>
-      <c r="K198" s="8" t="inlineStr"/>
-      <c r="L198" s="8" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t>Mechero/cerillas</t>
-        </is>
-      </c>
-      <c r="B199" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C199" s="11">
-        <f>SUM(D199:H199)</f>
-        <v/>
-      </c>
-      <c r="D199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I199" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J199" s="12" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Línea de la vida (Volante noche): «Mechero/cerillas»</t>
-        </is>
-      </c>
       <c r="K199" s="13" t="inlineStr"/>
       <c r="L199" s="13" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Medallas de goma eva (las hace el kraalete)</t>
+          <t>Mechero/cerillas</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -9682,10 +9685,10 @@
         <v>0</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
@@ -9694,7 +9697,7 @@
       </c>
       <c r="J200" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Medallas de goma eva (las hace el kraalete)»</t>
+          <t>RUTAS ICARO - Línea de la vida (Volante noche): «Mechero/cerillas»</t>
         </is>
       </c>
       <c r="K200" s="8" t="inlineStr"/>
@@ -9703,7 +9706,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>Menaje</t>
+          <t>Medallas de goma eva (las hace el kraalete)</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
@@ -9722,10 +9725,10 @@
         <v>0</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="10" t="n">
         <v>0</v>
@@ -9737,7 +9740,7 @@
       </c>
       <c r="J201" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Menaje»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Medallas de goma eva (las hace el kraalete)»</t>
         </is>
       </c>
       <c r="K201" s="13" t="inlineStr"/>
@@ -9746,12 +9749,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Menaje de cocina (sartenes, cazuelas, boles, hornillos, bombonas)</t>
+          <t>Menaje</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Cocina/menaje</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C202" s="6">
@@ -9759,26 +9762,69 @@
         <v/>
       </c>
       <c r="D202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Menaje»</t>
+        </is>
+      </c>
+      <c r="K202" s="8" t="inlineStr"/>
+      <c r="L202" s="8" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>Menaje de cocina (sartenes, cazuelas, boles, hornillos, bombonas)</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>Cocina/menaje</t>
+        </is>
+      </c>
+      <c r="C203" s="11">
+        <f>SUM(D203:H203)</f>
+        <v/>
+      </c>
+      <c r="D203" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="E202" s="3" t="n">
+      <c r="E203" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="F202" s="3" t="n">
+      <c r="F203" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G202" s="3" t="n">
+      <c r="G203" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H202" s="3" t="n">
+      <c r="H203" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I202" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J202" s="7" t="inlineStr">
+      <c r="I203" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J203" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Cazuela y cuchara de madera»
 CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Bolsas de basura»
@@ -9861,56 +9907,13 @@
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Vaso de plástico»</t>
         </is>
       </c>
-      <c r="K202" s="8" t="inlineStr"/>
-      <c r="L202" s="8" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="9" t="inlineStr">
-        <is>
-          <t>Mini tronquitos</t>
-        </is>
-      </c>
-      <c r="B203" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C203" s="11">
-        <f>SUM(D203:H203)</f>
-        <v/>
-      </c>
-      <c r="D203" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F203" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H203" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I203" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J203" s="12" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mini tronquitos»</t>
-        </is>
-      </c>
       <c r="K203" s="13" t="inlineStr"/>
       <c r="L203" s="13" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Mismo material que la noche previa</t>
+          <t>Mini tronquitos</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -9929,13 +9932,13 @@
         <v>0</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
@@ -9944,7 +9947,7 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Raids (L-27/07): «Mismo material que la noche previa»</t>
+          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mini tronquitos»</t>
         </is>
       </c>
       <c r="K204" s="8" t="inlineStr"/>
@@ -9953,7 +9956,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>Miss y Mister grupales</t>
+          <t>Mismo material que la noche previa</t>
         </is>
       </c>
       <c r="B205" s="10" t="inlineStr">
@@ -9972,10 +9975,10 @@
         <v>0</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="10" t="n">
         <v>0</v>
@@ -9987,7 +9990,7 @@
       </c>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Miss y Mister grupales»</t>
+          <t>EXPLORADORES - Raids (L-27/07): «Mismo material que la noche previa»</t>
         </is>
       </c>
       <c r="K205" s="13" t="inlineStr"/>
@@ -9996,7 +9999,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Miss y Mister plastificados</t>
+          <t>Miss y Mister grupales</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -10030,7 +10033,7 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Miss y Mister plastificados»</t>
+          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Miss y Mister grupales»</t>
         </is>
       </c>
       <c r="K206" s="8" t="inlineStr"/>
@@ -10039,7 +10042,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>Miss y Mister ya plastificados</t>
+          <t>Miss y Mister plastificados</t>
         </is>
       </c>
       <c r="B207" s="10" t="inlineStr">
@@ -10073,7 +10076,7 @@
       </c>
       <c r="J207" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Miss y Mister ya plastificados»</t>
+          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Miss y Mister plastificados»</t>
         </is>
       </c>
       <c r="K207" s="13" t="inlineStr"/>
@@ -10082,7 +10085,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Monedas de céntimo</t>
+          <t>Miss y Mister ya plastificados</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -10098,13 +10101,13 @@
         <v>0</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H208" s="3" t="n">
         <v>0</v>
@@ -10116,7 +10119,7 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Monedas de céntimo»</t>
+          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Miss y Mister ya plastificados»</t>
         </is>
       </c>
       <c r="K208" s="8" t="inlineStr"/>
@@ -10125,7 +10128,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>Máscaras (las del año pasado)</t>
+          <t>Monedas de céntimo</t>
         </is>
       </c>
       <c r="B209" s="10" t="inlineStr">
@@ -10141,10 +10144,10 @@
         <v>0</v>
       </c>
       <c r="E209" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" s="10" t="n">
         <v>0</v>
@@ -10159,7 +10162,7 @@
       </c>
       <c r="J209" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «Máscaras (las del año pasado)»</t>
+          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Monedas de céntimo»</t>
         </is>
       </c>
       <c r="K209" s="13" t="inlineStr"/>
@@ -10168,7 +10171,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Música india</t>
+          <t>Máscaras (las del año pasado)</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -10184,10 +10187,10 @@
         <v>0</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>0</v>
@@ -10202,7 +10205,7 @@
       </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Música india»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «Máscaras (las del año pasado)»</t>
         </is>
       </c>
       <c r="K210" s="8" t="inlineStr"/>
@@ -10211,7 +10214,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>Naturaleza recolectada en campa y río</t>
+          <t>Música india</t>
         </is>
       </c>
       <c r="B211" s="10" t="inlineStr">
@@ -10227,7 +10230,7 @@
         <v>0</v>
       </c>
       <c r="E211" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="10" t="n">
         <v>0</v>
@@ -10236,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I211" s="10" t="inlineStr">
         <is>
@@ -10245,7 +10248,7 @@
       </c>
       <c r="J211" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Naturaleza recolectada en campa y río»</t>
+          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Música india»</t>
         </is>
       </c>
       <c r="K211" s="13" t="inlineStr"/>
@@ -10254,7 +10257,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Navaja</t>
+          <t>Naturaleza recolectada en campa y río</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -10273,10 +10276,10 @@
         <v>0</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
         <v>1</v>
@@ -10287,62 +10290,62 @@
         </is>
       </c>
       <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Naturaleza recolectada en campa y río»</t>
+        </is>
+      </c>
+      <c r="K212" s="8" t="inlineStr"/>
+      <c r="L212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>Navaja</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C213" s="11">
+        <f>SUM(D213:H213)</f>
+        <v/>
+      </c>
+      <c r="D213" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J213" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Navaja»
 PIONEROS - Volantes (x3 días) (D-19 a M-21/07): «Navaja»
 RUTAS ICARO - Talleres personales (Charlie) (M-21/07): «Navaja»</t>
         </is>
       </c>
-      <c r="K212" s="8" t="inlineStr"/>
-      <c r="L212" s="8" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="9" t="inlineStr">
-        <is>
-          <t>Navajas (de los niños)</t>
-        </is>
-      </c>
-      <c r="B213" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C213" s="11">
-        <f>SUM(D213:H213)</f>
-        <v/>
-      </c>
-      <c r="D213" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F213" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I213" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J213" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Navajas (de los niños)»</t>
-        </is>
-      </c>
       <c r="K213" s="13" t="inlineStr"/>
       <c r="L213" s="13" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Nombres</t>
+          <t>Navajas (de los niños)</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -10358,10 +10361,10 @@
         <v>0</v>
       </c>
       <c r="E214" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G214" s="3" t="n">
         <v>0</v>
@@ -10376,7 +10379,7 @@
       </c>
       <c r="J214" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - FELSA (V-24/07 tarde 1): «Nombres»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Navajas (de los niños)»</t>
         </is>
       </c>
       <c r="K214" s="8" t="inlineStr"/>
@@ -10385,7 +10388,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>Nombres de los niños</t>
+          <t>Nombres</t>
         </is>
       </c>
       <c r="B215" s="10" t="inlineStr">
@@ -10419,7 +10422,7 @@
       </c>
       <c r="J215" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Nombres de los niños»</t>
+          <t>EXPLORADORES - FELSA (V-24/07 tarde 1): «Nombres»</t>
         </is>
       </c>
       <c r="K215" s="13" t="inlineStr"/>
@@ -10428,7 +10431,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Objetos varios que se cojan de material</t>
+          <t>Nombres de los niños</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -10444,10 +10447,10 @@
         <v>0</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" s="3" t="n">
         <v>0</v>
@@ -10462,7 +10465,7 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Juegos nocturnos (V-17/07 noche): «Objetos varios que se cojan de material»</t>
+          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Nombres de los niños»</t>
         </is>
       </c>
       <c r="K216" s="8" t="inlineStr"/>
@@ -10471,12 +10474,12 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>Ovillo de lana</t>
+          <t>Objetos varios que se cojan de material</t>
         </is>
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C217" s="11">
@@ -10496,113 +10499,113 @@
         <v>0</v>
       </c>
       <c r="H217" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" s="10" t="inlineStr">
         <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J217" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Juegos nocturnos (V-17/07 noche): «Objetos varios que se cojan de material»</t>
+        </is>
+      </c>
+      <c r="K217" s="13" t="inlineStr"/>
+      <c r="L217" s="13" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Ovillo de lana</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C218" s="6">
+        <f>SUM(D218:H218)</f>
+        <v/>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J217" s="12" t="inlineStr">
+      <c r="J218" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Un ovillo de lana»
 RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Ovillo de lana»</t>
         </is>
       </c>
-      <c r="K217" s="13" t="inlineStr"/>
-      <c r="L217" s="13" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="K218" s="8" t="inlineStr"/>
+      <c r="L218" s="8" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
         <is>
           <t>Pajitas</t>
         </is>
       </c>
-      <c r="B218" s="3" t="inlineStr">
+      <c r="B219" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C218" s="6">
-        <f>SUM(D218:H218)</f>
-        <v/>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
+      <c r="C219" s="11">
+        <f>SUM(D219:H219)</f>
+        <v/>
+      </c>
+      <c r="D219" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J218" s="7" t="inlineStr">
+      <c r="J219" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Pajitas»
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Pajitas»</t>
         </is>
       </c>
-      <c r="K218" s="8" t="inlineStr"/>
-      <c r="L218" s="8" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="9" t="inlineStr">
-        <is>
-          <t>Palas de ping pong y pelotitas</t>
-        </is>
-      </c>
-      <c r="B219" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C219" s="11">
-        <f>SUM(D219:H219)</f>
-        <v/>
-      </c>
-      <c r="D219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H219" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J219" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Palas de ping pong y pelotitas»</t>
-        </is>
-      </c>
       <c r="K219" s="13" t="inlineStr"/>
       <c r="L219" s="13" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Palillos alargados tipo brocheta</t>
+          <t>Palas de ping pong y pelotitas</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -10636,7 +10639,7 @@
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Taller de tejer (Lluvia): «Palillos alargados tipo brocheta»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Palas de ping pong y pelotitas»</t>
         </is>
       </c>
       <c r="K220" s="8" t="inlineStr"/>
@@ -10645,12 +10648,12 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>Palillos de madera largos (brocheta)</t>
+          <t>Palillos alargados tipo brocheta</t>
         </is>
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C221" s="11">
@@ -10661,25 +10664,25 @@
         <v>0</v>
       </c>
       <c r="E221" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I221" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Palillos de madera largos»</t>
+          <t>PIONEROS - Taller de tejer (Lluvia): «Palillos alargados tipo brocheta»</t>
         </is>
       </c>
       <c r="K221" s="13" t="inlineStr"/>
@@ -10688,12 +10691,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Palillos largos (bases)</t>
+          <t>Palillos de madera largos (brocheta)</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C222" s="6">
@@ -10701,10 +10704,10 @@
         <v/>
       </c>
       <c r="D222" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" s="3" t="n">
         <v>0</v>
@@ -10717,12 +10720,12 @@
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J222" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Palillos largos (bases)»</t>
+          <t>LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Palillos de madera largos»</t>
         </is>
       </c>
       <c r="K222" s="8" t="inlineStr"/>
@@ -10731,7 +10734,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>Palitos luminosos x3</t>
+          <t>Palillos largos (bases)</t>
         </is>
       </c>
       <c r="B223" s="10" t="inlineStr">
@@ -10744,7 +10747,7 @@
         <v/>
       </c>
       <c r="D223" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E223" s="10" t="n">
         <v>0</v>
@@ -10765,7 +10768,7 @@
       </c>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Palitos luminosos x3»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Palillos largos (bases)»</t>
         </is>
       </c>
       <c r="K223" s="13" t="inlineStr"/>
@@ -10774,7 +10777,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Palo de escoba</t>
+          <t>Palitos luminosos x3</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -10787,10 +10790,10 @@
         <v/>
       </c>
       <c r="D224" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" s="3" t="n">
         <v>0</v>
@@ -10808,7 +10811,7 @@
       </c>
       <c r="J224" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Palo de escoba»</t>
+          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Palitos luminosos x3»</t>
         </is>
       </c>
       <c r="K224" s="8" t="inlineStr"/>
@@ -10817,12 +10820,12 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>Papel albal</t>
+          <t>Palo de escoba</t>
         </is>
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C225" s="11">
@@ -10846,12 +10849,12 @@
       </c>
       <c r="I225" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J225" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Territorios (V-17/07 tarde 1): «Papel albal»</t>
+          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Palo de escoba»</t>
         </is>
       </c>
       <c r="K225" s="13" t="inlineStr"/>
@@ -10860,7 +10863,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Papel continuo</t>
+          <t>Papel albal</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -10873,26 +10876,69 @@
         <v/>
       </c>
       <c r="D226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Territorios (V-17/07 tarde 1): «Papel albal»</t>
+        </is>
+      </c>
+      <c r="K226" s="8" t="inlineStr"/>
+      <c r="L226" s="8" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>Papel continuo</t>
+        </is>
+      </c>
+      <c r="B227" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C227" s="11">
+        <f>SUM(D227:H227)</f>
+        <v/>
+      </c>
+      <c r="D227" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E226" s="3" t="n">
+      <c r="E227" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F226" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" s="3" t="n">
+      <c r="F227" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H226" s="3" t="n">
+      <c r="H227" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I226" s="3" t="inlineStr">
+      <c r="I227" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J226" s="7" t="inlineStr">
+      <c r="J227" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Normas de campamento + juegos (J-16/07 tarde 2): «Papel continuo 1m x 1m»
 CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Papel continuo 1x1»
@@ -10914,56 +10960,13 @@
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Papel»</t>
         </is>
       </c>
-      <c r="K226" s="8" t="inlineStr"/>
-      <c r="L226" s="8" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="9" t="inlineStr">
-        <is>
-          <t>Papel crepé verde, rojo y amarillo</t>
-        </is>
-      </c>
-      <c r="B227" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C227" s="11">
-        <f>SUM(D227:H227)</f>
-        <v/>
-      </c>
-      <c r="D227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I227" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J227" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Evaluación (X-29/07 tarde 2): «Papel crepé verde, rojo y amarillo»</t>
-        </is>
-      </c>
       <c r="K227" s="13" t="inlineStr"/>
       <c r="L227" s="13" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Papel de aluminio (albal)</t>
+          <t>Papel crepé verde, rojo y amarillo</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -10979,16 +10982,16 @@
         <v>0</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
@@ -10996,6 +10999,49 @@
         </is>
       </c>
       <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Evaluación (X-29/07 tarde 2): «Papel crepé verde, rojo y amarillo»</t>
+        </is>
+      </c>
+      <c r="K228" s="8" t="inlineStr"/>
+      <c r="L228" s="8" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>Papel de aluminio (albal)</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C229" s="11">
+        <f>SUM(D229:H229)</f>
+        <v/>
+      </c>
+      <c r="D229" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J229" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Preparación de volantes (noche) (S-18/07 noche): «Lumi»
 PIONEROS - Preparación volantes (noche) (S-18/07 noche): «Lumis»
@@ -11003,105 +11049,62 @@
 RUTAS ICARO - Preparación de raids (L-27/07): «Lumis»</t>
         </is>
       </c>
-      <c r="K228" s="8" t="inlineStr"/>
-      <c r="L228" s="8" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="9" t="inlineStr">
+      <c r="K229" s="13" t="inlineStr"/>
+      <c r="L229" s="13" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>Papel de cocina</t>
         </is>
       </c>
-      <c r="B229" s="10" t="inlineStr">
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C229" s="11">
-        <f>SUM(D229:H229)</f>
-        <v/>
-      </c>
-      <c r="D229" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E229" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H229" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I229" s="10" t="inlineStr">
+      <c r="C230" s="6">
+        <f>SUM(D230:H230)</f>
+        <v/>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J229" s="12" t="inlineStr">
+      <c r="J230" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Taller de tortilla de patata (S-25/07 tarde 1): «Papel de cocina»
 RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Papel de cocina»</t>
         </is>
       </c>
-      <c r="K229" s="13" t="inlineStr"/>
-      <c r="L229" s="13" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>Papel film</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C230" s="6">
-        <f>SUM(D230:H230)</f>
-        <v/>
-      </c>
-      <c r="D230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J230" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Papel film»</t>
-        </is>
-      </c>
       <c r="K230" s="8" t="inlineStr"/>
       <c r="L230" s="8" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>Papel higiénico y de cocina</t>
+          <t>Papel film</t>
         </is>
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>Higiene/limpieza</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C231" s="11">
@@ -11112,13 +11115,13 @@
         <v>0</v>
       </c>
       <c r="E231" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F231" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G231" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="10" t="n">
         <v>1</v>
@@ -11129,62 +11132,62 @@
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Papel film»</t>
+        </is>
+      </c>
+      <c r="K231" s="13" t="inlineStr"/>
+      <c r="L231" s="13" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Papel higiénico y de cocina</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>Higiene/limpieza</t>
+        </is>
+      </c>
+      <c r="C232" s="6">
+        <f>SUM(D232:H232)</f>
+        <v/>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J232" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Papel higiénico»
 PIONEROS - Raids (L-27 a M-28/07): «Papel higiénico»
 RUTAS ICARO - Raids (L-27 a M-28/07): «Papel higiénico»</t>
         </is>
       </c>
-      <c r="K231" s="13" t="inlineStr"/>
-      <c r="L231" s="13" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>Papel plastificado (lo lleva la comisión)</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C232" s="6">
-        <f>SUM(D232:H232)</f>
-        <v/>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F232" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H232" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J232" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «Papel plastificado (lo lleva la comisión)»</t>
-        </is>
-      </c>
       <c r="K232" s="8" t="inlineStr"/>
       <c r="L232" s="8" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>Papel seda de colores</t>
+          <t>Papel plastificado (lo lleva la comisión)</t>
         </is>
       </c>
       <c r="B233" s="10" t="inlineStr">
@@ -11200,7 +11203,7 @@
         <v>1</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F233" s="10" t="n">
         <v>0</v>
@@ -11217,61 +11220,61 @@
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «Papel plastificado (lo lleva la comisión)»</t>
+        </is>
+      </c>
+      <c r="K233" s="13" t="inlineStr"/>
+      <c r="L233" s="13" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Papel seda de colores</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C234" s="6">
+        <f>SUM(D234:H234)</f>
+        <v/>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J234" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Papel seda de colores»
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Papel seda de colores»</t>
         </is>
       </c>
-      <c r="K233" s="13" t="inlineStr"/>
-      <c r="L233" s="13" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>Papeles</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C234" s="6">
-        <f>SUM(D234:H234)</f>
-        <v/>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H234" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I234" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J234" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - Stalking con el Clan Ícaro (D-26/07 noche): «Papeles»</t>
-        </is>
-      </c>
       <c r="K234" s="8" t="inlineStr"/>
       <c r="L234" s="8" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>Papeles raid sorteo</t>
+          <t>Papeles</t>
         </is>
       </c>
       <c r="B235" s="10" t="inlineStr">
@@ -11293,10 +11296,10 @@
         <v>0</v>
       </c>
       <c r="G235" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" s="10" t="inlineStr">
         <is>
@@ -11305,7 +11308,7 @@
       </c>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Preparación raids (D-26/07 noche): «Papeles raid sorteo»</t>
+          <t>RUTAS PANDORA - Stalking con el Clan Ícaro (D-26/07 noche): «Papeles»</t>
         </is>
       </c>
       <c r="K235" s="13" t="inlineStr"/>
@@ -11314,7 +11317,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Papelitos dinámica</t>
+          <t>Papeles raid sorteo</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11336,10 +11339,10 @@
         <v>0</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
@@ -11348,7 +11351,7 @@
       </c>
       <c r="J236" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - PPV (Vali) (V-17/07): «Papelitos dinámica»</t>
+          <t>PIONEROS - Preparación raids (D-26/07 noche): «Papeles raid sorteo»</t>
         </is>
       </c>
       <c r="K236" s="8" t="inlineStr"/>
@@ -11357,12 +11360,12 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>Pasta moldeable de secado al aire: carne, rosa, azul, rojo, amarillo, blanco, negro</t>
+          <t>Papelitos dinámica</t>
         </is>
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C237" s="11">
@@ -11386,12 +11389,12 @@
       </c>
       <c r="I237" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J237" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Pasta moldeable de secado al aire: carne, rosa, azul, rojo, amarillo, blanco, negro»</t>
+          <t>RUTAS ICARO - PPV (Vali) (V-17/07): «Papelitos dinámica»</t>
         </is>
       </c>
       <c r="K237" s="13" t="inlineStr"/>
@@ -11400,7 +11403,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Pañoleta</t>
+          <t>Pasta moldeable de secado al aire: carne, rosa, azul, rojo, amarillo, blanco, negro</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11416,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F238" s="3" t="n">
         <v>0</v>
@@ -11425,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" s="3" t="inlineStr">
         <is>
@@ -11434,7 +11437,7 @@
       </c>
       <c r="J238" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Pañoleta»</t>
+          <t>RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Pasta moldeable de secado al aire: carne, rosa, azul, rojo, amarillo, blanco, negro»</t>
         </is>
       </c>
       <c r="K238" s="8" t="inlineStr"/>
@@ -11443,7 +11446,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>Pañoleta con tochos</t>
+          <t>Pañoleta</t>
         </is>
       </c>
       <c r="B239" s="10" t="inlineStr">
@@ -11468,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" s="10" t="inlineStr">
         <is>
@@ -11476,94 +11479,180 @@
         </is>
       </c>
       <c r="J239" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Pañoleta»</t>
+        </is>
+      </c>
+      <c r="K239" s="13" t="inlineStr"/>
+      <c r="L239" s="13" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Pañoleta con tochos</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C240" s="6">
+        <f>SUM(D240:H240)</f>
+        <v/>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J240" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Pañoleta con tochos»
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Pañoleta con tochos»</t>
         </is>
       </c>
-      <c r="K239" s="13" t="inlineStr"/>
-      <c r="L239" s="13" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+      <c r="K240" s="8" t="inlineStr"/>
+      <c r="L240" s="8" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="9" t="inlineStr">
         <is>
           <t>Pañoletas</t>
         </is>
       </c>
-      <c r="B240" s="3" t="inlineStr">
+      <c r="B241" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C240" s="6">
-        <f>SUM(D240:H240)</f>
-        <v/>
-      </c>
-      <c r="D240" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F240" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J240" s="7" t="inlineStr">
+      <c r="C241" s="11">
+        <f>SUM(D241:H241)</f>
+        <v/>
+      </c>
+      <c r="D241" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J241" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Juegos nocturnos (stalking) (S-25/07 noche): «Pañoletas»
 LOBATOS - Juegos (J-16/07 tarde 2): «Pañoletas»</t>
         </is>
       </c>
-      <c r="K240" s="8" t="inlineStr"/>
-      <c r="L240" s="8" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="9" t="inlineStr">
+      <c r="K241" s="13" t="inlineStr"/>
+      <c r="L241" s="13" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Pañuelos de colores (x8)</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C242" s="6">
+        <f>SUM(D242:H242)</f>
+        <v/>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J242" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Pañuelos de colores (x8)»</t>
+        </is>
+      </c>
+      <c r="K242" s="8" t="inlineStr"/>
+      <c r="L242" s="8" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="9" t="inlineStr">
         <is>
           <t>Pegamento / cola blanca</t>
         </is>
       </c>
-      <c r="B241" s="10" t="inlineStr">
+      <c r="B243" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C241" s="11">
-        <f>SUM(D241:H241)</f>
-        <v/>
-      </c>
-      <c r="D241" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F241" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" s="10" t="n">
+      <c r="C243" s="11">
+        <f>SUM(D243:H243)</f>
+        <v/>
+      </c>
+      <c r="D243" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H241" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I241" s="10" t="inlineStr">
+      <c r="H243" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J241" s="12" t="inlineStr">
+      <c r="J243" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Taller insignias (V-17/07 tarde): «Pegamentos»
 LOBATOS - Taller sexualidad: línea del tiempo (M-28/07 tarde 1): «Pegamento»
@@ -11571,99 +11660,13 @@
 PIONEROS - Cuenco serpentina (Lluvia): «Cola blanca»</t>
         </is>
       </c>
-      <c r="K241" s="13" t="inlineStr"/>
-      <c r="L241" s="13" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>Pegamento de goma eva</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C242" s="6">
-        <f>SUM(D242:H242)</f>
-        <v/>
-      </c>
-      <c r="D242" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J242" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Pegamento de goma eva»</t>
-        </is>
-      </c>
-      <c r="K242" s="8" t="inlineStr"/>
-      <c r="L242" s="8" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>Perforadora</t>
-        </is>
-      </c>
-      <c r="B243" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C243" s="11">
-        <f>SUM(D243:H243)</f>
-        <v/>
-      </c>
-      <c r="D243" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H243" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I243" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J243" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Perforadora»</t>
-        </is>
-      </c>
       <c r="K243" s="13" t="inlineStr"/>
       <c r="L243" s="13" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Periódicos y revistas</t>
+          <t>Pegamento de goma eva</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11676,7 +11679,7 @@
         <v/>
       </c>
       <c r="D244" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E244" s="3" t="n">
         <v>0</v>
@@ -11688,16 +11691,16 @@
         <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I244" s="3" t="inlineStr">
         <is>
-          <t>UNIDAD/COMISION</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J244" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Velada Vision Board (V-17/07 noche): «Periódicos y revistas (un par de cada)»</t>
+          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Pegamento de goma eva»</t>
         </is>
       </c>
       <c r="K244" s="8" t="inlineStr"/>
@@ -11706,12 +11709,12 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>Permanentes finos negros</t>
+          <t>Perforadora</t>
         </is>
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C245" s="11">
@@ -11728,10 +11731,10 @@
         <v>0</v>
       </c>
       <c r="G245" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" s="10" t="inlineStr">
         <is>
@@ -11740,7 +11743,7 @@
       </c>
       <c r="J245" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Permanentes finos negros»</t>
+          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Perforadora»</t>
         </is>
       </c>
       <c r="K245" s="13" t="inlineStr"/>
@@ -11749,12 +11752,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Picas</t>
+          <t>Periódicos y revistas</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C246" s="6">
@@ -11765,7 +11768,7 @@
         <v>0</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" s="3" t="n">
         <v>0</v>
@@ -11774,117 +11777,117 @@
         <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I246" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>UNIDAD/COMISION</t>
         </is>
       </c>
       <c r="J246" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Velada Vision Board (V-17/07 noche): «Periódicos y revistas (un par de cada)»</t>
+        </is>
+      </c>
+      <c r="K246" s="8" t="inlineStr"/>
+      <c r="L246" s="8" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="9" t="inlineStr">
+        <is>
+          <t>Permanentes finos negros</t>
+        </is>
+      </c>
+      <c r="B247" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C247" s="11">
+        <f>SUM(D247:H247)</f>
+        <v/>
+      </c>
+      <c r="D247" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J247" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Permanentes finos negros»</t>
+        </is>
+      </c>
+      <c r="K247" s="13" t="inlineStr"/>
+      <c r="L247" s="13" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Picas</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C248" s="6">
+        <f>SUM(D248:H248)</f>
+        <v/>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J248" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Picas»
 RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Pala o pica para excavar»</t>
         </is>
       </c>
-      <c r="K246" s="8" t="inlineStr"/>
-      <c r="L246" s="8" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="9" t="inlineStr">
-        <is>
-          <t>Piedras (de la campa)</t>
-        </is>
-      </c>
-      <c r="B247" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C247" s="11">
-        <f>SUM(D247:H247)</f>
-        <v/>
-      </c>
-      <c r="D247" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E247" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F247" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I247" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J247" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Juegos India (V-17/07 mañana): «Piedras (de la campa)»</t>
-        </is>
-      </c>
-      <c r="K247" s="13" t="inlineStr"/>
-      <c r="L247" s="13" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Piezas de metal de las bases que encajan</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C248" s="6">
-        <f>SUM(D248:H248)</f>
-        <v/>
-      </c>
-      <c r="D248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E248" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J248" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Lobatolimpiadas mentales (S-25/07 noche): «Piezas de metal de las bases que encajan»</t>
-        </is>
-      </c>
       <c r="K248" s="8" t="inlineStr"/>
       <c r="L248" s="8" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>Pinceles</t>
+          <t>Piedras (de la campa)</t>
         </is>
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C249" s="11">
@@ -11892,26 +11895,112 @@
         <v/>
       </c>
       <c r="D249" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J249" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Juegos India (V-17/07 mañana): «Piedras (de la campa)»</t>
+        </is>
+      </c>
+      <c r="K249" s="13" t="inlineStr"/>
+      <c r="L249" s="13" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Piezas de metal de las bases que encajan</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C250" s="6">
+        <f>SUM(D250:H250)</f>
+        <v/>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J250" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Lobatolimpiadas mentales (S-25/07 noche): «Piezas de metal de las bases que encajan»</t>
+        </is>
+      </c>
+      <c r="K250" s="8" t="inlineStr"/>
+      <c r="L250" s="8" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="9" t="inlineStr">
+        <is>
+          <t>Pinceles</t>
+        </is>
+      </c>
+      <c r="B251" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C251" s="11">
+        <f>SUM(D251:H251)</f>
+        <v/>
+      </c>
+      <c r="D251" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E249" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F249" s="10" t="n">
+      <c r="E251" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G249" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H249" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I249" s="10" t="inlineStr">
+      <c r="G251" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J249" s="12" t="inlineStr">
+      <c r="J251" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Pinceles»
 CASTORES - Taller de arcilla (S-25/07 tarde 1): «Pinceles»
@@ -11920,99 +12009,13 @@
 PIONEROS - Taller pintar tote bags (J-23/07 tarde 2): «Pinceles de varios tamaños»</t>
         </is>
       </c>
-      <c r="K249" s="13" t="inlineStr"/>
-      <c r="L249" s="13" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>Pintura acrílica</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C250" s="6">
-        <f>SUM(D250:H250)</f>
-        <v/>
-      </c>
-      <c r="D250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E250" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J250" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Pintura acrílica»</t>
-        </is>
-      </c>
-      <c r="K250" s="8" t="inlineStr"/>
-      <c r="L250" s="8" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t>Pintura de manos negra</t>
-        </is>
-      </c>
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C251" s="11">
-        <f>SUM(D251:H251)</f>
-        <v/>
-      </c>
-      <c r="D251" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F251" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I251" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J251" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Lluvia: Carteles con letras chinas (Lluvia): «Pintura de manos negra»</t>
-        </is>
-      </c>
       <c r="K251" s="13" t="inlineStr"/>
       <c r="L251" s="13" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Pintura para telas</t>
+          <t>Pintura acrílica</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -12025,16 +12028,16 @@
         <v/>
       </c>
       <c r="D252" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
         <v>0</v>
@@ -12045,104 +12048,104 @@
         </is>
       </c>
       <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Pintura acrílica»</t>
+        </is>
+      </c>
+      <c r="K252" s="8" t="inlineStr"/>
+      <c r="L252" s="8" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>Pintura de manos negra</t>
+        </is>
+      </c>
+      <c r="B253" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C253" s="11">
+        <f>SUM(D253:H253)</f>
+        <v/>
+      </c>
+      <c r="D253" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J253" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Lluvia: Carteles con letras chinas (Lluvia): «Pintura de manos negra»</t>
+        </is>
+      </c>
+      <c r="K253" s="13" t="inlineStr"/>
+      <c r="L253" s="13" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Pintura para telas</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C254" s="6">
+        <f>SUM(D254:H254)</f>
+        <v/>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Pintura para telas»
 PIONEROS - Taller pintar tote bags (J-23/07 tarde 2): «Pinturas acrílicas (o pintura para tela) de colores»</t>
         </is>
       </c>
-      <c r="K252" s="8" t="inlineStr"/>
-      <c r="L252" s="8" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="9" t="inlineStr">
-        <is>
-          <t>Pinturas blancas</t>
-        </is>
-      </c>
-      <c r="B253" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C253" s="11">
-        <f>SUM(D253:H253)</f>
-        <v/>
-      </c>
-      <c r="D253" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E253" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="F253" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I253" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J253" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Taller de estrellas (X-22/07 noche): «15 pinturas blancas»</t>
-        </is>
-      </c>
-      <c r="K253" s="13" t="inlineStr"/>
-      <c r="L253" s="13" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Pinturas de cara / maquillaje</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C254" s="6">
-        <f>SUM(D254:H254)</f>
-        <v/>
-      </c>
-      <c r="D254" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J254" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Pinturas de cara»</t>
-        </is>
-      </c>
       <c r="K254" s="8" t="inlineStr"/>
       <c r="L254" s="8" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>Pinturas o rotuladores</t>
+          <t>Pinturas blancas</t>
         </is>
       </c>
       <c r="B255" s="10" t="inlineStr">
@@ -12158,7 +12161,7 @@
         <v>0</v>
       </c>
       <c r="E255" s="10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F255" s="10" t="n">
         <v>0</v>
@@ -12176,7 +12179,7 @@
       </c>
       <c r="J255" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - GRUPAL: Gran Juego (S-18/07 mañana): «Pinturas o rotuladores»</t>
+          <t>LOBATOS - Taller de estrellas (X-22/07 noche): «15 pinturas blancas»</t>
         </is>
       </c>
       <c r="K255" s="13" t="inlineStr"/>
@@ -12185,7 +12188,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Pinturas para caracterizar villanos</t>
+          <t>Pinturas de cara / maquillaje</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -12198,10 +12201,10 @@
         <v/>
       </c>
       <c r="D256" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F256" s="3" t="n">
         <v>0</v>
@@ -12219,7 +12222,7 @@
       </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - GRUPAL: Velada inicial (J-16/07 noche): «Pinturas para caracterizar villanos»</t>
+          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Pinturas de cara»</t>
         </is>
       </c>
       <c r="K256" s="8" t="inlineStr"/>
@@ -12228,12 +12231,12 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>Pinzas (cobras)</t>
+          <t>Pinturas o rotuladores</t>
         </is>
       </c>
       <c r="B257" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C257" s="11">
@@ -12244,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="E257" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257" s="10" t="n">
         <v>0</v>
@@ -12257,12 +12260,12 @@
       </c>
       <c r="I257" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Pinzas (cobras)»</t>
+          <t>LOBATOS - GRUPAL: Gran Juego (S-18/07 mañana): «Pinturas o rotuladores»</t>
         </is>
       </c>
       <c r="K257" s="13" t="inlineStr"/>
@@ -12271,7 +12274,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Pinzas de madera</t>
+          <t>Pinturas para caracterizar villanos</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -12284,7 +12287,7 @@
         <v/>
       </c>
       <c r="D258" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258" s="3" t="n">
         <v>1</v>
@@ -12304,93 +12307,179 @@
         </is>
       </c>
       <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - GRUPAL: Velada inicial (J-16/07 noche): «Pinturas para caracterizar villanos»</t>
+        </is>
+      </c>
+      <c r="K258" s="8" t="inlineStr"/>
+      <c r="L258" s="8" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="9" t="inlineStr">
+        <is>
+          <t>Pinzas (cobras)</t>
+        </is>
+      </c>
+      <c r="B259" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C259" s="11">
+        <f>SUM(D259:H259)</f>
+        <v/>
+      </c>
+      <c r="D259" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G259" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I259" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J259" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Pinzas (cobras)»</t>
+        </is>
+      </c>
+      <c r="K259" s="13" t="inlineStr"/>
+      <c r="L259" s="13" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Pinzas de madera</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C260" s="6">
+        <f>SUM(D260:H260)</f>
+        <v/>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J260" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Talleres pinza (Bolsa de juegos): «Pinzas»
 LOBATOS - Taller de estrellas (X-22/07 noche): «Pinzas de madera»</t>
         </is>
       </c>
-      <c r="K258" s="8" t="inlineStr"/>
-      <c r="L258" s="8" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="9" t="inlineStr">
+      <c r="K260" s="8" t="inlineStr"/>
+      <c r="L260" s="8" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="9" t="inlineStr">
         <is>
           <t>Pinzas de orientación</t>
         </is>
       </c>
-      <c r="B259" s="10" t="inlineStr">
+      <c r="B261" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C259" s="11">
-        <f>SUM(D259:H259)</f>
-        <v/>
-      </c>
-      <c r="D259" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H259" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I259" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J259" s="12" t="inlineStr">
+      <c r="C261" s="11">
+        <f>SUM(D261:H261)</f>
+        <v/>
+      </c>
+      <c r="D261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J261" s="12" t="inlineStr">
         <is>
           <t>RUTAS PANDORA - Carrera de orientación (Reserva): «Pinzas de orientación»</t>
         </is>
       </c>
-      <c r="K259" s="13" t="inlineStr"/>
-      <c r="L259" s="13" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+      <c r="K261" s="13" t="inlineStr"/>
+      <c r="L261" s="13" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>Piquetas</t>
         </is>
       </c>
-      <c r="B260" s="3" t="inlineStr">
+      <c r="B262" s="3" t="inlineStr">
         <is>
           <t>Construccion/herramientas</t>
         </is>
       </c>
-      <c r="C260" s="6">
-        <f>SUM(D260:H260)</f>
-        <v/>
-      </c>
-      <c r="D260" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="3" t="n">
+      <c r="C262" s="6">
+        <f>SUM(D262:H262)</f>
+        <v/>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F260" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G260" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H260" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J260" s="7" t="inlineStr">
+      <c r="F262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J262" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Montaje (J-16/07 mañana): «Piquetas»
 LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Piquetas»
@@ -12398,104 +12487,18 @@
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Piquetas»</t>
         </is>
       </c>
-      <c r="K260" s="8" t="inlineStr"/>
-      <c r="L260" s="8" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="inlineStr">
-        <is>
-          <t>Placa de cartón + puntas (plinko)</t>
-        </is>
-      </c>
-      <c r="B261" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C261" s="11">
-        <f>SUM(D261:H261)</f>
-        <v/>
-      </c>
-      <c r="D261" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F261" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H261" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I261" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J261" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Placa de cartón + puntas (plinko)»</t>
-        </is>
-      </c>
-      <c r="K261" s="13" t="inlineStr"/>
-      <c r="L261" s="13" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>Plumas (manualidades)</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C262" s="6">
-        <f>SUM(D262:H262)</f>
-        <v/>
-      </c>
-      <c r="D262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I262" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J262" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Plumas»</t>
-        </is>
-      </c>
       <c r="K262" s="8" t="inlineStr"/>
       <c r="L262" s="8" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>Poleas para bandera</t>
+          <t>Placa de cartón + puntas (plinko)</t>
         </is>
       </c>
       <c r="B263" s="10" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C263" s="11">
@@ -12503,26 +12506,112 @@
         <v/>
       </c>
       <c r="D263" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J263" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Placa de cartón + puntas (plinko)»</t>
+        </is>
+      </c>
+      <c r="K263" s="13" t="inlineStr"/>
+      <c r="L263" s="13" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Plumas (manualidades)</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C264" s="6">
+        <f>SUM(D264:H264)</f>
+        <v/>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J264" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Plumas»</t>
+        </is>
+      </c>
+      <c r="K264" s="8" t="inlineStr"/>
+      <c r="L264" s="8" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="9" t="inlineStr">
+        <is>
+          <t>Poleas para bandera</t>
+        </is>
+      </c>
+      <c r="B265" s="10" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C265" s="11">
+        <f>SUM(D265:H265)</f>
+        <v/>
+      </c>
+      <c r="D265" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E263" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F263" s="10" t="n">
+      <c r="E265" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G263" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J263" s="12" t="inlineStr">
+      <c r="G265" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J265" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Poleas para banderas»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Poleas para banderas»
@@ -12530,99 +12619,13 @@
 EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «2 poleas para bandera»</t>
         </is>
       </c>
-      <c r="K263" s="13" t="inlineStr"/>
-      <c r="L263" s="13" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>Polvos Holi ecológicos (mirar los del año pasado)</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C264" s="6">
-        <f>SUM(D264:H264)</f>
-        <v/>
-      </c>
-      <c r="D264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J264" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - GRUPAL: Día guarro (X-22/07 día): «Polvos Holi ecológicos (mirar los del año pasado)»</t>
-        </is>
-      </c>
-      <c r="K264" s="8" t="inlineStr"/>
-      <c r="L264" s="8" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Pompones pequeños</t>
-        </is>
-      </c>
-      <c r="B265" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C265" s="11">
-        <f>SUM(D265:H265)</f>
-        <v/>
-      </c>
-      <c r="D265" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F265" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I265" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J265" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Taller insignias (V-17/07 tarde): «Pompones pequeños»</t>
-        </is>
-      </c>
       <c r="K265" s="13" t="inlineStr"/>
       <c r="L265" s="13" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Portada: 6 listones</t>
+          <t>Polvos Holi ecológicos (mirar los del año pasado)</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12638,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="E266" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F266" s="3" t="n">
         <v>0</v>
@@ -12647,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I266" s="3" t="inlineStr">
         <is>
@@ -12656,7 +12659,7 @@
       </c>
       <c r="J266" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Portada: 6 listones»</t>
+          <t>LOBATOS - GRUPAL: Día guarro (X-22/07 día): «Polvos Holi ecológicos (mirar los del año pasado)»</t>
         </is>
       </c>
       <c r="K266" s="8" t="inlineStr"/>
@@ -12665,7 +12668,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>Post-its</t>
+          <t>Pompones pequeños</t>
         </is>
       </c>
       <c r="B267" s="10" t="inlineStr">
@@ -12678,26 +12681,112 @@
         <v/>
       </c>
       <c r="D267" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E267" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F267" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J267" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Taller insignias (V-17/07 tarde): «Pompones pequeños»</t>
+        </is>
+      </c>
+      <c r="K267" s="13" t="inlineStr"/>
+      <c r="L267" s="13" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Portada: 6 listones</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C268" s="6">
+        <f>SUM(D268:H268)</f>
+        <v/>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J268" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Portada: 6 listones»</t>
+        </is>
+      </c>
+      <c r="K268" s="8" t="inlineStr"/>
+      <c r="L268" s="8" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>Post-its</t>
+        </is>
+      </c>
+      <c r="B269" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C269" s="11">
+        <f>SUM(D269:H269)</f>
+        <v/>
+      </c>
+      <c r="D269" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H267" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I267" s="10" t="inlineStr">
+      <c r="H269" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J267" s="12" t="inlineStr">
+      <c r="J269" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Presentación profunda (V-17/07 mañana): «Post-its (3 como mucho)»
 PIONEROS - Velada autopercepción (V-24/07 noche): «Post-its de colores»
@@ -12705,192 +12794,106 @@
 RUTAS PANDORA - PPV (V-17/07): «Post-its»</t>
         </is>
       </c>
-      <c r="K267" s="13" t="inlineStr"/>
-      <c r="L267" s="13" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+      <c r="K269" s="13" t="inlineStr"/>
+      <c r="L269" s="13" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>Preguntas scouts (kraalete)</t>
         </is>
       </c>
-      <c r="B268" s="3" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C268" s="6">
-        <f>SUM(D268:H268)</f>
-        <v/>
-      </c>
-      <c r="D268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I268" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J268" s="7" t="inlineStr">
+      <c r="C270" s="6">
+        <f>SUM(D270:H270)</f>
+        <v/>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J270" s="7" t="inlineStr">
         <is>
           <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Preguntas scouts (kraalete)»</t>
         </is>
       </c>
-      <c r="K268" s="8" t="inlineStr"/>
-      <c r="L268" s="8" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="9" t="inlineStr">
+      <c r="K270" s="8" t="inlineStr"/>
+      <c r="L270" s="8" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="9" t="inlineStr">
         <is>
           <t>Productos de limpieza (Fairy, estropajo, jabón)</t>
         </is>
       </c>
-      <c r="B269" s="10" t="inlineStr">
+      <c r="B271" s="10" t="inlineStr">
         <is>
           <t>Higiene/limpieza</t>
         </is>
       </c>
-      <c r="C269" s="11">
-        <f>SUM(D269:H269)</f>
-        <v/>
-      </c>
-      <c r="D269" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E269" s="10" t="n">
+      <c r="C271" s="11">
+        <f>SUM(D271:H271)</f>
+        <v/>
+      </c>
+      <c r="D271" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F269" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I269" s="10" t="inlineStr">
+      <c r="F271" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J269" s="12" t="inlineStr">
+      <c r="J271" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Fairy»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Fairy»
 LOBATOS - Gymkana de agua (V-24/07 mañana): «Jabón líquido o detergente suave»</t>
         </is>
       </c>
-      <c r="K269" s="13" t="inlineStr"/>
-      <c r="L269" s="13" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>Pruebas (kraalete)</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C270" s="6">
-        <f>SUM(D270:H270)</f>
-        <v/>
-      </c>
-      <c r="D270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J270" s="7" t="inlineStr">
-        <is>
-          <t>PIONEROS - Carrera de orientación (X-22/07 tarde): «Pruebas (kraalete)»</t>
-        </is>
-      </c>
-      <c r="K270" s="8" t="inlineStr"/>
-      <c r="L270" s="8" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>Puntero láser</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="inlineStr">
-        <is>
-          <t>Iluminacion/electronica</t>
-        </is>
-      </c>
-      <c r="C271" s="11">
-        <f>SUM(D271:H271)</f>
-        <v/>
-      </c>
-      <c r="D271" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F271" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I271" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J271" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Taller constelaciones (S-18/07 noche): «Puntero láser»</t>
-        </is>
-      </c>
       <c r="K271" s="13" t="inlineStr"/>
       <c r="L271" s="13" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Punzón y agujas</t>
+          <t>Pruebas (kraalete)</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C272" s="6">
@@ -12907,115 +12910,115 @@
         <v>0</v>
       </c>
       <c r="G272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J272" s="7" t="inlineStr">
+        <is>
+          <t>PIONEROS - Carrera de orientación (X-22/07 tarde): «Pruebas (kraalete)»</t>
+        </is>
+      </c>
+      <c r="K272" s="8" t="inlineStr"/>
+      <c r="L272" s="8" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>Puntero láser</t>
+        </is>
+      </c>
+      <c r="B273" s="10" t="inlineStr">
+        <is>
+          <t>Iluminacion/electronica</t>
+        </is>
+      </c>
+      <c r="C273" s="11">
+        <f>SUM(D273:H273)</f>
+        <v/>
+      </c>
+      <c r="D273" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J273" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Taller constelaciones (S-18/07 noche): «Puntero láser»</t>
+        </is>
+      </c>
+      <c r="K273" s="13" t="inlineStr"/>
+      <c r="L273" s="13" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Punzón y agujas</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C274" s="6">
+        <f>SUM(D274:H274)</f>
+        <v/>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I272" s="3" t="inlineStr">
+      <c r="H274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J272" s="7" t="inlineStr">
+      <c r="J274" s="7" t="inlineStr">
         <is>
           <t>PIONEROS - Decorar fotos (Lluvia): «Punzón»
 PIONEROS - Decorar fotos (Lluvia): «Agujas»</t>
         </is>
       </c>
-      <c r="K272" s="8" t="inlineStr"/>
-      <c r="L272" s="8" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>Puzzles de las bases</t>
-        </is>
-      </c>
-      <c r="B273" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C273" s="11">
-        <f>SUM(D273:H273)</f>
-        <v/>
-      </c>
-      <c r="D273" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E273" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F273" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I273" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J273" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Pruebas Herberth (J-23/07 tarde 1): «Puzzles de las bases»</t>
-        </is>
-      </c>
-      <c r="K273" s="13" t="inlineStr"/>
-      <c r="L273" s="13" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>Puño de mono (ganador)</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C274" s="6">
-        <f>SUM(D274:H274)</f>
-        <v/>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H274" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I274" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J274" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - ILLRA (L-20/07 tarde): «Puño de mono (ganador)»</t>
-        </is>
-      </c>
       <c r="K274" s="8" t="inlineStr"/>
       <c r="L274" s="8" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>Rana de sorteo</t>
+          <t>Puzzles de las bases</t>
         </is>
       </c>
       <c r="B275" s="10" t="inlineStr">
@@ -13034,162 +13037,162 @@
         <v>0</v>
       </c>
       <c r="F275" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J275" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Pruebas Herberth (J-23/07 tarde 1): «Puzzles de las bases»</t>
+        </is>
+      </c>
+      <c r="K275" s="13" t="inlineStr"/>
+      <c r="L275" s="13" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Puño de mono (ganador)</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C276" s="6">
+        <f>SUM(D276:H276)</f>
+        <v/>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J276" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - ILLRA (L-20/07 tarde): «Puño de mono (ganador)»</t>
+        </is>
+      </c>
+      <c r="K276" s="8" t="inlineStr"/>
+      <c r="L276" s="8" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Rana de sorteo</t>
+        </is>
+      </c>
+      <c r="B277" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C277" s="11">
+        <f>SUM(D277:H277)</f>
+        <v/>
+      </c>
+      <c r="D277" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G275" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I275" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J275" s="12" t="inlineStr">
+      <c r="G277" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J277" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Rana de sorteo»
 EXPLORADORES - FELSA (V-24/07 tarde 1): «Rana de sorteo»</t>
         </is>
       </c>
-      <c r="K275" s="13" t="inlineStr"/>
-      <c r="L275" s="13" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+      <c r="K277" s="13" t="inlineStr"/>
+      <c r="L277" s="13" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>Rastrillo y herramientas</t>
         </is>
       </c>
-      <c r="B276" s="3" t="inlineStr">
+      <c r="B278" s="3" t="inlineStr">
         <is>
           <t>Construccion/herramientas</t>
         </is>
       </c>
-      <c r="C276" s="6">
-        <f>SUM(D276:H276)</f>
-        <v/>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F276" s="3" t="n">
+      <c r="C278" s="6">
+        <f>SUM(D278:H278)</f>
+        <v/>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G276" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J276" s="7" t="inlineStr">
+      <c r="G278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J278" s="7" t="inlineStr">
         <is>
           <t>EXPLORADORES - Desmontar construcciones (M-29/07 mañana): «Rastrillo»
 EXPLORADORES - Desmontar construcciones (M-29/07 mañana): «Herramientas»</t>
         </is>
       </c>
-      <c r="K276" s="8" t="inlineStr"/>
-      <c r="L276" s="8" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Red de volleyball</t>
-        </is>
-      </c>
-      <c r="B277" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C277" s="11">
-        <f>SUM(D277:H277)</f>
-        <v/>
-      </c>
-      <c r="D277" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E277" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F277" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H277" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I277" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J277" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Red de volleyball»</t>
-        </is>
-      </c>
-      <c r="K277" s="13" t="inlineStr"/>
-      <c r="L277" s="13" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>Relojes x4 (si hay más mejor)</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C278" s="6">
-        <f>SUM(D278:H278)</f>
-        <v/>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F278" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H278" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I278" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J278" s="7" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Relojes x4 (si hay más mejor)»</t>
-        </is>
-      </c>
       <c r="K278" s="8" t="inlineStr"/>
       <c r="L278" s="8" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>Rotulador punta fina</t>
+          <t>Red de volleyball</t>
         </is>
       </c>
       <c r="B279" s="10" t="inlineStr">
@@ -13211,10 +13214,10 @@
         <v>0</v>
       </c>
       <c r="G279" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H279" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I279" s="10" t="inlineStr">
         <is>
@@ -13223,7 +13226,7 @@
       </c>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Rotulador punta fina»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Red de volleyball»</t>
         </is>
       </c>
       <c r="K279" s="13" t="inlineStr"/>
@@ -13232,7 +13235,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Rotuladores algo gorditos y normales</t>
+          <t>Relojes x4 (si hay más mejor)</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -13245,13 +13248,13 @@
         <v/>
       </c>
       <c r="D280" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F280" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G280" s="3" t="n">
         <v>0</v>
@@ -13266,7 +13269,7 @@
       </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Lluvia: Pintar piedras (Lluvia): «Rotuladores algo gorditos y normales»</t>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Relojes x4 (si hay más mejor)»</t>
         </is>
       </c>
       <c r="K280" s="8" t="inlineStr"/>
@@ -13275,12 +13278,12 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>Rotuladores de colores</t>
+          <t>Rotulador punta fina</t>
         </is>
       </c>
       <c r="B281" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C281" s="11">
@@ -13288,26 +13291,112 @@
         <v/>
       </c>
       <c r="D281" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J281" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Rotulador punta fina»</t>
+        </is>
+      </c>
+      <c r="K281" s="13" t="inlineStr"/>
+      <c r="L281" s="13" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Rotuladores algo gorditos y normales</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C282" s="6">
+        <f>SUM(D282:H282)</f>
+        <v/>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J282" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Lluvia: Pintar piedras (Lluvia): «Rotuladores algo gorditos y normales»</t>
+        </is>
+      </c>
+      <c r="K282" s="8" t="inlineStr"/>
+      <c r="L282" s="8" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>Rotuladores de colores</t>
+        </is>
+      </c>
+      <c r="B283" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C283" s="11">
+        <f>SUM(D283:H283)</f>
+        <v/>
+      </c>
+      <c r="D283" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="E281" s="10" t="n">
+      <c r="E283" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F281" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G281" s="10" t="n">
+      <c r="F283" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H281" s="10" t="n">
+      <c r="H283" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I281" s="10" t="inlineStr">
+      <c r="I283" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J281" s="12" t="inlineStr">
+      <c r="J283" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Normas de campamento + juegos (J-16/07 tarde 2): «Rotuladores»
 CASTORES - Hacer mochilas acampada volante (S-18/07 tarde 2): «Rotuladores»
@@ -13332,278 +13421,192 @@
 RUTAS ICARO - Actividad para Castores (X-22/07): «Rotuladores»</t>
         </is>
       </c>
-      <c r="K281" s="13" t="inlineStr"/>
-      <c r="L281" s="13" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+      <c r="K283" s="13" t="inlineStr"/>
+      <c r="L283" s="13" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
         <is>
           <t>Rotuladores negros</t>
         </is>
       </c>
-      <c r="B282" s="3" t="inlineStr">
+      <c r="B284" s="3" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C282" s="6">
-        <f>SUM(D282:H282)</f>
-        <v/>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I282" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J282" s="7" t="inlineStr">
+      <c r="C284" s="6">
+        <f>SUM(D284:H284)</f>
+        <v/>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J284" s="7" t="inlineStr">
         <is>
           <t>RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Rotuladores negros»</t>
         </is>
       </c>
-      <c r="K282" s="8" t="inlineStr"/>
-      <c r="L282" s="8" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="9" t="inlineStr">
+      <c r="K284" s="8" t="inlineStr"/>
+      <c r="L284" s="8" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
         <is>
           <t>Rotuladores permanentes</t>
         </is>
       </c>
-      <c r="B283" s="10" t="inlineStr">
+      <c r="B285" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C283" s="11">
-        <f>SUM(D283:H283)</f>
-        <v/>
-      </c>
-      <c r="D283" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E283" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F283" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G283" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H283" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I283" s="10" t="inlineStr">
+      <c r="C285" s="11">
+        <f>SUM(D285:H285)</f>
+        <v/>
+      </c>
+      <c r="D285" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J283" s="12" t="inlineStr">
+      <c r="J285" s="12" t="inlineStr">
         <is>
           <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Rotuladores permanentes finos»
 RUTAS PANDORA - PPV (V-17/07): «Permanentes»</t>
         </is>
       </c>
-      <c r="K283" s="13" t="inlineStr"/>
-      <c r="L283" s="13" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+      <c r="K285" s="13" t="inlineStr"/>
+      <c r="L285" s="13" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
         <is>
           <t>Rotuladores, pinturas, ceras</t>
         </is>
       </c>
-      <c r="B284" s="3" t="inlineStr">
+      <c r="B286" s="3" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C284" s="6">
-        <f>SUM(D284:H284)</f>
-        <v/>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
+      <c r="C286" s="6">
+        <f>SUM(D286:H286)</f>
+        <v/>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J284" s="7" t="inlineStr">
+      <c r="J286" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Rotuladores, pinturas, ceras»</t>
         </is>
       </c>
-      <c r="K284" s="8" t="inlineStr"/>
-      <c r="L284" s="8" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="9" t="inlineStr">
+      <c r="K286" s="8" t="inlineStr"/>
+      <c r="L286" s="8" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
         <is>
           <t>Rotus de colores</t>
         </is>
       </c>
-      <c r="B285" s="10" t="inlineStr">
+      <c r="B287" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C285" s="11">
-        <f>SUM(D285:H285)</f>
-        <v/>
-      </c>
-      <c r="D285" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E285" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F285" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H285" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I285" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J285" s="12" t="inlineStr">
+      <c r="C287" s="11">
+        <f>SUM(D287:H287)</f>
+        <v/>
+      </c>
+      <c r="D287" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J287" s="12" t="inlineStr">
         <is>
           <t>PIONEROS - Fe (V-24/07 tarde 2): «Rotus de colores»
 RUTAS ICARO - PPV (Vali) (V-17/07): «Rotus de colores»</t>
         </is>
       </c>
-      <c r="K285" s="13" t="inlineStr"/>
-      <c r="L285" s="13" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>Sangre de toro</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C286" s="6">
-        <f>SUM(D286:H286)</f>
-        <v/>
-      </c>
-      <c r="D286" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F286" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G286" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H286" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J286" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Sangre de toro»</t>
-        </is>
-      </c>
-      <c r="K286" s="8" t="inlineStr"/>
-      <c r="L286" s="8" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="9" t="inlineStr">
-        <is>
-          <t>Sellos (1 por niño)</t>
-        </is>
-      </c>
-      <c r="B287" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C287" s="11">
-        <f>SUM(D287:H287)</f>
-        <v/>
-      </c>
-      <c r="D287" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E287" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F287" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G287" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H287" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I287" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J287" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Sellos (1 por niño)»</t>
-        </is>
-      </c>
       <c r="K287" s="13" t="inlineStr"/>
       <c r="L287" s="13" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Serpentina de colores</t>
+          <t>Sangre de toro</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C288" s="6">
@@ -13614,25 +13617,25 @@
         <v>0</v>
       </c>
       <c r="E288" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H288" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I288" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="J288" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Cuenco serpentina (Lluvia): «Serpentina de colores»</t>
+          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Sangre de toro»</t>
         </is>
       </c>
       <c r="K288" s="8" t="inlineStr"/>
@@ -13641,12 +13644,12 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>Silbato</t>
+          <t>Sellos (1 por niño)</t>
         </is>
       </c>
       <c r="B289" s="10" t="inlineStr">
         <is>
-          <t>Juegos/deporte</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C289" s="11">
@@ -13657,23 +13660,109 @@
         <v>1</v>
       </c>
       <c r="E289" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J289" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Sellos (1 por niño)»</t>
+        </is>
+      </c>
+      <c r="K289" s="13" t="inlineStr"/>
+      <c r="L289" s="13" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Serpentina de colores</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C290" s="6">
+        <f>SUM(D290:H290)</f>
+        <v/>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J290" s="7" t="inlineStr">
+        <is>
+          <t>PIONEROS - Cuenco serpentina (Lluvia): «Serpentina de colores»</t>
+        </is>
+      </c>
+      <c r="K290" s="8" t="inlineStr"/>
+      <c r="L290" s="8" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>Silbato</t>
+        </is>
+      </c>
+      <c r="B291" s="10" t="inlineStr">
+        <is>
+          <t>Juegos/deporte</t>
+        </is>
+      </c>
+      <c r="C291" s="11">
+        <f>SUM(D291:H291)</f>
+        <v/>
+      </c>
+      <c r="D291" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F289" s="10" t="n">
+      <c r="F291" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G289" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H289" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I289" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J289" s="12" t="inlineStr">
+      <c r="G291" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J291" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Juegos nocturnos (stalking) (S-25/07 noche): «Silbato»
 LOBATOS - Juegos nocturnos (V-17/07 noche): «Silbatos»
@@ -13685,99 +13774,13 @@
 PIONEROS - Velada conjunta Tropa - Stratego (J-23/07 noche): «Silbato»</t>
         </is>
       </c>
-      <c r="K289" s="13" t="inlineStr"/>
-      <c r="L289" s="13" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>Silicona líquida</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C290" s="6">
-        <f>SUM(D290:H290)</f>
-        <v/>
-      </c>
-      <c r="D290" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F290" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G290" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="J290" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - Taller insignias (V-17/07 tarde): «Silicona líquida para pegar los imperdibles»</t>
-        </is>
-      </c>
-      <c r="K290" s="8" t="inlineStr"/>
-      <c r="L290" s="8" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="9" t="inlineStr">
-        <is>
-          <t>Sillas de camping del kraal (prestadas)</t>
-        </is>
-      </c>
-      <c r="B291" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C291" s="11">
-        <f>SUM(D291:H291)</f>
-        <v/>
-      </c>
-      <c r="D291" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E291" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F291" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G291" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H291" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I291" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J291" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Velada NNEE (S-25/07 noche): «Sillas de camping del kraal (prestadas)»</t>
-        </is>
-      </c>
       <c r="K291" s="13" t="inlineStr"/>
       <c r="L291" s="13" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Sobres</t>
+          <t>Silicona líquida</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -13796,124 +13799,124 @@
         <v>0</v>
       </c>
       <c r="F292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="J292" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Taller insignias (V-17/07 tarde): «Silicona líquida para pegar los imperdibles»</t>
+        </is>
+      </c>
+      <c r="K292" s="8" t="inlineStr"/>
+      <c r="L292" s="8" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>Sillas de camping del kraal (prestadas)</t>
+        </is>
+      </c>
+      <c r="B293" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C293" s="11">
+        <f>SUM(D293:H293)</f>
+        <v/>
+      </c>
+      <c r="D293" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H293" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J293" s="12" t="inlineStr">
+        <is>
+          <t>PIONEROS - Velada NNEE (S-25/07 noche): «Sillas de camping del kraal (prestadas)»</t>
+        </is>
+      </c>
+      <c r="K293" s="13" t="inlineStr"/>
+      <c r="L293" s="13" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Sobres</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C294" s="6">
+        <f>SUM(D294:H294)</f>
+        <v/>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G292" s="3" t="n">
+      <c r="G294" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H292" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
+      <c r="H294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J292" s="7" t="inlineStr">
+      <c r="J294" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Rastreo nocturno (V-17/07 noche): «Paquete de sobres»
 EXPLORADORES - Presentación profunda (V-17/07 mañana): «5 sobres»
 PIONEROS - Carrera de orientación (X-22/07 tarde): «Sobres pequeños x10»</t>
         </is>
       </c>
-      <c r="K292" s="8" t="inlineStr"/>
-      <c r="L292" s="8" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="9" t="inlineStr">
-        <is>
-          <t>Sombrajo (tela)</t>
-        </is>
-      </c>
-      <c r="B293" s="10" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C293" s="11">
-        <f>SUM(D293:H293)</f>
-        <v/>
-      </c>
-      <c r="D293" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E293" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F293" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G293" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H293" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I293" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J293" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Telas»</t>
-        </is>
-      </c>
-      <c r="K293" s="13" t="inlineStr"/>
-      <c r="L293" s="13" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>Tablas rotas</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C294" s="6">
-        <f>SUM(D294:H294)</f>
-        <v/>
-      </c>
-      <c r="D294" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F294" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G294" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J294" s="7" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablas rotas»</t>
-        </is>
-      </c>
       <c r="K294" s="8" t="inlineStr"/>
       <c r="L294" s="8" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>Tablita para columpio</t>
+          <t>Sombrajo (tela)</t>
         </is>
       </c>
       <c r="B295" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C295" s="11">
@@ -13924,10 +13927,10 @@
         <v>0</v>
       </c>
       <c r="E295" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G295" s="10" t="n">
         <v>0</v>
@@ -13942,7 +13945,7 @@
       </c>
       <c r="J295" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablita para columpio»</t>
+          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Telas»</t>
         </is>
       </c>
       <c r="K295" s="13" t="inlineStr"/>
@@ -13951,7 +13954,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Tablones de madera</t>
+          <t>Tablas rotas</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -13985,7 +13988,7 @@
       </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablones de madera»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablas rotas»</t>
         </is>
       </c>
       <c r="K296" s="8" t="inlineStr"/>
@@ -13994,7 +13997,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>Tapones 6</t>
+          <t>Tablita para columpio</t>
         </is>
       </c>
       <c r="B297" s="10" t="inlineStr">
@@ -14010,10 +14013,10 @@
         <v>0</v>
       </c>
       <c r="E297" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F297" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G297" s="10" t="n">
         <v>0</v>
@@ -14028,7 +14031,7 @@
       </c>
       <c r="J297" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Tapones 6»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablita para columpio»</t>
         </is>
       </c>
       <c r="K297" s="13" t="inlineStr"/>
@@ -14037,7 +14040,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Tarjetas de personajes (unidad)</t>
+          <t>Tablones de madera</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -14071,7 +14074,7 @@
       </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Presentación profunda (V-17/07 mañana): «Tarjetas de personajes (unidad)»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Tablones de madera»</t>
         </is>
       </c>
       <c r="K298" s="8" t="inlineStr"/>
@@ -14080,7 +14083,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>Tarros con líquidos de color (x5 colores)</t>
+          <t>Tapones 6</t>
         </is>
       </c>
       <c r="B299" s="10" t="inlineStr">
@@ -14096,10 +14099,10 @@
         <v>0</v>
       </c>
       <c r="E299" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F299" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G299" s="10" t="n">
         <v>0</v>
@@ -14114,7 +14117,7 @@
       </c>
       <c r="J299" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Tarros con líquidos de color (x5 colores)»</t>
+          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Tapones 6»</t>
         </is>
       </c>
       <c r="K299" s="13" t="inlineStr"/>
@@ -14123,12 +14126,12 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Telas, disfraces y maquillaje de caracterización</t>
+          <t>Tarjetas de personajes (unidad)</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Textil/disfraces</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C300" s="6">
@@ -14136,26 +14139,112 @@
         <v/>
       </c>
       <c r="D300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J300" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Presentación profunda (V-17/07 mañana): «Tarjetas de personajes (unidad)»</t>
+        </is>
+      </c>
+      <c r="K300" s="8" t="inlineStr"/>
+      <c r="L300" s="8" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="9" t="inlineStr">
+        <is>
+          <t>Tarros con líquidos de color (x5 colores)</t>
+        </is>
+      </c>
+      <c r="B301" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C301" s="11">
+        <f>SUM(D301:H301)</f>
+        <v/>
+      </c>
+      <c r="D301" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G301" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J301" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Tarros con líquidos de color (x5 colores)»</t>
+        </is>
+      </c>
+      <c r="K301" s="13" t="inlineStr"/>
+      <c r="L301" s="13" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Telas, disfraces y maquillaje de caracterización</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Textil/disfraces</t>
+        </is>
+      </c>
+      <c r="C302" s="6">
+        <f>SUM(D302:H302)</f>
+        <v/>
+      </c>
+      <c r="D302" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E300" s="3" t="n">
+      <c r="E302" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F300" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G300" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H300" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J300" s="7" t="inlineStr">
+      <c r="F302" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J302" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Normas de campamento + juegos (J-16/07 tarde 2): «Tela pequeña o pañoleta (pañuelito)»
 CASTORES - Caza Gamusino (M-21/07 noche): «6 sacos de tela»
@@ -14170,135 +14259,135 @@
 PIONEROS - Carrera de orientación (X-22/07 tarde): «Trozos de telas pequeños (o cinta reflectante) de 2 colores»</t>
         </is>
       </c>
-      <c r="K300" s="8" t="inlineStr"/>
-      <c r="L300" s="8" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="9" t="inlineStr">
+      <c r="K302" s="8" t="inlineStr"/>
+      <c r="L302" s="8" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="9" t="inlineStr">
         <is>
           <t>Textiles para talleres (camisetas, tote bags)</t>
         </is>
       </c>
-      <c r="B301" s="10" t="inlineStr">
+      <c r="B303" s="10" t="inlineStr">
         <is>
           <t>Textil/disfraces</t>
         </is>
       </c>
-      <c r="C301" s="11">
-        <f>SUM(D301:H301)</f>
-        <v/>
-      </c>
-      <c r="D301" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E301" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F301" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G301" s="10">
+      <c r="C303" s="11">
+        <f>SUM(D303:H303)</f>
+        <v/>
+      </c>
+      <c r="D303" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F303" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" s="10">
         <f>CONFIG!$B$5</f>
         <v/>
       </c>
-      <c r="H301" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I301" s="10" t="inlineStr">
+      <c r="H303" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" s="10" t="inlineStr">
         <is>
           <t>LO TRAE EL NINO</t>
         </is>
       </c>
-      <c r="J301" s="12" t="inlineStr">
+      <c r="J303" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Camiseta blanca o básica (cada castor debe llevar una)»
 LOBATOS - Voluntariado conjunto Lobatos-Pioneros (J-23/07 mañana): «Camiseta de cambio»</t>
         </is>
       </c>
-      <c r="K301" s="13" t="inlineStr"/>
-      <c r="L301" s="13" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
+      <c r="K303" s="13" t="inlineStr"/>
+      <c r="L303" s="13" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>Tiendas de campaña</t>
         </is>
       </c>
-      <c r="B302" s="3" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr">
         <is>
           <t>Construccion/herramientas</t>
         </is>
       </c>
-      <c r="C302" s="6">
-        <f>SUM(D302:H302)</f>
-        <v/>
-      </c>
-      <c r="D302" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F302" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G302" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I302" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J302" s="7" t="inlineStr">
+      <c r="C304" s="6">
+        <f>SUM(D304:H304)</f>
+        <v/>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G304" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J304" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Montaje (J-16/07 mañana): «Tiendas»
 EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Tiendas»
 RUTAS ICARO - Construcciones (J-16/07): «Tienda»</t>
         </is>
       </c>
-      <c r="K302" s="8" t="inlineStr"/>
-      <c r="L302" s="8" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="9" t="inlineStr">
+      <c r="K304" s="8" t="inlineStr"/>
+      <c r="L304" s="8" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="9" t="inlineStr">
         <is>
           <t>Tijeras</t>
         </is>
       </c>
-      <c r="B303" s="10" t="inlineStr">
+      <c r="B305" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C303" s="11">
-        <f>SUM(D303:H303)</f>
-        <v/>
-      </c>
-      <c r="D303" s="10" t="n">
+      <c r="C305" s="11">
+        <f>SUM(D305:H305)</f>
+        <v/>
+      </c>
+      <c r="D305" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E303" s="10" t="n">
+      <c r="E305" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F303" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" s="10" t="n">
+      <c r="F305" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H303" s="10" t="n">
+      <c r="H305" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I303" s="10" t="inlineStr">
+      <c r="I305" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J303" s="12" t="inlineStr">
+      <c r="J305" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Tijeras de punta redonda»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Tijeras de punta redonda»
@@ -14317,104 +14406,18 @@
 RUTAS ICARO - Voluntariado Manuela (J-23/07): «Tijeras»</t>
         </is>
       </c>
-      <c r="K303" s="13" t="inlineStr"/>
-      <c r="L303" s="13" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>Tronquitos (se encarga la unidad)</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C304" s="6">
-        <f>SUM(D304:H304)</f>
-        <v/>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F304" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H304" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J304" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Tronquitos (se encarga la unidad)»</t>
-        </is>
-      </c>
-      <c r="K304" s="8" t="inlineStr"/>
-      <c r="L304" s="8" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="9" t="inlineStr">
-        <is>
-          <t>Tubos de PVC liso 16mm cortados a 50cm (1 por explorador)</t>
-        </is>
-      </c>
-      <c r="B305" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C305" s="11">
-        <f>SUM(D305:H305)</f>
-        <v/>
-      </c>
-      <c r="D305" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E305" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F305" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G305" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H305" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I305" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J305" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Tubos de PVC liso 16mm cortados a 50cm (1 por explorador)»</t>
-        </is>
-      </c>
       <c r="K305" s="13" t="inlineStr"/>
       <c r="L305" s="13" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Témperas</t>
+          <t>Tronquitos (se encarga la unidad)</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C306" s="6">
@@ -14422,26 +14425,112 @@
         <v/>
       </c>
       <c r="D306" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J306" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Tronquitos (se encarga la unidad)»</t>
+        </is>
+      </c>
+      <c r="K306" s="8" t="inlineStr"/>
+      <c r="L306" s="8" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>Tubos de PVC liso 16mm cortados a 50cm (1 por explorador)</t>
+        </is>
+      </c>
+      <c r="B307" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C307" s="11">
+        <f>SUM(D307:H307)</f>
+        <v/>
+      </c>
+      <c r="D307" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G307" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J307" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Tubos de PVC liso 16mm cortados a 50cm (1 por explorador)»</t>
+        </is>
+      </c>
+      <c r="K307" s="13" t="inlineStr"/>
+      <c r="L307" s="13" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Témperas</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C308" s="6">
+        <f>SUM(D308:H308)</f>
+        <v/>
+      </c>
+      <c r="D308" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E306" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F306" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H306" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I306" s="3" t="inlineStr">
+      <c r="E308" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J306" s="7" t="inlineStr">
+      <c r="J308" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Témperas (colores a concretar)»
 CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Témperas y 10 pinceles»
@@ -14450,186 +14539,100 @@
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Témperas»</t>
         </is>
       </c>
-      <c r="K306" s="8" t="inlineStr"/>
-      <c r="L306" s="8" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="9" t="inlineStr">
+      <c r="K308" s="8" t="inlineStr"/>
+      <c r="L308" s="8" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="inlineStr">
         <is>
           <t>Tótem 'Paco'</t>
         </is>
       </c>
-      <c r="B307" s="10" t="inlineStr">
+      <c r="B309" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C307" s="11">
-        <f>SUM(D307:H307)</f>
-        <v/>
-      </c>
-      <c r="D307" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E307" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F307" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H307" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I307" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J307" s="12" t="inlineStr">
+      <c r="C309" s="11">
+        <f>SUM(D309:H309)</f>
+        <v/>
+      </c>
+      <c r="D309" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J309" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Consejo de troncos (V-24/07 noche): «Tótem 'Paco'»</t>
         </is>
       </c>
-      <c r="K307" s="13" t="inlineStr"/>
-      <c r="L307" s="13" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
+      <c r="K309" s="13" t="inlineStr"/>
+      <c r="L309" s="13" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
         <is>
           <t>Un banco</t>
         </is>
       </c>
-      <c r="B308" s="3" t="inlineStr">
+      <c r="B310" s="3" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C308" s="6">
-        <f>SUM(D308:H308)</f>
-        <v/>
-      </c>
-      <c r="D308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I308" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J308" s="7" t="inlineStr">
+      <c r="C310" s="6">
+        <f>SUM(D310:H310)</f>
+        <v/>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J310" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Un banco»
 RUTAS ICARO - Actividad para Lobatos (Charlie y David) (J-23/07): «Un banco»</t>
         </is>
       </c>
-      <c r="K308" s="8" t="inlineStr"/>
-      <c r="L308" s="8" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="9" t="inlineStr">
-        <is>
-          <t>Una caja de cartón</t>
-        </is>
-      </c>
-      <c r="B309" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C309" s="11">
-        <f>SUM(D309:H309)</f>
-        <v/>
-      </c>
-      <c r="D309" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E309" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F309" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G309" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H309" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I309" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J309" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Una caja de cartón»</t>
-        </is>
-      </c>
-      <c r="K309" s="13" t="inlineStr"/>
-      <c r="L309" s="13" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>Vasija</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C310" s="6">
-        <f>SUM(D310:H310)</f>
-        <v/>
-      </c>
-      <c r="D310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E310" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I310" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J310" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Vasija»</t>
-        </is>
-      </c>
       <c r="K310" s="8" t="inlineStr"/>
       <c r="L310" s="8" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>Vasitos o cucharitas</t>
+          <t>Una caja de cartón</t>
         </is>
       </c>
       <c r="B311" s="10" t="inlineStr">
@@ -14663,7 +14666,7 @@
       </c>
       <c r="J311" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - GRUPAL: Día guarro (X-22/07 día): «Vasitos o cucharitas»</t>
+          <t>LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Una caja de cartón»</t>
         </is>
       </c>
       <c r="K311" s="13" t="inlineStr"/>
@@ -14672,12 +14675,12 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Velas</t>
+          <t>Vasija</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Iluminacion/electronica</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C312" s="6">
@@ -14688,7 +14691,7 @@
         <v>0</v>
       </c>
       <c r="E312" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" s="3" t="n">
         <v>0</v>
@@ -14697,14 +14700,100 @@
         <v>0</v>
       </c>
       <c r="H312" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J312" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - GRUPAL: Barracas - El Gran Bazar (D-26/07 tarde): «Vasija»</t>
+        </is>
+      </c>
+      <c r="K312" s="8" t="inlineStr"/>
+      <c r="L312" s="8" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>Vasitos o cucharitas</t>
+        </is>
+      </c>
+      <c r="B313" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C313" s="11">
+        <f>SUM(D313:H313)</f>
+        <v/>
+      </c>
+      <c r="D313" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J313" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - GRUPAL: Día guarro (X-22/07 día): «Vasitos o cucharitas»</t>
+        </is>
+      </c>
+      <c r="K313" s="13" t="inlineStr"/>
+      <c r="L313" s="13" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Velas</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Iluminacion/electronica</t>
+        </is>
+      </c>
+      <c r="C314" s="6">
+        <f>SUM(D314:H314)</f>
+        <v/>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I312" s="3" t="inlineStr">
+      <c r="I314" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="J312" s="7" t="inlineStr">
+      <c r="J314" s="7" t="inlineStr">
         <is>
           <t>RUTAS PANDORA - Línea de la vida (Volante noche): «Velas pequeñas (15)»
 RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Velas altas»
@@ -14712,61 +14801,61 @@
 RUTAS ICARO - OLIMPIADAS (grupal) (X-29/07 mañana): «Velas»</t>
         </is>
       </c>
-      <c r="K312" s="8" t="inlineStr"/>
-      <c r="L312" s="8" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="9" t="inlineStr">
+      <c r="K314" s="8" t="inlineStr"/>
+      <c r="L314" s="8" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="inlineStr">
         <is>
           <t>Walkie-talkies</t>
         </is>
       </c>
-      <c r="B313" s="10" t="inlineStr">
+      <c r="B315" s="10" t="inlineStr">
         <is>
           <t>Iluminacion/electronica</t>
         </is>
       </c>
-      <c r="C313" s="11">
-        <f>SUM(D313:H313)</f>
-        <v/>
-      </c>
-      <c r="D313" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E313" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F313" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G313" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H313" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I313" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="J313" s="12" t="inlineStr">
+      <c r="C315" s="11">
+        <f>SUM(D315:H315)</f>
+        <v/>
+      </c>
+      <c r="D315" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F315" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G315" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I315" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="J315" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Chalecos y Walkie talkies»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Chalecos y Walkie talkies»
 EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Walkie-talkies»</t>
         </is>
       </c>
-      <c r="K313" s="13" t="inlineStr"/>
-      <c r="L313" s="13" t="inlineStr"/>
+      <c r="K315" s="13" t="inlineStr"/>
+      <c r="L315" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L313"/>
+  <autoFilter ref="A1:L315"/>
   <dataValidations count="2">
-    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245 I246 I247 I248 I249 I250 I251 I252 I253 I254 I255 I256 I257 I258 I259 I260 I261 I262 I263 I264 I265 I266 I267 I268 I269 I270 I271 I272 I273 I274 I275 I276 I277 I278 I279 I280 I281 I282 I283 I284 I285 I286 I287 I288 I289 I290 I291 I292 I293 I294 I295 I296 I297 I298 I299 I300 I301 I302 I303 I304 I305 I306 I307 I308 I309 I310 I311 I312 I313" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245 I246 I247 I248 I249 I250 I251 I252 I253 I254 I255 I256 I257 I258 I259 I260 I261 I262 I263 I264 I265 I266 I267 I268 I269 I270 I271 I272 I273 I274 I275 I276 I277 I278 I279 I280 I281 I282 I283 I284 I285 I286 I287 I288 I289 I290 I291 I292 I293 I294 I295 I296 I297 I298 I299 I300 I301 I302 I303 I304 I305 I306 I307 I308 I309 I310 I311 I312 I313 I314 I315" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"COMPRAR,YA HAY (bases) - revisar,LO TRAE EL NINO,UNIDAD/COMISION,PEDIR A COCINA/MENU"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300 B301 B302 B303 B304 B305 B306 B307 B308 B309 B310 B311 B312 B313" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300 B301 B302 B303 B304 B305 B306 B307 B308 B309 B310 B311 B312 B313 B314 B315" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Construccion/herramientas,Papeleria/manualidades,Juegos/deporte,Cocina/menaje,Iluminacion/electronica,Higiene/limpieza,Textil/disfraces,Impresiones/documentacion,Equipo campamento,Otros"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16383,7 +16472,12 @@
 Conos
 Folios
 Bolis
-Saco y cuerda gorda</t>
+Saco y cuerda gorda
+5 aros pequeños para prender
+Pañuelos de colores (x8)
+Alambre
+Gasolina
+Mechero</t>
         </is>
       </c>
     </row>

--- a/LISTA_COMPRA_CAMPAMENTO.xlsx
+++ b/LISTA_COMPRA_CAMPAMENTO.xlsx
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Harina (alternativa para celíacos, para esconder las gominolas en los cubos cantidad en función del tamaño de cubos</t>
+          <t>Harina (alternativa para celíacos, para esconder las gominolas en los cubos cantidad en función del tamaño de cubos)</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>))</t>
+          <t>1 bote de espárragos</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -2786,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - GRAN JUEGO (S-18/07 mañana): «))»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 bote de espárragos»</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1 bote de espárragos</t>
+          <t>1 caja</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 bote de espárragos»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 caja»</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>1 caja</t>
+          <t>1 llave</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 caja»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 llave»</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1 llave</t>
+          <t>1 paquete de chía</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 llave»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 paquete de chía»</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>1 paquete de chía</t>
+          <t>10 mantas</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «1 paquete de chía»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «10 mantas»</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10 mantas</t>
+          <t>150 globos</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3010,13 +3010,13 @@
         <v/>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «10 mantas»</t>
+          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «150 globos»</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>150 globos</t>
+          <t>2 barreños</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="D11" s="10" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>0</v>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «150 globos»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «2 barreños»</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2 barreños</t>
+          <t>2 lumis</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3102,11 +3102,11 @@
         <v/>
       </c>
       <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «2 barreños»</t>
+          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «2 lumis»</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2 lumis</t>
+          <t>2 pechugas de pollo</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -3151,17 +3151,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" s="10" t="n">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «2 lumis»</t>
+          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «2 pechugas de pollo»</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2 pechugas de pollo</t>
+          <t>2 rollos de pita grandes</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3200,13 +3200,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «2 pechugas de pollo»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «2 rollos de pita grandes»</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2 rollos de pita grandes</t>
+          <t>2 rotuladores</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «2 rollos de pita grandes»</t>
+          <t>EXPLORADORES - Velada de código morse (V-17/07 noche): «2 rotuladores»</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr"/>
@@ -3273,7 +3273,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2 rotuladores</t>
+          <t>2 sillas</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3286,13 +3286,13 @@
         <v/>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de código morse (V-17/07 noche): «2 rotuladores»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «2 sillas»</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2 sillas</t>
+          <t>20 esponjas de las que pesan con agua</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -3332,7 +3332,7 @@
         <v/>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «2 sillas»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «20 esponjas de las que pesan con agua»</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20 esponjas de las que pesan con agua</t>
+          <t>3 mantas</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3378,7 +3378,7 @@
         <v/>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «20 esponjas de las que pesan con agua»</t>
+          <t>CASTORES - Taller constelaciones (S-18/07 noche): «3 mantas»</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>3 mantas</t>
+          <t>30 pinzas de 3 colores distintos (10 de cada)</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -3424,13 +3424,13 @@
         <v/>
       </c>
       <c r="D19" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>0</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Taller constelaciones (S-18/07 noche): «3 mantas»</t>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «30 pinzas de 3 colores distintos (10 de cada)»</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>30 pinzas de 3 colores distintos (10 de cada)</t>
+          <t>4 botellas pequeñas</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3470,13 +3470,13 @@
         <v/>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «30 pinzas de 3 colores distintos (10 de cada)»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 botellas pequeñas»</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>4 botellas pequeñas</t>
+          <t>4 cubos</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 botellas pequeñas»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 cubos»</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>4 cubos</t>
+          <t>4 garrafas de agua (da igual tamaño)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 cubos»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 garrafas de agua (da igual tamaño)»</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr"/>
@@ -3595,7 +3595,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>4 garrafas de agua (da igual tamaño)</t>
+          <t>4 tobilleras de gimnasio o similares (ref Temu en el doc)</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «4 garrafas de agua (da igual tamaño)»</t>
+          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «4 tobilleras de gimnasio o similares (ref Temu en el doc)»</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr"/>
@@ -3641,12 +3641,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>4 tobilleras de gimnasio o similares (ref Temu en el doc)</t>
+          <t>5 cartulinas</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C24" s="6">
@@ -3654,13 +3654,13 @@
         <v/>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0</v>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «4 tobilleras de gimnasio o similares (ref Temu en el doc)»</t>
+          <t>EXPLORADORES - Miss y Mister: sacos de especias (M-29/07 tarde 1): «5 cartulinas»</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr"/>
@@ -3687,12 +3687,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>5 cartulinas</t>
+          <t>5 pieles de kiwi</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C25" s="11">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Miss y Mister: sacos de especias (M-29/07 tarde 1): «5 cartulinas»</t>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «5 pieles de kiwi»</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr"/>
@@ -3733,12 +3733,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>5 pieles de kiwi</t>
+          <t>Abalorios</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C26" s="6">
@@ -3749,85 +3749,85 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «5 pieles de kiwi»</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Abalorios</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C27" s="11">
-        <f>SUM(D27:I27)</f>
-        <v/>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - El amuleto del elefante sagrado (orientación) (X-22/07 tarde): «Abalorios grandes y pequeños de distintos colores (7 bolsas, si son pequeñas más)»
 LOBATOS - Atrapasueños (L-27/07 tarde 1): «Abalorios»
 RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Abalorios»</t>
         </is>
       </c>
+      <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C27" s="11">
+        <f>SUM(D27:I27)</f>
+        <v/>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Aceite»</t>
+        </is>
+      </c>
       <c r="L27" s="13" t="inlineStr"/>
       <c r="M27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Aceite</t>
+          <t>Aceite de oliva</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3846,13 +3846,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Aceite»</t>
+          <t>EXPLORADORES - Masterchef pizza (V-24/07 mañana): «Aceite de oliva»</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Aceite de oliva</t>
+          <t>Agua</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -3886,10 +3886,10 @@
         <v/>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>1</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>0</v>
@@ -3909,52 +3909,6 @@
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Masterchef pizza (V-24/07 mañana): «Aceite de oliva»</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr"/>
-      <c r="M29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agua</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C30" s="6">
-        <f>SUM(D30:I30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Agua»
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Agua»
@@ -3964,18 +3918,64 @@
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Agua»</t>
         </is>
       </c>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Akela</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C30" s="6">
+        <f>SUM(D30:I30)</f>
+        <v/>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Akela»</t>
+        </is>
+      </c>
       <c r="L30" s="8" t="inlineStr"/>
       <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Akela</t>
+          <t>Alambre</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C31" s="11">
@@ -3989,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>0</v>
@@ -3998,73 +3998,73 @@
         <v>0</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Akela»</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr"/>
-      <c r="M31" s="13" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Alambre</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C32" s="6">
-        <f>SUM(D32:I32)</f>
-        <v/>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Alambre»
 EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Alambre»
 COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Alambre, coger para forrar LOS 5 aritos»</t>
         </is>
       </c>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Alcohol 96º</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C32" s="6">
+        <f>SUM(D32:I32)</f>
+        <v/>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Alcohol 96º»</t>
+        </is>
+      </c>
       <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Alcohol 96º</t>
+          <t>Alcohol o parafina</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Alcohol 96º»</t>
+          <t>COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Alcohol o parafina»</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr"/>
@@ -4110,12 +4110,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Alcohol o parafina</t>
+          <t>Alcotanas</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C34" s="6">
@@ -4129,16 +4129,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4146,100 +4146,54 @@
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Alcohol o parafina»</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Alcotanas</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C35" s="11">
-        <f>SUM(D35:I35)</f>
-        <v/>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «6 alcotanas»
 EXPLORADORES - Desmontar construcciones (M-29/07 mañana): «Alcotana»
 PIONEROS - Construcciones (J-16 y V-17/07): «Alcotanas»</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr"/>
-      <c r="M35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Algodón</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C36" s="6">
-        <f>SUM(D36:I36)</f>
-        <v/>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="C35" s="11">
+        <f>SUM(D35:I35)</f>
+        <v/>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="I35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>PIONEROS - Actividad Clan Ícaro - Drogas (S-18/07 tarde 1): «Algodón»
 PIONEROS - Taller pintar tote bags (J-23/07 tarde 2): «Tote bags 100% algodón x1 por chaval»
@@ -4247,18 +4201,64 @@
 RUTAS ICARO - Taller para Pioneros - Drogas (S-18/07): «Algodón»</t>
         </is>
       </c>
+      <c r="L35" s="13" t="inlineStr"/>
+      <c r="M35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Alguna herramienta básica</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C36" s="6">
+        <f>SUM(D36:I36)</f>
+        <v/>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Voluntariado Manuela (J-23/07): «Alguna herramienta básica»</t>
+        </is>
+      </c>
       <c r="L36" s="8" t="inlineStr"/>
       <c r="M36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Alguna herramienta básica</t>
+          <t>Altavoz bluetooth</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Iluminacion/electronica</t>
         </is>
       </c>
       <c r="C37" s="11">
@@ -4266,22 +4266,22 @@
         <v/>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
@@ -4289,52 +4289,6 @@
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Voluntariado Manuela (J-23/07): «Alguna herramienta básica»</t>
-        </is>
-      </c>
-      <c r="L37" s="13" t="inlineStr"/>
-      <c r="M37" s="13" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Altavoz bluetooth</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Iluminacion/electronica</t>
-        </is>
-      </c>
-      <c r="C38" s="6">
-        <f>SUM(D38:I38)</f>
-        <v/>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Taller constelaciones (S-18/07 noche): «Altavoz (música relajante)»
 LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Altavoz»
@@ -4347,13 +4301,60 @@
 COMISIONES - GRAN JUEGO (S-18/07 mañana): «Altavoz»</t>
         </is>
       </c>
+      <c r="L37" s="13" t="inlineStr"/>
+      <c r="M37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Anillas de llavero</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C38" s="6">
+        <f>SUM(D38:I38)</f>
+        <v/>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Anillas de llavero»
+COMISIONES - VELADA INICIAL (J-16/07 noche): «Llaves»</t>
+        </is>
+      </c>
       <c r="L38" s="8" t="inlineStr"/>
       <c r="M38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Anillas de llavero</t>
+          <t>Arcilla</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -4365,8 +4366,9 @@
         <f>SUM(D39:I39)</f>
         <v/>
       </c>
-      <c r="D39" s="10" t="n">
-        <v>0</v>
+      <c r="D39" s="10">
+        <f>CONFIG!$B$2*0.5</f>
+        <v/>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
@@ -4378,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
@@ -4390,8 +4392,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Anillas de llavero»
-COMISIONES - VELADA INICIAL (J-16/07 noche): «Llaves»</t>
+          <t>CASTORES - Taller de arcilla (S-25/07 tarde 1): «X kilos de arcilla (AÑADIR CUANDO SE SEPA Nº DE NIÑOS)»</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr"/>
@@ -4400,24 +4401,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Arcilla</t>
+          <t>Arco</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C40" s="6">
         <f>SUM(D40:I40)</f>
         <v/>
       </c>
-      <c r="D40" s="3">
-        <f>CONFIG!$B$2*0.5</f>
-        <v/>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -4433,12 +4433,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Taller de arcilla (S-25/07 tarde 1): «X kilos de arcilla (AÑADIR CUANDO SE SEPA Nº DE NIÑOS)»</t>
+          <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Arco»
+LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Arco»</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr"/>
@@ -4447,7 +4448,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Arco</t>
+          <t>Arena fina</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -4460,7 +4461,7 @@
         <v/>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1</v>
@@ -4472,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>0</v>
@@ -4484,8 +4485,8 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Arco»
-LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Arco»</t>
+          <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Arena fina»
+RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Arena fina»</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr"/>
@@ -4494,7 +4495,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Arena fina</t>
+          <t>Arena gruesa</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4531,8 +4532,8 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Arena fina»
-RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Arena fina»</t>
+          <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Arena gruesa»
+RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Arena gruesa»</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr"/>
@@ -4541,12 +4542,12 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Arena gruesa</t>
+          <t>Aros de plástico</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juegos/deporte</t>
         </is>
       </c>
       <c r="C43" s="11">
@@ -4557,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>0</v>
@@ -4566,10 +4567,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
@@ -4577,53 +4578,6 @@
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Arena gruesa»
-RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Arena gruesa»</t>
-        </is>
-      </c>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Aros de plástico</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Juegos/deporte</t>
-        </is>
-      </c>
-      <c r="C44" s="6">
-        <f>SUM(D44:I44)</f>
-        <v/>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Aros»
 LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Un palo/algo para meter aros»
@@ -4634,13 +4588,59 @@
 COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Papel pinocho de los 5 colores de los aros olímpicos que no papel de seda»</t>
         </is>
       </c>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Awen (peluche castor)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C44" s="6">
+        <f>SUM(D44:I44)</f>
+        <v/>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Awen (peluche castor)»</t>
+        </is>
+      </c>
       <c r="L44" s="8" t="inlineStr"/>
       <c r="M44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Awen (peluche castor)</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>1</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>0</v>
@@ -4676,52 +4676,6 @@
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Awen (peluche castor)»</t>
-        </is>
-      </c>
-      <c r="L45" s="13" t="inlineStr"/>
-      <c r="M45" s="13" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Balde</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C46" s="6">
-        <f>SUM(D46:I46)</f>
-        <v/>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Balde»
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Balde»
@@ -4730,18 +4684,64 @@
 RUTAS ICARO - Taller para Pioneros - Drogas (S-18/07): «Balde»</t>
         </is>
       </c>
+      <c r="L45" s="13" t="inlineStr"/>
+      <c r="M45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Balde grande y objetos que floten un poco (para la Pesca en el Ganges).</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C46" s="6">
+        <f>SUM(D46:I46)</f>
+        <v/>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>COMISIONES - BARRACAS (D-26/07 tarde): «Balde grande y objetos que floten un poco (para la Pesca en el Ganges).»</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr"/>
       <c r="M46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Balde grande y objetos que floten un poco (para la Pesca en el Ganges).</t>
+          <t>Balones y pelotas deportivas / Petanca</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juegos/deporte</t>
         </is>
       </c>
       <c r="C47" s="11">
@@ -4749,22 +4749,22 @@
         <v/>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
@@ -4772,52 +4772,6 @@
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>COMISIONES - BARRACAS (D-26/07 tarde): «Balde grande y objetos que floten un poco (para la Pesca en el Ganges).»</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="inlineStr"/>
-      <c r="M47" s="13" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Balones y pelotas deportivas / Petanca</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Juegos/deporte</t>
-        </is>
-      </c>
-      <c r="C48" s="6">
-        <f>SUM(D48:I48)</f>
-        <v/>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Normas de campamento + juegos (J-16/07 tarde 2): «Balón»
 LOBATOS - Juegos (J-16/07 tarde 2): «Balón goma espuma»
@@ -4843,13 +4797,59 @@
 COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Pelotas de pin-pon»</t>
         </is>
       </c>
+      <c r="L47" s="13" t="inlineStr"/>
+      <c r="M47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Bancos</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C48" s="6">
+        <f>SUM(D48:I48)</f>
+        <v/>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Bancos»</t>
+        </is>
+      </c>
       <c r="L48" s="8" t="inlineStr"/>
       <c r="M48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Bancos</t>
+          <t>Bancos del comedor</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -4865,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="10" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Bancos»</t>
+          <t>COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Bancos del comedor»</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr"/>
@@ -4895,7 +4895,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Bancos del comedor</t>
+          <t>Bancos, mesa (circuito)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -4917,13 +4917,13 @@
         <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Bancos del comedor»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Bancos, mesa (circuito)»</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr"/>
@@ -4941,7 +4941,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Bancos, mesa (circuito)</t>
+          <t>Bandera de castores</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -4954,7 +4954,7 @@
         <v/>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="10" t="n">
         <v>0</v>
@@ -4978,7 +4978,8 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Bancos, mesa (circuito)»</t>
+          <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Bandera de castores»
+CASTORES - Construcciones zona común (V-17/07 mañana): «Bandera de castores»</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr"/>
@@ -4987,7 +4988,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Bandera de castores</t>
+          <t>Bandera de lobatos</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -5000,10 +5001,10 @@
         <v/>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
@@ -5024,8 +5025,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Bandera de castores»
-CASTORES - Construcciones zona común (V-17/07 mañana): «Bandera de castores»</t>
+          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Bandera de lobatos»</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr"/>
@@ -5034,7 +5034,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Bandera de lobatos</t>
+          <t>Bandera rutas</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Roca del Consejo (V-24/07 noche): «Bandera de lobatos»</t>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Bandera rutas»</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr"/>
@@ -5080,7 +5080,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Bandera rutas</t>
+          <t>Barreños (8)</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -5105,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Bandera rutas»</t>
+          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Barreños (8)»</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Barreños (8)</t>
+          <t>Bingo (David)</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -5151,10 +5151,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Barreños (8)»</t>
+          <t>RUTAS ICARO - Taller David (V-17/07): «Bingo (David)»</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr"/>
@@ -5172,12 +5172,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Bingo (David)</t>
+          <t>Boli de tinta invisible</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C56" s="6">
@@ -5185,22 +5185,22 @@
         <v/>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -5208,52 +5208,6 @@
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Taller David (V-17/07): «Bingo (David)»</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="inlineStr"/>
-      <c r="M56" s="8" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>Boli de tinta invisible</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C57" s="11">
-        <f>SUM(D57:I57)</f>
-        <v/>
-      </c>
-      <c r="D57" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H57" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I57" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Cuento de imágenes (Bolsa de juegos): «Bolis»
 CASTORES - Dinámica abanico (Bolsa de juegos): «Bolis»
@@ -5281,48 +5235,48 @@
 COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Bolis»</t>
         </is>
       </c>
-      <c r="L57" s="13" t="inlineStr"/>
-      <c r="M57" s="13" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Bolígrafos</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C58" s="6">
-        <f>SUM(D58:I58)</f>
-        <v/>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="n">
+      <c r="C57" s="11">
+        <f>SUM(D57:I57)</f>
+        <v/>
+      </c>
+      <c r="D57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="n">
+      <c r="F57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="H57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="I57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K57" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - ILLRA (L-20/07 tarde): «Bolígrafos»
 LOBATOS - Teleclub (M-21/07 noche): «Bolígrafos»
@@ -5338,13 +5292,59 @@
 RUTAS ICARO - Taller David (V-17/07): «Bolígrafo»</t>
         </is>
       </c>
+      <c r="L57" s="13" t="inlineStr"/>
+      <c r="M57" s="13" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Botella de agua</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C58" s="6">
+        <f>SUM(D58:I58)</f>
+        <v/>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Piscina pueblo (con Pioneros) (J-23/07 día): «Botella de agua»</t>
+        </is>
+      </c>
       <c r="L58" s="8" t="inlineStr"/>
       <c r="M58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Botella de agua</t>
+          <t>Botella de plástico</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I59" s="10" t="n">
         <v>0</v>
@@ -5380,70 +5380,70 @@
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Piscina pueblo (con Pioneros) (J-23/07 día): «Botella de agua»</t>
-        </is>
-      </c>
-      <c r="L59" s="13" t="inlineStr"/>
-      <c r="M59" s="13" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Botella de plástico</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C60" s="6">
-        <f>SUM(D60:I60)</f>
-        <v/>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Botella de plástico»
 RUTAS PANDORA - Actividad de adicciones con pipis (J-16/07): «Botella de plástico»
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Botella de plástico»</t>
         </is>
       </c>
+      <c r="L59" s="13" t="inlineStr"/>
+      <c r="M59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Botella de vidrio (de los chinos) de este estilo. No sé cómo especificar tamaño, es para guardar papelitos doblados (me llamáis si no).</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C60" s="6">
+        <f>SUM(D60:I60)</f>
+        <v/>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>COMISIONES - FE (V-24/07 tarde): «Botella de vidrio (de los chinos) de este estilo. No sé cómo especificar tamaño, es para guardar papelitos doblados (me llamáis si no).»</t>
+        </is>
+      </c>
       <c r="L60" s="8" t="inlineStr"/>
       <c r="M60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Botella de vidrio (de los chinos) de este estilo. No sé cómo especificar tamaño, es para guardar papelitos doblados (me llamáis si no).</t>
+          <t>Botellas de plástico</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C61" s="11">
@@ -5460,22 +5460,23 @@
         <v>0</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - FE (V-24/07 tarde): «Botella de vidrio (de los chinos) de este estilo. No sé cómo especificar tamaño, es para guardar papelitos doblados (me llamáis si no).»</t>
+          <t>PIONEROS - Actividad Clan Ícaro - Drogas (S-18/07 tarde 1): «Botellas de plástico»
+RUTAS ICARO - Taller para Pioneros - Drogas (S-18/07): «Botellas de plástico»</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr"/>
@@ -5484,12 +5485,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Botellas de plástico</t>
+          <t>Botiquín de primeros auxilios / Tarjetas sanitarias</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Higiene/limpieza</t>
         </is>
       </c>
       <c r="C62" s="6">
@@ -5497,22 +5498,22 @@
         <v/>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -5520,53 +5521,6 @@
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>PIONEROS - Actividad Clan Ícaro - Drogas (S-18/07 tarde 1): «Botellas de plástico»
-RUTAS ICARO - Taller para Pioneros - Drogas (S-18/07): «Botellas de plástico»</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="inlineStr"/>
-      <c r="M62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>Botiquín de primeros auxilios / Tarjetas sanitarias</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Higiene/limpieza</t>
-        </is>
-      </c>
-      <c r="C63" s="11">
-        <f>SUM(D63:I63)</f>
-        <v/>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Botiquín»
 CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Tarjetas sanitarias niños»
@@ -5588,13 +5542,59 @@
 COMISIONES - FE (V-24/07 tarde): «Toallitas para limpiarse (un paquete o si se lleva de botiquín)»</t>
         </is>
       </c>
+      <c r="L62" s="8" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>Báscula</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C63" s="11">
+        <f>SUM(D63:I63)</f>
+        <v/>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Báscula»</t>
+        </is>
+      </c>
       <c r="L63" s="13" t="inlineStr"/>
       <c r="M63" s="13" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Báscula</t>
+          <t>Caja de madera que se pueda cerrar</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Báscula»</t>
+          <t>EXPLORADORES - Actividad maristas (L-20/07 tarde): «Caja de madera que se pueda cerrar»</t>
         </is>
       </c>
       <c r="L64" s="8" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>Caja de madera que se pueda cerrar</t>
+          <t>Caja de palillos (dientes)</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C65" s="11">
@@ -5653,13 +5653,13 @@
         <v/>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="10" t="n">
         <v>0</v>
@@ -5672,12 +5672,12 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Actividad maristas (L-20/07 tarde): «Caja de madera que se pueda cerrar»</t>
+          <t>CASTORES - Taller de arcilla (S-25/07 tarde 1): «Caja de palillos»</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr"/>
@@ -5686,12 +5686,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Caja de palillos (dientes)</t>
+          <t>Cajas grandes de cartón del chino por niño +3</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C66" s="6">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Taller de arcilla (S-25/07 tarde 1): «Caja de palillos»</t>
+          <t>CASTORES - Organizar mochilero (J-16/07 tarde 1): «Cajas grandes de cartón del chino por niño +3»</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr"/>
@@ -5732,7 +5732,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>Cajas grandes de cartón del chino por niño +3</t>
+          <t>Cancioneros</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -5745,13 +5745,13 @@
         <v/>
       </c>
       <c r="D67" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0</v>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
@@ -5768,65 +5768,65 @@
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Organizar mochilero (J-16/07 tarde 1): «Cajas grandes de cartón del chino por niño +3»</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr"/>
-      <c r="M67" s="13" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Cancioneros</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C68" s="6">
-        <f>SUM(D68:I68)</f>
-        <v/>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Cancioneros»
 EXPLORADORES - FELSA (V-24/07 tarde 1): «Cancioneros»
 COMISIONES - FE (V-24/07 tarde): «Cancioneros»</t>
         </is>
       </c>
+      <c r="L67" s="13" t="inlineStr"/>
+      <c r="M67" s="13" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Canicas</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C68" s="6">
+        <f>SUM(D68:I68)</f>
+        <v/>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Canicas»</t>
+        </is>
+      </c>
       <c r="L68" s="8" t="inlineStr"/>
       <c r="M68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>Canicas</t>
+          <t>Carbón vegetal</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -5839,10 +5839,10 @@
         <v/>
       </c>
       <c r="D69" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" s="10" t="n">
         <v>0</v>
@@ -5862,70 +5862,70 @@
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Canicas»</t>
-        </is>
-      </c>
-      <c r="L69" s="13" t="inlineStr"/>
-      <c r="M69" s="13" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Carbón vegetal</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C70" s="6">
-        <f>SUM(D70:I70)</f>
-        <v/>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Clan Ícaro: brújula casera y potabilizar (V-24/07 tarde 1): «Carbón vegetal»
 RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Carbón vegetal»
 RUTAS ICARO - Técnicas scouts (brújula casera, potabilizar) (V-24/07): «Carbón vegetal»</t>
         </is>
       </c>
+      <c r="L69" s="13" t="inlineStr"/>
+      <c r="M69" s="13" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Cartel rutas</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C70" s="6">
+        <f>SUM(D70:I70)</f>
+        <v/>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Cartel rutas»</t>
+        </is>
+      </c>
       <c r="L70" s="8" t="inlineStr"/>
       <c r="M70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>Cartel rutas</t>
+          <t>Cartones</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C71" s="11">
@@ -5936,16 +5936,16 @@
         <v>0</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="10" t="n">
         <v>0</v>
@@ -5957,7 +5957,8 @@
       </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Cartel rutas»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Cartones (3-4 cajas grandes)»
+PIONEROS - Taller de tejer (Lluvia): «Cartones (recortes pequeños)»</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr"/>
@@ -5966,7 +5967,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Cartones</t>
+          <t>Cartulina A3 grises claras</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5982,29 +5983,28 @@
         <v>0</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Cartones (3-4 cajas grandes)»
-PIONEROS - Taller de tejer (Lluvia): «Cartones (recortes pequeños)»</t>
+          <t>RUTAS ICARO - Velada Vision Board (V-17/07 noche): «Cartulina A3 grises claras»</t>
         </is>
       </c>
       <c r="L72" s="8" t="inlineStr"/>
@@ -6013,7 +6013,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>Cartulina A3 grises claras</t>
+          <t>Cartulina blanca A4</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -6026,7 +6026,7 @@
         <v/>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="10" t="n">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="10" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Velada Vision Board (V-17/07 noche): «Cartulina A3 grises claras»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Cartulina blanca A4»</t>
         </is>
       </c>
       <c r="L73" s="13" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Cartulina blanca A4</t>
+          <t>Cartulina para el himno</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -6072,10 +6072,10 @@
         <v/>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Cartulina blanca A4»</t>
+          <t>LOBATOS - ILLRA (L-20/07 tarde): «Cartulina para el himno»</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr"/>
@@ -6105,7 +6105,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>Cartulina para el himno</t>
+          <t>Cartulinas A4 de colores</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -6118,10 +6118,11 @@
         <v/>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E75" s="10">
+        <f>CONFIG!$B$3</f>
+        <v/>
       </c>
       <c r="F75" s="10" t="n">
         <v>0</v>
@@ -6130,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="10" t="n">
         <v>0</v>
@@ -6141,53 +6142,6 @@
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - ILLRA (L-20/07 tarde): «Cartulina para el himno»</t>
-        </is>
-      </c>
-      <c r="L75" s="13" t="inlineStr"/>
-      <c r="M75" s="13" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Cartulinas A4 de colores</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C76" s="6">
-        <f>SUM(D76:I76)</f>
-        <v/>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" s="3">
-        <f>CONFIG!$B$3</f>
-        <v/>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Actividad Clan Ícaro (X-22/07 tarde 2): «Cartulina»
 CASTORES - Talleres pinza (Bolsa de juegos): «Cartulina»
@@ -6195,13 +6149,59 @@
 RUTAS ICARO - Actividad para Castores (X-22/07): «Cartulina»</t>
         </is>
       </c>
+      <c r="L75" s="13" t="inlineStr"/>
+      <c r="M75" s="13" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Cartulinas amarillas 2 A4</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C76" s="6">
+        <f>SUM(D76:I76)</f>
+        <v/>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>PIONEROS - Taller de estrellas (V-17/07 noche): «Cartulinas amarillas 2 A4»</t>
+        </is>
+      </c>
       <c r="L76" s="8" t="inlineStr"/>
       <c r="M76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>Cartulinas amarillas 2 A4</t>
+          <t>Cartulinas de colores A4 (1 por niño)</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -6214,7 +6214,7 @@
         <v/>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="10" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="10" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Taller de estrellas (V-17/07 noche): «Cartulinas amarillas 2 A4»</t>
+          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Cartulinas de colores A4 (1 por niño)»</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr"/>
@@ -6247,7 +6247,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Cartulinas de colores A4 (1 por niño)</t>
+          <t>Cartulinas negras</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -6260,10 +6260,10 @@
         <v/>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Cartulinas de colores A4 (1 por niño)»</t>
+          <t>LOBATOS - Taller de estrellas (X-22/07 noche): «20 cartulinas negras»</t>
         </is>
       </c>
       <c r="L78" s="8" t="inlineStr"/>
@@ -6293,12 +6293,12 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>Cartulinas negras</t>
+          <t>Cascos inalámbricos y un móvil (o tapones)</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C79" s="11">
@@ -6309,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F79" s="10" t="n">
         <v>0</v>
@@ -6318,19 +6318,19 @@
         <v>0</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Taller de estrellas (X-22/07 noche): «20 cartulinas negras»</t>
+          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Cascos inalámbricos y un móvil (o tapones)»</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Cascos inalámbricos y un móvil (o tapones)</t>
+          <t>Casquería (texturas, en descripción)</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6352,7 +6352,7 @@
         <v/>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>0</v>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Cocina con hándicaps (gyozas/empanadillas) (J-23/07): «Cascos inalámbricos y un móvil (o tapones)»</t>
+          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Casquería (texturas, en descripción)»</t>
         </is>
       </c>
       <c r="L80" s="8" t="inlineStr"/>
@@ -6385,12 +6385,12 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>Casquería (texturas, en descripción)</t>
+          <t>Celo</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C81" s="11">
@@ -6398,16 +6398,16 @@
         <v/>
       </c>
       <c r="D81" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="10" t="n">
         <v>0</v>
@@ -6417,56 +6417,10 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>CASTORES - Entrenamiento Caza Gamusino (M-21/07 tarde 1): «Casquería (texturas, en descripción)»</t>
-        </is>
-      </c>
-      <c r="L81" s="13" t="inlineStr"/>
-      <c r="M81" s="13" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Celo</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C82" s="6">
-        <f>SUM(D82:I82)</f>
-        <v/>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Normas de campamento + juegos (J-16/07 tarde 2): «Celo gordo»
 CASTORES - T.E.G.A. (Torneo de Globos) (V-17/07 tarde 2): «Celo»
@@ -6474,13 +6428,59 @@
 PIONEROS - Pulseras (Lluvia): «Celo»</t>
         </is>
       </c>
+      <c r="L81" s="13" t="inlineStr"/>
+      <c r="M81" s="13" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Cerillas o mechero</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C82" s="6">
+        <f>SUM(D82:I82)</f>
+        <v/>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Acampada volante (x3 días) (D-19 a M-21/07): «Cerillas o mechero»</t>
+        </is>
+      </c>
       <c r="L82" s="8" t="inlineStr"/>
       <c r="M82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>Cerillas o mechero</t>
+          <t>Cerillas/mecheros</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="K83" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Acampada volante (x3 días) (D-19 a M-21/07): «Cerillas o mechero»</t>
+          <t>RUTAS PANDORA - Línea de la vida (Volante noche): «Cerillas/mecheros»</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr"/>
@@ -6526,7 +6526,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Cerillas/mecheros</t>
+          <t>Chalecos</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -6545,13 +6545,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0</v>
@@ -6562,52 +6562,6 @@
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - Línea de la vida (Volante noche): «Cerillas/mecheros»</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr"/>
-      <c r="M84" s="8" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>Chalecos</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C85" s="11">
-        <f>SUM(D85:I85)</f>
-        <v/>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr">
         <is>
           <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Chalecos»
 PIONEROS - Volantes (x3 días) (D-19 a M-21/07): «Chalecos»
@@ -6618,13 +6572,60 @@
 RUTAS ICARO - Voluntariado Manuela (J-23/07): «Chalecos»</t>
         </is>
       </c>
+      <c r="L84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Chalecos reflectantes</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C85" s="11">
+        <f>SUM(D85:I85)</f>
+        <v/>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Servicio en el pueblo (J-23/07 mañana): «Chalecos reflectantes»
+RUTAS ICARO - Raids (L-27 a M-28/07): «Chalecos reflectantes»</t>
+        </is>
+      </c>
       <c r="L85" s="13" t="inlineStr"/>
       <c r="M85" s="13" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Chalecos reflectantes</t>
+          <t>Chalecos reflectantes 1 por explorador y kraalete</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -6649,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>0</v>
@@ -6661,8 +6662,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Servicio en el pueblo (J-23/07 mañana): «Chalecos reflectantes»
-RUTAS ICARO - Raids (L-27 a M-28/07): «Chalecos reflectantes»</t>
+          <t>EXPLORADORES - Raids (L-27/07): «Chalecos reflectantes 1 por explorador y kraalete»</t>
         </is>
       </c>
       <c r="L86" s="8" t="inlineStr"/>
@@ -6671,7 +6671,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>Chalecos reflectantes 1 por explorador y kraalete</t>
+          <t>Chapa naranja (vueltas de pañoleta)</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -6684,13 +6684,13 @@
         <v/>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="10" t="n">
         <v>0</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Raids (L-27/07): «Chalecos reflectantes 1 por explorador y kraalete»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Chapa naranja (vueltas de pañoleta)»</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr"/>
@@ -6717,12 +6717,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Chapa naranja (vueltas de pañoleta)</t>
+          <t>Chinchetas</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C88" s="6">
@@ -6730,13 +6730,13 @@
         <v/>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0</v>
@@ -6749,12 +6749,13 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Chapa naranja (vueltas de pañoleta)»</t>
+          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Chinchetas»
+EXPLORADORES - FELSA (V-24/07 tarde 1): «Chinchetas»</t>
         </is>
       </c>
       <c r="L88" s="8" t="inlineStr"/>
@@ -6763,12 +6764,12 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>Chinchetas</t>
+          <t>Churros</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C89" s="11">
@@ -6779,10 +6780,10 @@
         <v>0</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -6795,13 +6796,12 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Chinchetas»
-EXPLORADORES - FELSA (V-24/07 tarde 1): «Chinchetas»</t>
+          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Churros»</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr"/>
@@ -6810,12 +6810,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Churros</t>
+          <t>Cigarrillos</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C90" s="6">
@@ -6826,168 +6826,122 @@
         <v>0</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Churros»</t>
-        </is>
-      </c>
-      <c r="L90" s="8" t="inlineStr"/>
-      <c r="M90" s="8" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>Cigarrillos</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C91" s="11">
-        <f>SUM(D91:I91)</f>
-        <v/>
-      </c>
-      <c r="D91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K91" s="12" t="inlineStr">
         <is>
           <t>PIONEROS - Actividad Clan Ícaro - Drogas (S-18/07 tarde 1): «Cigarrillos»
 RUTAS PANDORA - Actividad de adicciones con pipis (J-16/07): «Cigarrillos»
 RUTAS ICARO - Taller para Pioneros - Drogas (S-18/07): «Cigarrillos»</t>
         </is>
       </c>
-      <c r="L91" s="13" t="inlineStr"/>
-      <c r="M91" s="13" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="L90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Cinta adhesiva / precinto</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C92" s="6">
-        <f>SUM(D92:I92)</f>
-        <v/>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3" t="n">
+      <c r="C91" s="11">
+        <f>SUM(D91:I91)</f>
+        <v/>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="H91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr">
+      <c r="K91" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - Territorios (V-17/07 tarde 1): «Precinto»
 PIONEROS - Taller de estrellas (V-17/07 noche): «Precinto»
 PIONEROS - Sexualidad (S-25/07 tarde 1): «Cinta adhesiva»</t>
         </is>
       </c>
-      <c r="L92" s="8" t="inlineStr"/>
-      <c r="M92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+      <c r="L91" s="13" t="inlineStr"/>
+      <c r="M91" s="13" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Cinta aislante de colores</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Papeleria/manualidades</t>
         </is>
       </c>
-      <c r="C93" s="11">
-        <f>SUM(D93:I93)</f>
-        <v/>
-      </c>
-      <c r="D93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="10" t="n">
+      <c r="C92" s="6">
+        <f>SUM(D92:I92)</f>
+        <v/>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="10" t="inlineStr">
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Taller constelaciones (S-18/07 noche): «Aislantes»
 EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Cinta aislante de colores»
@@ -6996,13 +6950,59 @@
 RUTAS ICARO - Línea de la vida (Volante noche): «Aislantes»</t>
         </is>
       </c>
+      <c r="L92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Cinta americana</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C93" s="11">
+        <f>SUM(D93:I93)</f>
+        <v/>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Jugger (X-22/07 tarde 2): «Cinta americana»</t>
+        </is>
+      </c>
       <c r="L93" s="13" t="inlineStr"/>
       <c r="M93" s="13" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Cinta americana</t>
+          <t>Cinta de regalo</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Jugger (X-22/07 tarde 2): «Cinta americana»</t>
+          <t>LOBATOS - Atrapasueños (L-27/07 tarde 1): «Cinta de regalo (mucha)»</t>
         </is>
       </c>
       <c r="L94" s="8" t="inlineStr"/>
@@ -7048,7 +7048,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>Cinta de regalo</t>
+          <t>Cinta roja, verde y azul (2m de cada)</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -7064,10 +7064,10 @@
         <v>0</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Atrapasueños (L-27/07 tarde 1): «Cinta de regalo (mucha)»</t>
+          <t>EXPLORADORES - Carrera de orientación nocturna (V-24/07 noche): «Cinta roja, verde y azul (2m de cada)»</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Cinta roja, verde y azul (2m de cada)</t>
+          <t>Cintas reflectantes</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7107,13 +7107,13 @@
         <v/>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
@@ -7130,100 +7130,54 @@
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Carrera de orientación nocturna (V-24/07 noche): «Cinta roja, verde y azul (2m de cada)»</t>
-        </is>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>Cintas reflectantes</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C97" s="11">
-        <f>SUM(D97:I97)</f>
-        <v/>
-      </c>
-      <c r="D97" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K97" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Rastreo nocturno (V-17/07 noche): «Cintas reflectantes amarillas»
 CASTORES - Rastreo nocturno (V-17/07 noche): «Cintas reflectantes naranjas»
 EXPLORADORES - Carrera de orientación nocturna (V-24/07 noche): «Cintas reflectantes»</t>
         </is>
       </c>
-      <c r="L97" s="13" t="inlineStr"/>
-      <c r="M97" s="13" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="L96" s="8" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Clavos</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Construccion/herramientas</t>
         </is>
       </c>
-      <c r="C98" s="6">
-        <f>SUM(D98:I98)</f>
-        <v/>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="3" t="n">
+      <c r="C97" s="11">
+        <f>SUM(D97:I97)</f>
+        <v/>
+      </c>
+      <c r="D97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="3" t="n">
+      <c r="G97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="J97" s="10" t="inlineStr">
         <is>
           <t>COMPRAR</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="K97" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - Construcción de parcela (J-16/07 tarde 1): «Clavos»
 EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Clavos (indeterminados)»
@@ -7232,13 +7186,59 @@
 COMISIONES - BARRACAS (D-26/07 tarde): «Cartón grueso clavos/puntas, rotuladores y chapas (para el Plinko).»</t>
         </is>
       </c>
+      <c r="L97" s="13" t="inlineStr"/>
+      <c r="M97" s="13" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Coche/furgo para llegar</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C98" s="6">
+        <f>SUM(D98:I98)</f>
+        <v/>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Voluntariado Neila (V-24/07): «Coche/furgo para llegar»</t>
+        </is>
+      </c>
       <c r="L98" s="8" t="inlineStr"/>
       <c r="M98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>Coche/furgo para llegar</t>
+          <t>Cofre cerrado con candado y varias llaves</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -7257,13 +7257,13 @@
         <v>0</v>
       </c>
       <c r="F99" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="10" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Voluntariado Neila (V-24/07): «Coche/furgo para llegar»</t>
+          <t>EXPLORADORES - Presentación profunda (V-17/07 mañana): «Cofre cerrado con candado y varias llaves»</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Cofre cerrado con candado y varias llaves</t>
+          <t>Cola blanca 2 botes</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7297,13 +7297,13 @@
         <v/>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Presentación profunda (V-17/07 mañana): «Cofre cerrado con candado y varias llaves»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Cola blanca 2 botes»</t>
         </is>
       </c>
       <c r="L100" s="8" t="inlineStr"/>
@@ -7330,12 +7330,12 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>Cola blanca 2 botes</t>
+          <t>Cola de ratón</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C101" s="11">
@@ -7343,11 +7343,11 @@
         <v/>
       </c>
       <c r="D101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="F101" s="10" t="n">
         <v>0</v>
       </c>
@@ -7355,19 +7355,20 @@
         <v>0</v>
       </c>
       <c r="H101" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Cola blanca 2 botes»</t>
+          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Cola de ratón x2»
+RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Cola de ratón que pase por pernos de argolla»</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr"/>
@@ -7376,12 +7377,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Cola de ratón</t>
+          <t>Cola para madera</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C102" s="6">
@@ -7392,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
@@ -7401,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>0</v>
@@ -7413,8 +7414,8 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Cola de ratón x2»
-RUTAS PANDORA - Miss y Mister (llaveros) (X-29/07 tarde): «Cola de ratón que pase por pernos de argolla»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Cola para madera 2 botes»
+LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Cola»</t>
         </is>
       </c>
       <c r="L102" s="8" t="inlineStr"/>
@@ -7423,12 +7424,12 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>Cola para madera</t>
+          <t>Conos deportivos / Conos chinos</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Juegos/deporte</t>
         </is>
       </c>
       <c r="C103" s="11">
@@ -7439,73 +7440,26 @@
         <v>0</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G103" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K103" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Cola para madera 2 botes»
-LOBATOS - Tipi indio - Miss y Mister (X-29/07 tarde): «Cola»</t>
-        </is>
-      </c>
-      <c r="L103" s="13" t="inlineStr"/>
-      <c r="M103" s="13" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Conos deportivos / Conos chinos</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Juegos/deporte</t>
-        </is>
-      </c>
-      <c r="C104" s="6">
-        <f>SUM(D104:I104)</f>
-        <v/>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>LOBATOS - Juegos (J-16/07 tarde 2): «Conos chinos»
 LOBATOS - De aventura en la India (V-17/07 tarde 2): «Conos chinos»
@@ -7520,97 +7474,97 @@
 COMISIONES - BARRACAS (D-26/07 tarde): «Aros y 1 cono de tráfico bases (para el Desafío del Faquir).»</t>
         </is>
       </c>
+      <c r="L103" s="13" t="inlineStr"/>
+      <c r="M103" s="13" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Corchera</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C104" s="6">
+        <f>SUM(D104:I104)</f>
+        <v/>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Corchera»
+EXPLORADORES - FELSA (V-24/07 tarde 1): «Corchera»</t>
+        </is>
+      </c>
       <c r="L104" s="8" t="inlineStr"/>
       <c r="M104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Corchera</t>
+          <t>Cordino</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C105" s="11">
         <f>SUM(D105:I105)</f>
         <v/>
       </c>
-      <c r="D105" s="10" t="n">
-        <v>0</v>
+      <c r="D105" s="10">
+        <f>CONFIG!$B$2*1.5</f>
+        <v/>
       </c>
       <c r="E105" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="10" t="n">
+      <c r="F105" s="10">
+        <f>CONFIG!$B$4*1.5</f>
+        <v/>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G105" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="I105" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K105" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Inauguración de la FELSA (V-17/07 tarde 2): «Corchera»
-EXPLORADORES - FELSA (V-24/07 tarde 1): «Corchera»</t>
-        </is>
-      </c>
-      <c r="L105" s="13" t="inlineStr"/>
-      <c r="M105" s="13" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Cordino</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C106" s="6">
-        <f>SUM(D106:I106)</f>
-        <v/>
-      </c>
-      <c r="D106" s="3">
-        <f>CONFIG!$B$2*1.5</f>
-        <v/>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3">
-        <f>CONFIG!$B$4*1.5</f>
-        <v/>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>EXPLORADORES - Miss y Mister: sacos de especias (M-29/07 tarde 1): «40cm de cordino por niño»
 EXPLORADORES - Evaluación (cuentas) (M-29/07 tarde 2): «60cm de cordino por niño (oscuro mejor)»
@@ -7620,48 +7574,48 @@
 COMISIONES - FE (V-24/07 tarde): «Cordino tipo macramé (como el de la foto, no es cordino como tal): 1m por niño y monitor de 6 colores diferentes (sino lo encontráis podéis variar los colores o todos el mismo, no pasa nada): naranja para castores, amarillo para lobatos, azul para Tropa, rojo para Pioneros, verde para Rutas y morado para Kraal»</t>
         </is>
       </c>
-      <c r="L106" s="8" t="inlineStr"/>
-      <c r="M106" s="8" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="L105" s="13" t="inlineStr"/>
+      <c r="M105" s="13" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Crema de protección solar / Aftersun</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Higiene/limpieza</t>
         </is>
       </c>
-      <c r="C107" s="11">
-        <f>SUM(D107:I107)</f>
-        <v/>
-      </c>
-      <c r="D107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="10" t="n">
+      <c r="C106" s="6">
+        <f>SUM(D106:I106)</f>
+        <v/>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="10" t="inlineStr">
+      <c r="F106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>LO TRAE EL NINO</t>
         </is>
       </c>
-      <c r="K107" s="12" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Crema solar»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Crema solar»
@@ -7671,13 +7625,59 @@
 PIONEROS - Relax (M-21/07 tarde 2): «Cremita aftersun»</t>
         </is>
       </c>
+      <c r="L106" s="8" t="inlineStr"/>
+      <c r="M106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>Cubitera x2</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C107" s="11">
+        <f>SUM(D107:I107)</f>
+        <v/>
+      </c>
+      <c r="D107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Cubitera x2»</t>
+        </is>
+      </c>
       <c r="L107" s="13" t="inlineStr"/>
       <c r="M107" s="13" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Cubitera x2</t>
+          <t>Cubo grande de colores (barreño)</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7696,10 +7696,10 @@
         <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Cubitera x2»</t>
+          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Cubo grande de colores (barreño)»</t>
         </is>
       </c>
       <c r="L108" s="8" t="inlineStr"/>
@@ -7723,7 +7723,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Cubo grande de colores (barreño)</t>
+          <t>Cubos de agua 6</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="10" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Cubo grande de colores (barreño)»</t>
+          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Cubos de agua 6»</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr"/>
@@ -7769,7 +7769,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Cubos de agua 6</t>
+          <t>Cubos de plástico ( 2)</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -7797,7 +7797,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Cubos de agua 6»</t>
+          <t>COMISIONES - GRAN JUEGO (S-18/07 mañana): «Cubos de plástico ( 2)»</t>
         </is>
       </c>
       <c r="L110" s="8" t="inlineStr"/>
@@ -7815,12 +7815,12 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>Cubos de plástico ( 2)</t>
+          <t>Cuentas amarillas, verdes y rojas</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C111" s="11">
@@ -7833,8 +7833,9 @@
       <c r="E111" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="10" t="n">
-        <v>0</v>
+      <c r="F111" s="10">
+        <f>CONFIG!$B$4*30</f>
+        <v/>
       </c>
       <c r="G111" s="10" t="n">
         <v>0</v>
@@ -7843,16 +7844,16 @@
         <v>0</v>
       </c>
       <c r="I111" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K111" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - GRAN JUEGO (S-18/07 mañana): «Cubos de plástico ( 2)»</t>
+          <t>EXPLORADORES - Evaluación (cuentas) (M-29/07 tarde 2): «Cuentas amarillas, verdes y rojas (~30 por niño, más verdes)»</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr"/>
@@ -7861,12 +7862,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Cuentas amarillas, verdes y rojas</t>
+          <t>Cuerda (gorda mejor) y una rueda/algo que pese</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C112" s="6">
@@ -7877,11 +7878,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="3">
-        <f>CONFIG!$B$4*30</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Evaluación (cuentas) (M-29/07 tarde 2): «Cuentas amarillas, verdes y rojas (~30 por niño, más verdes)»</t>
+          <t>LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Cuerda (gorda mejor) y una rueda/algo que pese»</t>
         </is>
       </c>
       <c r="L112" s="8" t="inlineStr"/>
@@ -7908,7 +7908,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Cuerda (gorda mejor) y una rueda/algo que pese</t>
+          <t>Cuerda de pulsera de encoger y estirar negra</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="K113" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Cuerda (gorda mejor) y una rueda/algo que pese»</t>
+          <t>LOBATOS - El amuleto del elefante sagrado (orientación) (X-22/07 tarde): «Cuerda de pulsera de encoger y estirar negra»</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr"/>
@@ -7954,7 +7954,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Cuerda de pulsera de encoger y estirar negra</t>
+          <t>Cuerda gorda (sogatira)</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7970,13 +7970,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - El amuleto del elefante sagrado (orientación) (X-22/07 tarde): «Cuerda de pulsera de encoger y estirar negra»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Cuerda gorda (sogatira)»</t>
         </is>
       </c>
       <c r="L114" s="8" t="inlineStr"/>
@@ -8000,7 +8000,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Cuerda gorda (sogatira)</t>
+          <t>Cuerda gorda y una rueda/algo que pese</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -8022,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="10" t="n">
         <v>0</v>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="K115" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Cuerda gorda (sogatira)»</t>
+          <t>RUTAS ICARO - Actividad para Lobatos (Charlie y David) (J-23/07): «Cuerda gorda y una rueda/algo que pese»</t>
         </is>
       </c>
       <c r="L115" s="13" t="inlineStr"/>
@@ -8046,7 +8046,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Cuerda gorda y una rueda/algo que pese</t>
+          <t>Cuerda gruesa (ni soga ni pita)</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -8065,13 +8065,13 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Actividad para Lobatos (Charlie y David) (J-23/07): «Cuerda gorda y una rueda/algo que pese»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Cuerda gruesa (ni soga ni pita)»</t>
         </is>
       </c>
       <c r="L116" s="8" t="inlineStr"/>
@@ -8092,12 +8092,12 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Cuerda gruesa (ni soga ni pita)</t>
+          <t>Cuerda pita</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C117" s="11">
@@ -8105,75 +8105,29 @@
         <v/>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F117" s="10" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H117" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I117" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K117" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Cuerda gruesa (ni soga ni pita)»</t>
-        </is>
-      </c>
-      <c r="L117" s="13" t="inlineStr"/>
-      <c r="M117" s="13" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Cuerda pita</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C118" s="6">
-        <f>SUM(D118:I118)</f>
-        <v/>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K118" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Cuerda pita- 2 rollos»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Cuerda pita- 2 rollos»
@@ -8198,13 +8152,59 @@
 COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Cuerda pita»</t>
         </is>
       </c>
+      <c r="L117" s="13" t="inlineStr"/>
+      <c r="M117" s="13" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Cuerdas largas (3)</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C118" s="6">
+        <f>SUM(D118:I118)</f>
+        <v/>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Cuerdas largas (3)»</t>
+        </is>
+      </c>
       <c r="L118" s="8" t="inlineStr"/>
       <c r="M118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Cuerdas largas (3)</t>
+          <t>Cámara de fotos</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -8226,13 +8226,13 @@
         <v>0</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="K119" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Cuerdas largas (3)»</t>
+          <t>PIONEROS - Carrera de orientación (X-22/07 tarde): «Cámara de fotos»</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr"/>
@@ -8250,7 +8250,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Cámara de fotos</t>
+          <t>Dardos de gomaespuma (unidad)</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -8269,10 +8269,10 @@
         <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Carrera de orientación (X-22/07 tarde): «Cámara de fotos»</t>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Dardos de gomaespuma (unidad)»</t>
         </is>
       </c>
       <c r="L120" s="8" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Dardos de gomaespuma (unidad)</t>
+          <t>Dos fotos (a mayores, no de los niños)</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -8312,10 +8312,10 @@
         <v>0</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="10" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="K121" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Dardos de gomaespuma (unidad)»</t>
+          <t>LOBATOS - Territorios (V-17/07 tarde 1): «Dos fotos (a mayores, no de los niños)»</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Dos fotos (a mayores, no de los niños)</t>
+          <t>Dos pañoletas</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -8358,7 +8358,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Territorios (V-17/07 tarde 1): «Dos fotos (a mayores, no de los niños)»</t>
+          <t>COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Dos pañoletas»</t>
         </is>
       </c>
       <c r="L122" s="8" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>Dos pañoletas</t>
+          <t>Ejercicios mentales: Kraalete</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -8410,13 +8410,13 @@
         <v>0</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="K123" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Dos pañoletas»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Ejercicios mentales: Kraalete»</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr"/>
@@ -8434,7 +8434,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Ejercicios mentales: Kraalete</t>
+          <t>Elementos de la naturaleza</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8450,13 +8450,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Ejercicios mentales: Kraalete»</t>
+          <t>LOBATOS - Construcción de parcela (J-16/07 tarde 1): «Elementos de la naturaleza»</t>
         </is>
       </c>
       <c r="L124" s="8" t="inlineStr"/>
@@ -8480,12 +8480,12 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>Elementos de la naturaleza</t>
+          <t>Equipo de campamento (Tiendas, lonas, piquetas, rafias, picas)</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Equipo campamento</t>
         </is>
       </c>
       <c r="C125" s="11">
@@ -8493,19 +8493,19 @@
         <v/>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="10" t="n">
         <v>0</v>
@@ -8516,52 +8516,6 @@
         </is>
       </c>
       <c r="K125" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Construcción de parcela (J-16/07 tarde 1): «Elementos de la naturaleza»</t>
-        </is>
-      </c>
-      <c r="L125" s="13" t="inlineStr"/>
-      <c r="M125" s="13" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de campamento (Tiendas, lonas, piquetas, rafias, picas)</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>Equipo campamento</t>
-        </is>
-      </c>
-      <c r="C126" s="6">
-        <f>SUM(D126:I126)</f>
-        <v/>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K126" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Tienda de campaña x2»
 CASTORES - Montaje de tiendas (J-16/07 mañana): «Listones de los viejos para estructuras y mástil»
@@ -8572,48 +8526,48 @@
 RUTAS ICARO - Construcciones (J-16/07): «Mástil»</t>
         </is>
       </c>
-      <c r="L126" s="8" t="inlineStr"/>
-      <c r="M126" s="8" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="L125" s="13" t="inlineStr"/>
+      <c r="M125" s="13" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Equipo personal (mochila, saco, esterilla, toalla, etc.)</t>
         </is>
       </c>
-      <c r="B127" s="10" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C127" s="11">
-        <f>SUM(D127:I127)</f>
-        <v/>
-      </c>
-      <c r="D127" s="10" t="n">
+      <c r="C126" s="6">
+        <f>SUM(D126:I126)</f>
+        <v/>
+      </c>
+      <c r="D126" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E127" s="10" t="n">
+      <c r="E126" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F127" s="10" t="n">
+      <c r="F126" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G127" s="10" t="n">
+      <c r="G126" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H127" s="10" t="n">
+      <c r="H126" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I127" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
+      <c r="I126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>LO TRAE EL NINO</t>
         </is>
       </c>
-      <c r="K127" s="12" t="inlineStr">
+      <c r="K126" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Hacer mochilas acampada volante (S-18/07 tarde 2): «Mochilas de cada castor»
 CASTORES - Hacer mochilas acampada volante (S-18/07 tarde 2): «Ropa»
@@ -8658,13 +8612,59 @@
 COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Sacos para carrera de sacos»</t>
         </is>
       </c>
+      <c r="L126" s="8" t="inlineStr"/>
+      <c r="M126" s="8" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Espaguetis</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C127" s="11">
+        <f>SUM(D127:I127)</f>
+        <v/>
+      </c>
+      <c r="D127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «Espaguetis»</t>
+        </is>
+      </c>
       <c r="L127" s="13" t="inlineStr"/>
       <c r="M127" s="13" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Espaguetis</t>
+          <t>Esponjas (15)</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Velada de terror (X-22/07 noche): «Espaguetis»</t>
+          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Esponjas (15)»</t>
         </is>
       </c>
       <c r="L128" s="8" t="inlineStr"/>
@@ -8710,7 +8710,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Esponjas (15)</t>
+          <t>Esponjas x10</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -8726,7 +8726,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F129" s="10" t="n">
         <v>0</v>
@@ -8738,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="K129" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - DIA GUARRO (X-22/07 día): «Esponjas (15)»</t>
+          <t>LOBATOS - Poza (L-27/07 mañana): «Esponjas x10»</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr"/>
@@ -8756,7 +8756,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Esponjas x10</t>
+          <t>Estructura para tendedero</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -8772,10 +8772,10 @@
         <v>0</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>0</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Poza (L-27/07 mañana): «Esponjas x10»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Estructura para tendedero»</t>
         </is>
       </c>
       <c r="L130" s="8" t="inlineStr"/>
@@ -8802,7 +8802,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Estructura para tendedero</t>
+          <t>Extintor y batefuegos</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -8821,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="10" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Estructura para tendedero»</t>
+          <t>COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Extintor y batefuegos»</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr"/>
@@ -8848,7 +8848,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Extintor y batefuegos</t>
+          <t>Falta confirmar si dejan todo o llevamos nosotros</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Extintor y batefuegos»</t>
+          <t>RUTAS PANDORA - Voluntariado Neila (V-24/07): «Falta confirmar si dejan todo o llevamos nosotros»</t>
         </is>
       </c>
       <c r="L132" s="8" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Falta confirmar si dejan todo o llevamos nosotros</t>
+          <t>Fieltro marrón oscuro x4 láminas A3 (bandas de flecos indias)</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -8910,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F133" s="10" t="n">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="10" t="n">
         <v>0</v>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Voluntariado Neila (V-24/07): «Falta confirmar si dejan todo o llevamos nosotros»</t>
+          <t>LOBATOS - Juegos India (V-17/07 mañana): «Fieltro marrón oscuro x4 láminas A3 (bandas de flecos indias)»</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr"/>
@@ -8940,12 +8940,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Fieltro marrón oscuro x4 láminas A3 (bandas de flecos indias)</t>
+          <t>Folios</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C134" s="6">
@@ -8953,75 +8953,29 @@
         <v/>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Juegos India (V-17/07 mañana): «Fieltro marrón oscuro x4 láminas A3 (bandas de flecos indias)»</t>
-        </is>
-      </c>
-      <c r="L134" s="8" t="inlineStr"/>
-      <c r="M134" s="8" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Folios</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C135" s="11">
-        <f>SUM(D135:I135)</f>
-        <v/>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F135" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G135" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H135" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I135" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J135" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K135" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Folios»
 CASTORES - Lluvia: Flipbook (D-26/07 (lluvia)): «Folios»
@@ -9060,18 +9014,64 @@
 COMISIONES - FE (V-24/07 tarde): «Folios de colores»</t>
         </is>
       </c>
+      <c r="L134" s="8" t="inlineStr"/>
+      <c r="M134" s="8" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Foto impresa en papel de foto (cada uno la suya)</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Papeleria/manualidades</t>
+        </is>
+      </c>
+      <c r="C135" s="11">
+        <f>SUM(D135:I135)</f>
+        <v/>
+      </c>
+      <c r="D135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>COMPRAR</t>
+        </is>
+      </c>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>PIONEROS - Decorar fotos (Lluvia): «Foto impresa en papel de foto (cada uno la suya)»</t>
+        </is>
+      </c>
       <c r="L135" s="13" t="inlineStr"/>
       <c r="M135" s="13" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Foto impresa en papel de foto (cada uno la suya)</t>
+          <t>Fotocopias, fichas de actividades y reflexiones</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Impresiones/documentacion</t>
         </is>
       </c>
       <c r="C136" s="6">
@@ -9079,19 +9079,19 @@
         <v/>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>0</v>
@@ -9102,52 +9102,6 @@
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
-        <is>
-          <t>PIONEROS - Decorar fotos (Lluvia): «Foto impresa en papel de foto (cada uno la suya)»</t>
-        </is>
-      </c>
-      <c r="L136" s="8" t="inlineStr"/>
-      <c r="M136" s="8" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Fotocopias, fichas de actividades y reflexiones</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>Impresiones/documentacion</t>
-        </is>
-      </c>
-      <c r="C137" s="11">
-        <f>SUM(D137:I137)</f>
-        <v/>
-      </c>
-      <c r="D137" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F137" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G137" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H137" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K137" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Rastreo nocturno (V-17/07 noche): «Leyendas de las constelaciones (comisión) - imprimir antes»
 CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Taj Mahal impreso (se encarga la unidad)»
@@ -9182,13 +9136,59 @@
 RUTAS ICARO - Raids (L-27 a M-28/07): «Reflexiones (Vali)»</t>
         </is>
       </c>
+      <c r="L136" s="8" t="inlineStr"/>
+      <c r="M136" s="8" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>Frascos grandes de cristal con tapa hermética</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C137" s="11">
+        <f>SUM(D137:I137)</f>
+        <v/>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Frascos grandes de cristal con tapa hermética»</t>
+        </is>
+      </c>
       <c r="L137" s="13" t="inlineStr"/>
       <c r="M137" s="13" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Frascos grandes de cristal con tapa hermética</t>
+          <t>Furgoneta</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Cambio climático y ecosistemas autosostenibles (S-25/07): «Frascos grandes de cristal con tapa hermética»</t>
+          <t>RUTAS PANDORA - Rapel (D-26/07): «Furgoneta»</t>
         </is>
       </c>
       <c r="L138" s="8" t="inlineStr"/>
@@ -9234,12 +9234,12 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>Furgoneta</t>
+          <t>Ganchos de tornillo</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C139" s="11">
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F139" s="10" t="n">
         <v>0</v>
@@ -9259,19 +9259,19 @@
         <v>0</v>
       </c>
       <c r="H139" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K139" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - Rapel (D-26/07): «Furgoneta»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «10 ganchos de tornillo»</t>
         </is>
       </c>
       <c r="L139" s="13" t="inlineStr"/>
@@ -9280,12 +9280,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Ganchos de tornillo</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C140" s="6">
@@ -9296,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F140" s="3" t="n">
         <v>0</v>
@@ -9308,16 +9308,17 @@
         <v>0</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «10 ganchos de tornillo»</t>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Gasolina»
+COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Gasolina»</t>
         </is>
       </c>
       <c r="L140" s="8" t="inlineStr"/>
@@ -9326,7 +9327,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>Gasolina</t>
+          <t>Globos de agua (hinchados en barreño)</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -9342,19 +9343,19 @@
         <v>0</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="10" t="n">
         <v>0</v>
       </c>
       <c r="I141" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
@@ -9363,8 +9364,7 @@
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Gasolina»
-COMISIONES - OLIMPIADAS (M-28 y X-29/07): «Gasolina»</t>
+          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Globos de agua (hinchados en barreño)»</t>
         </is>
       </c>
       <c r="L141" s="13" t="inlineStr"/>
@@ -9373,7 +9373,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Globos de agua (hinchados en barreño)</t>
+          <t>Globos de agua 100</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9389,13 +9389,13 @@
         <v>0</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="3" t="n">
         <v>0</v>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Globos de agua (hinchados en barreño)»</t>
+          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Globos de agua 100»</t>
         </is>
       </c>
       <c r="L142" s="8" t="inlineStr"/>
@@ -9419,12 +9419,12 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>Globos de agua 100</t>
+          <t>Goma eva de colores</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C143" s="11">
@@ -9432,7 +9432,7 @@
         <v/>
       </c>
       <c r="D143" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E143" s="10" t="n">
         <v>1</v>
@@ -9451,56 +9451,10 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K143" s="12" t="inlineStr">
-        <is>
-          <t>LOBATOS - Gymkana de agua (V-24/07 mañana): «Globos de agua 100»</t>
-        </is>
-      </c>
-      <c r="L143" s="13" t="inlineStr"/>
-      <c r="M143" s="13" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Goma eva de colores</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C144" s="6">
-        <f>SUM(D144:I144)</f>
-        <v/>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K144" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Taller insignias (V-17/07 tarde): «Goma eva de colores»
 CASTORES - Gran Juego: El Taj perdido (con Lobatos) (S-18/07 tarde 1): «Goma eva de colores (vale con recortes)»
@@ -9508,18 +9462,64 @@
 LOBATOS - El Taj perdido (con Castores) (S-18/07 tarde 1): «Goma eva de colores (recortes)»</t>
         </is>
       </c>
+      <c r="L143" s="13" t="inlineStr"/>
+      <c r="M143" s="13" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Goma eva de muchos colores (bastante)</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C144" s="6">
+        <f>SUM(D144:I144)</f>
+        <v/>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Goma eva de muchos colores (bastante)»</t>
+        </is>
+      </c>
       <c r="L144" s="8" t="inlineStr"/>
       <c r="M144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>Goma eva de muchos colores (bastante)</t>
+          <t>Goma eva dorada brillantina A4</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C145" s="11">
@@ -9530,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="10" t="n">
         <v>0</v>
@@ -9539,19 +9539,19 @@
         <v>0</v>
       </c>
       <c r="H145" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Revisar olimpiadas + hacer premios (S-26/07): «Goma eva de muchos colores (bastante)»</t>
+          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Lámina goma eva dorada brillantina A4»</t>
         </is>
       </c>
       <c r="L145" s="13" t="inlineStr"/>
@@ -9560,12 +9560,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Goma eva dorada brillantina A4</t>
+          <t>Gomas de plástico</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C146" s="6">
@@ -9573,10 +9573,10 @@
         <v/>
       </c>
       <c r="D146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" s="3" t="n">
         <v>0</v>
@@ -9592,12 +9592,12 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Lobatolimpiadas (S-25/07 tarde 2): «Lámina goma eva dorada brillantina A4»</t>
+          <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Gomas de plástico»</t>
         </is>
       </c>
       <c r="L146" s="8" t="inlineStr"/>
@@ -9606,12 +9606,12 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>Gomas de plástico</t>
+          <t>Gomas elásticas</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C147" s="11">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="J147" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Diseño de camisetas (X-22/07 tarde 1): «Gomas de plástico»</t>
+          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Gomas elásticas (paquete)»</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr"/>
@@ -9652,12 +9652,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Gomas elásticas</t>
+          <t>Gomets o pegatinas de las bases</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C148" s="6">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Actividad de agua: El descenso del Ganges (V-24/07 mañana): «Gomas elásticas (paquete)»</t>
+          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Gomets o pegatinas de las bases»</t>
         </is>
       </c>
       <c r="L148" s="8" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>Gomets o pegatinas de las bases</t>
+          <t>Gomitas de colores para pulseras</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -9711,7 +9711,7 @@
         <v/>
       </c>
       <c r="D149" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="10" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="10" t="n">
         <v>0</v>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Taller de sobres y cartas (Bolsa de juegos): «Gomets o pegatinas de las bases»</t>
+          <t>PIONEROS - Pulseras (L-20/07 noche): «Gomitas de colores para pulseras»</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
@@ -9744,7 +9744,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Gomitas de colores para pulseras</t>
+          <t>Gorro castor</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -9757,7 +9757,7 @@
         <v/>
       </c>
       <c r="D150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="3" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Pulseras (L-20/07 noche): «Gomitas de colores para pulseras»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Gorro castor»</t>
         </is>
       </c>
       <c r="L150" s="8" t="inlineStr"/>
@@ -9790,12 +9790,12 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>Gorro castor</t>
+          <t>Grapadora</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C151" s="11">
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="D151" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="10" t="n">
         <v>0</v>
@@ -9827,7 +9827,8 @@
       </c>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Gorro castor»</t>
+          <t>CASTORES - Lluvia: Flipbook (D-26/07 (lluvia)): «Grapadora»
+CASTORES - Cuento de imágenes (Bolsa de juegos): «Grapadora»</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr"/>
@@ -9836,12 +9837,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Grapadora</t>
+          <t>Guantes de trabajo (protección)</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Higiene/limpieza</t>
         </is>
       </c>
       <c r="C152" s="6">
@@ -9849,76 +9850,29 @@
         <v/>
       </c>
       <c r="D152" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>LO TRAE EL NINO</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
-        <is>
-          <t>CASTORES - Lluvia: Flipbook (D-26/07 (lluvia)): «Grapadora»
-CASTORES - Cuento de imágenes (Bolsa de juegos): «Grapadora»</t>
-        </is>
-      </c>
-      <c r="L152" s="8" t="inlineStr"/>
-      <c r="M152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>Guantes de trabajo (protección)</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>Higiene/limpieza</t>
-        </is>
-      </c>
-      <c r="C153" s="11">
-        <f>SUM(D153:I153)</f>
-        <v/>
-      </c>
-      <c r="D153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="10" t="inlineStr">
-        <is>
-          <t>LO TRAE EL NINO</t>
-        </is>
-      </c>
-      <c r="K153" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - Voluntariado conjunto Lobatos-Pioneros (J-23/07 mañana): «Guantes»
 EXPLORADORES - Servicio en el pueblo (J-23/07 mañana): «Pendiente del voluntariado, se suelen necesitar: Guantes»
@@ -9926,18 +9880,65 @@
 RUTAS ICARO - Voluntariado Manuela (J-23/07): «Guantes»</t>
         </is>
       </c>
+      <c r="L152" s="8" t="inlineStr"/>
+      <c r="M152" s="8" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>Hierros de tienda</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C153" s="11">
+        <f>SUM(D153:I153)</f>
+        <v/>
+      </c>
+      <c r="D153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K153" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Montaje (J-16/07 mañana): «Hierros»
+COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Hierros de tiendas de 3-4 tamaños»</t>
+        </is>
+      </c>
       <c r="L153" s="13" t="inlineStr"/>
       <c r="M153" s="13" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Hierros de tienda</t>
+          <t>Hierros y listones para tendedero</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C154" s="6">
@@ -9948,7 +9949,7 @@
         <v>0</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="3" t="n">
         <v>0</v>
@@ -9957,10 +9958,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -9969,8 +9970,7 @@
       </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Montaje (J-16/07 mañana): «Hierros»
-COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Hierros de tiendas de 3-4 tamaños»</t>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Hierros y listones para tendedero»</t>
         </is>
       </c>
       <c r="L154" s="8" t="inlineStr"/>
@@ -9979,7 +9979,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>Hierros y listones para tendedero</t>
+          <t>Hilo coreano de diferentes colores (3 m x niño)</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -9994,8 +9994,9 @@
       <c r="D155" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
+      <c r="E155" s="10">
+        <f>CONFIG!$B$3*3</f>
+        <v/>
       </c>
       <c r="F155" s="10" t="n">
         <v>0</v>
@@ -10004,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" s="10" t="n">
         <v>0</v>
@@ -10016,7 +10017,7 @@
       </c>
       <c r="K155" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Hierros y listones para tendedero»</t>
+          <t>LOBATOS - Taller de pulseras (D-19/07 tarde): «Hilo coreano de diferentes colores (3 m x niño)»</t>
         </is>
       </c>
       <c r="L155" s="13" t="inlineStr"/>
@@ -10025,7 +10026,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Hilo coreano de diferentes colores (3 m x niño)</t>
+          <t>Hilo de colores (fino, no lana)</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10040,15 +10041,14 @@
       <c r="D156" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E156" s="3">
-        <f>CONFIG!$B$3*3</f>
-        <v/>
+      <c r="E156" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Taller de pulseras (D-19/07 tarde): «Hilo coreano de diferentes colores (3 m x niño)»</t>
+          <t>PIONEROS - Decorar fotos (Lluvia): «Hilo de colores (fino, no lana)»</t>
         </is>
       </c>
       <c r="L156" s="8" t="inlineStr"/>
@@ -10072,7 +10072,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>Hilo de colores (fino, no lana)</t>
+          <t>Hilo de colores para atar (gordito, no lana ni de pulseras fino)</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="K157" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Decorar fotos (Lluvia): «Hilo de colores (fino, no lana)»</t>
+          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Hilo de colores para atar (gordito, no lana ni de pulseras fino)»</t>
         </is>
       </c>
       <c r="L157" s="13" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Hilo de colores para atar (gordito, no lana ni de pulseras fino)</t>
+          <t>Hilo de pulsera, 7-8 colores</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="K158" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Hilo de colores para atar (gordito, no lana ni de pulseras fino)»</t>
+          <t>PIONEROS - Pulseras (Lluvia): «Hilo de pulsera, 7-8 colores»</t>
         </is>
       </c>
       <c r="L158" s="8" t="inlineStr"/>
@@ -10164,12 +10164,12 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>Hilo de pulsera, 7-8 colores</t>
+          <t>Imperdibles</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C159" s="11">
@@ -10177,7 +10177,7 @@
         <v/>
       </c>
       <c r="D159" s="10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E159" s="10" t="n">
         <v>0</v>
@@ -10189,63 +10189,17 @@
         <v>1</v>
       </c>
       <c r="H159" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K159" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Pulseras (Lluvia): «Hilo de pulsera, 7-8 colores»</t>
-        </is>
-      </c>
-      <c r="L159" s="13" t="inlineStr"/>
-      <c r="M159" s="13" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Imperdibles</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C160" s="6">
-        <f>SUM(D160:I160)</f>
-        <v/>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K160" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Imperdibles x4»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Imperdibles x4»
@@ -10254,13 +10208,59 @@
 RUTAS ICARO - Construcciones (J-16/07): «Imperdibles»</t>
         </is>
       </c>
+      <c r="L159" s="13" t="inlineStr"/>
+      <c r="M159" s="13" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Incienso</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C160" s="6">
+        <f>SUM(D160:I160)</f>
+        <v/>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K160" s="7" t="inlineStr">
+        <is>
+          <t>LOBATOS - Juegos India (V-17/07 mañana): «Incienso»</t>
+        </is>
+      </c>
       <c r="L160" s="8" t="inlineStr"/>
       <c r="M160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>Incienso</t>
+          <t>Insignia de arat</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -10273,10 +10273,10 @@
         <v/>
       </c>
       <c r="D161" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" s="10" t="n">
         <v>0</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="K161" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Juegos India (V-17/07 mañana): «Incienso»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia de arat»</t>
         </is>
       </c>
       <c r="L161" s="13" t="inlineStr"/>
@@ -10306,7 +10306,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Insignia de arat</t>
+          <t>Insignia del tronco (promesa)</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="K162" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia de arat»</t>
+          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia del tronco (promesa)»</t>
         </is>
       </c>
       <c r="L162" s="8" t="inlineStr"/>
@@ -10352,7 +10352,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>Insignia del tronco (promesa)</t>
+          <t>Insignias territorios</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -10365,10 +10365,10 @@
         <v/>
       </c>
       <c r="D163" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="10" t="n">
         <v>0</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="K163" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Consejo de troncos (V-24/07 noche): «Insignia del tronco (promesa)»</t>
+          <t>LOBATOS - Promesas + progresión personal (S-25/07 mañana): «Insignias territorios»</t>
         </is>
       </c>
       <c r="L163" s="13" t="inlineStr"/>
@@ -10398,7 +10398,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Insignias territorios</t>
+          <t>Jarras de cocina</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10414,13 +10414,13 @@
         <v>0</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="3" t="n">
         <v>0</v>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Promesas + progresión personal (S-25/07 mañana): «Insignias territorios»</t>
+          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Jarras de cocina»</t>
         </is>
       </c>
       <c r="L164" s="8" t="inlineStr"/>
@@ -10444,7 +10444,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>Jarras de cocina</t>
+          <t>Juegos de la caja</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="K165" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Juegos de agua (J-23/07 tarde 1): «Jarras de cocina»</t>
+          <t>PIONEROS - Velada teleclub (X-22/07 noche): «Juegos de la caja»</t>
         </is>
       </c>
       <c r="L165" s="13" t="inlineStr"/>
@@ -10490,12 +10490,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Juegos de la caja</t>
+          <t>Juegos de mesa y barajas de cartas</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Juegos/deporte</t>
         </is>
       </c>
       <c r="C166" s="6">
@@ -10503,22 +10503,22 @@
         <v/>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -10526,52 +10526,6 @@
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr">
-        <is>
-          <t>PIONEROS - Velada teleclub (X-22/07 noche): «Juegos de la caja»</t>
-        </is>
-      </c>
-      <c r="L166" s="8" t="inlineStr"/>
-      <c r="M166" s="8" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>Juegos de mesa y barajas de cartas</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>Juegos/deporte</t>
-        </is>
-      </c>
-      <c r="C167" s="11">
-        <f>SUM(D167:I167)</f>
-        <v/>
-      </c>
-      <c r="D167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G167" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H167" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I167" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J167" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K167" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Juegos de mesa (X-22/07 noche): «Juegos de mesa de las bases»
 LOBATOS - Juegos India (V-17/07 mañana): «Parchís y fichas x3»
@@ -10599,13 +10553,59 @@
 COMISIONES - BARRACAS (D-26/07 tarde): «6 dados y 6 figuras de camellos o piedras numeradas (para la Carrera).»</t>
         </is>
       </c>
+      <c r="L166" s="8" t="inlineStr"/>
+      <c r="M166" s="8" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Lana de colores</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C167" s="11">
+        <f>SUM(D167:I167)</f>
+        <v/>
+      </c>
+      <c r="D167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K167" s="12" t="inlineStr">
+        <is>
+          <t>PIONEROS - Taller de tejer (Lluvia): «Lana de colores»</t>
+        </is>
+      </c>
       <c r="L167" s="13" t="inlineStr"/>
       <c r="M167" s="13" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Lana de colores</t>
+          <t>Lanzadoras tipo Nerf (unidad, solo monitores)</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10624,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
         <v>0</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="K168" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Taller de tejer (Lluvia): «Lana de colores»</t>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lanzadoras tipo Nerf (unidad, solo monitores)»</t>
         </is>
       </c>
       <c r="L168" s="8" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>Lanzadoras tipo Nerf (unidad, solo monitores)</t>
+          <t>Lata de aluminio 2 por niño</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="K169" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lanzadoras tipo Nerf (unidad, solo monitores)»</t>
+          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Lata de aluminio 2 por niño»</t>
         </is>
       </c>
       <c r="L169" s="13" t="inlineStr"/>
@@ -10697,7 +10697,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Lata de aluminio 2 por niño</t>
+          <t>Latas de refresco vacías y piedras o arena para darles peso.</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10716,7 +10716,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170" s="3" t="n">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="K170" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Taller de hornillo (S-18/07 tarde 1): «Lata de aluminio 2 por niño»</t>
+          <t>COMISIONES - BARRACAS (D-26/07 tarde): «Latas de refresco vacías y piedras o arena para darles peso.»</t>
         </is>
       </c>
       <c r="L170" s="8" t="inlineStr"/>
@@ -10743,7 +10743,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>Latas de refresco vacías y piedras o arena para darles peso.</t>
+          <t>Lentejas x300</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G171" s="10" t="n">
         <v>0</v>
@@ -10771,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" s="10" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="K171" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - BARRACAS (D-26/07 tarde): «Latas de refresco vacías y piedras o arena para darles peso.»</t>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Lentejas x300»</t>
         </is>
       </c>
       <c r="L171" s="13" t="inlineStr"/>
@@ -10789,7 +10789,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Lentejas x300</t>
+          <t>Libro con muchas páginas</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10808,7 +10808,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G172" s="3" t="n">
         <v>0</v>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="K172" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Lentejas x300»</t>
+          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Libro con muchas páginas»</t>
         </is>
       </c>
       <c r="L172" s="8" t="inlineStr"/>
@@ -10835,12 +10835,12 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>Libro con muchas páginas</t>
+          <t>Lija de grano fino</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C173" s="11">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="J173" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K173" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Scape room (S-25/07 tarde 1): «Libro con muchas páginas»</t>
+          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lija de grano fino»</t>
         </is>
       </c>
       <c r="L173" s="13" t="inlineStr"/>
@@ -10881,12 +10881,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Lija de grano fino</t>
+          <t>Linternas / Frontales</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Iluminacion/electronica</t>
         </is>
       </c>
       <c r="C174" s="6">
@@ -10894,75 +10894,29 @@
         <v/>
       </c>
       <c r="D174" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>LO TRAE EL NINO</t>
         </is>
       </c>
       <c r="K174" s="7" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Juegos (Tropiolimpiadas - cerbatanas) (J-16/07 tarde): «Lija de grano fino»</t>
-        </is>
-      </c>
-      <c r="L174" s="8" t="inlineStr"/>
-      <c r="M174" s="8" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="9" t="inlineStr">
-        <is>
-          <t>Linternas / Frontales</t>
-        </is>
-      </c>
-      <c r="B175" s="10" t="inlineStr">
-        <is>
-          <t>Iluminacion/electronica</t>
-        </is>
-      </c>
-      <c r="C175" s="11">
-        <f>SUM(D175:I175)</f>
-        <v/>
-      </c>
-      <c r="D175" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G175" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H175" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I175" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="10" t="inlineStr">
-        <is>
-          <t>LO TRAE EL NINO</t>
-        </is>
-      </c>
-      <c r="K175" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Taller constelaciones (S-18/07 noche): «Frontal o linterna del móvil»
 CASTORES - Caza Gamusino (M-21/07 noche): «Frontales»
@@ -10978,13 +10932,59 @@
 RUTAS ICARO - Stalking con Pandora y pipis (D-26/07 noche): «Frontales»</t>
         </is>
       </c>
+      <c r="L174" s="8" t="inlineStr"/>
+      <c r="M174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Lista de preguntas impresa (Eva y Vali)</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C175" s="11">
+        <f>SUM(D175:I175)</f>
+        <v/>
+      </c>
+      <c r="D175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K175" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Taller feminismo (actividad país) (X-22/07 noche): «Lista de preguntas impresa (Eva y Vali)»</t>
+        </is>
+      </c>
       <c r="L175" s="13" t="inlineStr"/>
       <c r="M175" s="13" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Lista de preguntas impresa (Eva y Vali)</t>
+          <t>Listones circulares</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11003,13 +11003,13 @@
         <v>0</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>0</v>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="K176" s="7" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Taller feminismo (actividad país) (X-22/07 noche): «Lista de preguntas impresa (Eva y Vali)»</t>
+          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Listones circulares»</t>
         </is>
       </c>
       <c r="L176" s="8" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>Listones circulares</t>
+          <t>Listones para portada</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="K177" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones adicionales (V-17/07 tarde 1): «Listones circulares»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listones para portada»</t>
         </is>
       </c>
       <c r="L177" s="13" t="inlineStr"/>
@@ -11076,7 +11076,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Listones para portada</t>
+          <t>Listones sobrantes</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -11095,13 +11095,13 @@
         <v>0</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listones para portada»</t>
+          <t>RUTAS ICARO - Construcciones (J-16/07): «Listones sobrantes»</t>
         </is>
       </c>
       <c r="L178" s="8" t="inlineStr"/>
@@ -11122,12 +11122,12 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>Listones sobrantes</t>
+          <t>Listones y tablas de madera</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C179" s="11">
@@ -11135,10 +11135,10 @@
         <v/>
       </c>
       <c r="D179" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E179" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F179" s="10" t="n">
         <v>0</v>
@@ -11147,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="10" t="n">
         <v>0</v>
@@ -11158,52 +11158,6 @@
         </is>
       </c>
       <c r="K179" s="12" t="inlineStr">
-        <is>
-          <t>RUTAS ICARO - Construcciones (J-16/07): «Listones sobrantes»</t>
-        </is>
-      </c>
-      <c r="L179" s="13" t="inlineStr"/>
-      <c r="M179" s="13" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Listones y tablas de madera</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C180" s="6">
-        <f>SUM(D180:I180)</f>
-        <v/>
-      </c>
-      <c r="D180" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K180" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Listones»
 CASTORES - Montaje de tiendas (J-16/07 mañana): «Tablas de madera»
@@ -11214,13 +11168,59 @@
 LOBATOS - Construcción de parcela (J-16/07 tarde 1): «Listones»</t>
         </is>
       </c>
+      <c r="L179" s="13" t="inlineStr"/>
+      <c r="M179" s="13" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Listón para potero</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C180" s="6">
+        <f>SUM(D180:I180)</f>
+        <v/>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K180" s="7" t="inlineStr">
+        <is>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listón para potero»</t>
+        </is>
+      </c>
       <c r="L180" s="8" t="inlineStr"/>
       <c r="M180" s="8" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>Listón para potero</t>
+          <t>Lo que nos pidan</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
@@ -11239,10 +11239,10 @@
         <v>0</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n">
         <v>0</v>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="K181" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Listón para potero»</t>
+          <t>PIONEROS - Voluntariado con Lobatos (J-23/07 mañana): «Lo que nos pidan»</t>
         </is>
       </c>
       <c r="L181" s="13" t="inlineStr"/>
@@ -11266,12 +11266,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Lo que nos pidan</t>
+          <t>Lonas</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C182" s="6">
@@ -11279,22 +11279,22 @@
         <v/>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -11302,52 +11302,6 @@
         </is>
       </c>
       <c r="K182" s="7" t="inlineStr">
-        <is>
-          <t>PIONEROS - Voluntariado con Lobatos (J-23/07 mañana): «Lo que nos pidan»</t>
-        </is>
-      </c>
-      <c r="L182" s="8" t="inlineStr"/>
-      <c r="M182" s="8" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Lonas</t>
-        </is>
-      </c>
-      <c r="B183" s="10" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C183" s="11">
-        <f>SUM(D183:I183)</f>
-        <v/>
-      </c>
-      <c r="D183" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F183" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="G183" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I183" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J183" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K183" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Lona + segunda estructura de tienda (mochilero)»
 LOBATOS - Gymkana de agua (V-24/07 mañana): «Lona grande o plástico resistente»
@@ -11359,13 +11313,60 @@
 COMISIONES - GRAN JUEGO (S-18/07 mañana): «papeles más pequeños o varias lonas grandes para prueba de dibujar y pintar,»</t>
         </is>
       </c>
+      <c r="L182" s="8" t="inlineStr"/>
+      <c r="M182" s="8" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>Lumi gas</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C183" s="11">
+        <f>SUM(D183:I183)</f>
+        <v/>
+      </c>
+      <c r="D183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K183" s="12" t="inlineStr">
+        <is>
+          <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Lumi gas»
+LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Lumi gas»</t>
+        </is>
+      </c>
       <c r="L183" s="13" t="inlineStr"/>
       <c r="M183" s="13" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Lumi gas</t>
+          <t>Lumis para el centro</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -11378,16 +11379,16 @@
         <v/>
       </c>
       <c r="D184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
@@ -11402,8 +11403,7 @@
       </c>
       <c r="K184" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Lumi gas»
-LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Lumi gas»</t>
+          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Lumis para el centro»</t>
         </is>
       </c>
       <c r="L184" s="8" t="inlineStr"/>
@@ -11412,12 +11412,12 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>Lumis para el centro</t>
+          <t>Lápices de colores / ceras / pinturas de palo</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C185" s="11">
@@ -11434,7 +11434,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H185" s="10" t="n">
         <v>0</v>
@@ -11444,74 +11444,74 @@
       </c>
       <c r="J185" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K185" s="12" t="inlineStr">
-        <is>
-          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Lumis para el centro»</t>
-        </is>
-      </c>
-      <c r="L185" s="13" t="inlineStr"/>
-      <c r="M185" s="13" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Lápices de colores / ceras / pinturas de palo</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>Papeleria/manualidades</t>
-        </is>
-      </c>
-      <c r="C186" s="6">
-        <f>SUM(D186:I186)</f>
-        <v/>
-      </c>
-      <c r="D186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" s="3" t="inlineStr">
-        <is>
-          <t>COMPRAR</t>
-        </is>
-      </c>
-      <c r="K186" s="7" t="inlineStr">
         <is>
           <t>PIONEROS - Fe (V-24/07 tarde 2): «Pinturas de palo»
 PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Pinturas de palo»
 PIONEROS - Pintar mandalas (Lluvia): «Pinturas de palo»</t>
         </is>
       </c>
+      <c r="L185" s="13" t="inlineStr"/>
+      <c r="M185" s="13" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Lápices de colores o ceras</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C186" s="6">
+        <f>SUM(D186:I186)</f>
+        <v/>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K186" s="7" t="inlineStr">
+        <is>
+          <t>CASTORES - Progresión Personal (mandalas) (J-23/07 tarde 1): «Lápices de colores o ceras»</t>
+        </is>
+      </c>
       <c r="L186" s="8" t="inlineStr"/>
       <c r="M186" s="8" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>Lápices de colores o ceras</t>
+          <t>Lápices y gomas</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Papeleria/manualidades</t>
         </is>
       </c>
       <c r="C187" s="11">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="K187" s="12" t="inlineStr">
         <is>
-          <t>CASTORES - Progresión Personal (mandalas) (J-23/07 tarde 1): «Lápices de colores o ceras»</t>
+          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Lápices y gomas»</t>
         </is>
       </c>
       <c r="L187" s="13" t="inlineStr"/>
@@ -11552,12 +11552,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Lápices y gomas</t>
+          <t>Maderas varias para parcela y FELSA</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Papeleria/manualidades</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C188" s="6">
@@ -11565,13 +11565,13 @@
         <v/>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
-          <t>CASTORES - Talleres pinza (Bolsa de juegos): «Lápices y gomas»</t>
+          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Maderas varias para parcela y FELSA»</t>
         </is>
       </c>
       <c r="L188" s="8" t="inlineStr"/>
@@ -11598,12 +11598,12 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>Maderas varias para parcela y FELSA</t>
+          <t>Malla de alambre 1m x 30cm</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C189" s="11">
@@ -11614,10 +11614,10 @@
         <v>0</v>
       </c>
       <c r="E189" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" s="10" t="n">
         <v>0</v>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>YA HAY (bases) - revisar</t>
+          <t>COMPRAR</t>
         </is>
       </c>
       <c r="K189" s="12" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Construcciones rústicas (J-16/07 mañana+tarde): «Maderas varias para parcela y FELSA»</t>
+          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Malla de alambre 1m x 30cm aprox (ref Temu en el doc)»</t>
         </is>
       </c>
       <c r="L189" s="13" t="inlineStr"/>
@@ -11644,12 +11644,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Malla de alambre 1m x 30cm</t>
+          <t>Mandalas (20)</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C190" s="6">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>COMPRAR</t>
+          <t>YA HAY (bases) - revisar</t>
         </is>
       </c>
       <c r="K190" s="7" t="inlineStr">
         <is>
-          <t>LOBATOS - Hotel de insectos (M-28/07 mañana): «Malla de alambre 1m x 30cm aprox (ref Temu en el doc)»</t>
+          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Mandalas (20)»</t>
         </is>
       </c>
       <c r="L190" s="8" t="inlineStr"/>
@@ -11690,7 +11690,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>Mandalas (20)</t>
+          <t>Manojo de llaves o cascabel</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
@@ -11706,10 +11706,10 @@
         <v>0</v>
       </c>
       <c r="E191" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" s="10" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="K191" s="12" t="inlineStr">
         <is>
-          <t>LOBATOS - Bailes tradicionales indios + país (M-21/07 tarde 1): «Mandalas (20)»</t>
+          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Manojo de llaves o cascabel»</t>
         </is>
       </c>
       <c r="L191" s="13" t="inlineStr"/>
@@ -11736,7 +11736,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Manojo de llaves o cascabel</t>
+          <t>Manta hippy/india (la lleva Vali)</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -11755,7 +11755,7 @@
         <v>0</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>0</v>
@@ -11764,7 +11764,7 @@
         <v>0</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="K192" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Guardián de las llaves / Pueblo duerme (Lluvia): «Manojo de llaves o cascabel»</t>
+          <t>COMISIONES - FE (V-24/07 tarde): «Manta hippy/india (la lleva Vali)»</t>
         </is>
       </c>
       <c r="L192" s="8" t="inlineStr"/>
@@ -11782,7 +11782,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>Manta hippy/india (la lleva Vali)</t>
+          <t>Mantas</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
@@ -11807,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" s="10" t="n">
         <v>1</v>
@@ -11819,7 +11819,8 @@
       </c>
       <c r="K193" s="12" t="inlineStr">
         <is>
-          <t>COMISIONES - FE (V-24/07 tarde): «Manta hippy/india (la lleva Vali)»</t>
+          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mantas»
+COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Mantas»</t>
         </is>
       </c>
       <c r="L193" s="13" t="inlineStr"/>
@@ -11828,12 +11829,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Mantas</t>
+          <t>Mapas de la zona y Brújulas</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Impresiones/documentacion</t>
         </is>
       </c>
       <c r="C194" s="6">
@@ -11844,19 +11845,19 @@
         <v>0</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -11864,53 +11865,6 @@
         </is>
       </c>
       <c r="K194" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mantas»
-COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Mantas»</t>
-        </is>
-      </c>
-      <c r="L194" s="8" t="inlineStr"/>
-      <c r="M194" s="8" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="9" t="inlineStr">
-        <is>
-          <t>Mapas de la zona y Brújulas</t>
-        </is>
-      </c>
-      <c r="B195" s="10" t="inlineStr">
-        <is>
-          <t>Impresiones/documentacion</t>
-        </is>
-      </c>
-      <c r="C195" s="11">
-        <f>SUM(D195:I195)</f>
-        <v/>
-      </c>
-      <c r="D195" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F195" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G195" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H195" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="I195" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K195" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Mapas 312-I, 315-II, 315-IV, 316-III»
 LOBATOS - El amuleto del elefante sagrado (orientación) (X-22/07 tarde): «5 brújulas»
@@ -11936,18 +11890,64 @@
 RUTAS ICARO - Preparación de raids (L-27/07): «Mapas»</t>
         </is>
       </c>
+      <c r="L194" s="8" t="inlineStr"/>
+      <c r="M194" s="8" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>Martillos</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>Construccion/herramientas</t>
+        </is>
+      </c>
+      <c r="C195" s="11">
+        <f>SUM(D195:I195)</f>
+        <v/>
+      </c>
+      <c r="D195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K195" s="12" t="inlineStr">
+        <is>
+          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Martillos o maza»</t>
+        </is>
+      </c>
       <c r="L195" s="13" t="inlineStr"/>
       <c r="M195" s="13" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Martillos</t>
+          <t>Material de juegos especiales (Jugger, frisbee, combas, sogatira)</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Construccion/herramientas</t>
+          <t>Juegos/deporte</t>
         </is>
       </c>
       <c r="C196" s="6">
@@ -11958,16 +11958,16 @@
         <v>0</v>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I196" s="3" t="n">
         <v>0</v>
@@ -11978,52 +11978,6 @@
         </is>
       </c>
       <c r="K196" s="7" t="inlineStr">
-        <is>
-          <t>LOBATOS - Olimpiadas tarde + vivacs (M-28/07 tarde-noche): «Martillos o maza»</t>
-        </is>
-      </c>
-      <c r="L196" s="8" t="inlineStr"/>
-      <c r="M196" s="8" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="9" t="inlineStr">
-        <is>
-          <t>Material de juegos especiales (Jugger, frisbee, combas, sogatira)</t>
-        </is>
-      </c>
-      <c r="B197" s="10" t="inlineStr">
-        <is>
-          <t>Juegos/deporte</t>
-        </is>
-      </c>
-      <c r="C197" s="11">
-        <f>SUM(D197:I197)</f>
-        <v/>
-      </c>
-      <c r="D197" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F197" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G197" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I197" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K197" s="12" t="inlineStr">
         <is>
           <t>LOBATOS - De aventura en la India (V-17/07 tarde 2): «Comba»
 LOBATOS - Actividad lobatos (Clan Ícaro - Charlie y David) (J-23/07 tarde 2): «Discos para lanzar»
@@ -12037,18 +11991,64 @@
 RUTAS ICARO - Jugger con Pandora (S-25/07): «Armas de jugger»</t>
         </is>
       </c>
+      <c r="L196" s="8" t="inlineStr"/>
+      <c r="M196" s="8" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Material dejado por la empresa</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C197" s="11">
+        <f>SUM(D197:I197)</f>
+        <v/>
+      </c>
+      <c r="D197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K197" s="12" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - Rapel (D-26/07): «Material dejado por la empresa»</t>
+        </is>
+      </c>
       <c r="L197" s="13" t="inlineStr"/>
       <c r="M197" s="13" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Material dejado por la empresa</t>
+          <t>Mazas / martillo de goma</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Construccion/herramientas</t>
         </is>
       </c>
       <c r="C198" s="6">
@@ -12056,10 +12056,10 @@
         <v/>
       </c>
       <c r="D198" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F198" s="3" t="n">
         <v>0</v>
@@ -12068,10 +12068,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -12079,52 +12079,6 @@
         </is>
       </c>
       <c r="K198" s="7" t="inlineStr">
-        <is>
-          <t>RUTAS PANDORA - Rapel (D-26/07): «Material dejado por la empresa»</t>
-        </is>
-      </c>
-      <c r="L198" s="8" t="inlineStr"/>
-      <c r="M198" s="8" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t>Mazas / martillo de goma</t>
-        </is>
-      </c>
-      <c r="B199" s="10" t="inlineStr">
-        <is>
-          <t>Construccion/herramientas</t>
-        </is>
-      </c>
-      <c r="C199" s="11">
-        <f>SUM(D199:I199)</f>
-        <v/>
-      </c>
-      <c r="D199" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E199" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J199" s="10" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K199" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Montaje de tiendas (J-16/07 mañana): «Martillo de goma»
 CASTORES - Construcciones zona común (V-17/07 mañana): «Martillo de goma»
@@ -12133,48 +12087,48 @@
 COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Martillo»</t>
         </is>
       </c>
-      <c r="L199" s="13" t="inlineStr"/>
-      <c r="M199" s="13" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="L198" s="8" t="inlineStr"/>
+      <c r="M198" s="8" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
         <is>
           <t>Mechero</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="C200" s="6">
-        <f>SUM(D200:I200)</f>
-        <v/>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="3" t="n">
+      <c r="C199" s="11">
+        <f>SUM(D199:I199)</f>
+        <v/>
+      </c>
+      <c r="D199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F200" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="3" t="n">
+      <c r="F199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H200" s="3" t="n">
+      <c r="H199" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I200" s="3" t="n">
+      <c r="I199" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J200" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K200" s="7" t="inlineStr">
+      <c r="J199" s="10" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K199" s="12" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Mechero»
 LOBATOS - Ruta volante (x3 días) (D-19 a M-21/07): «Mechero»
@@ -12190,13 +12144,59 @@
 COMISIONES - OLIMPIADAS (grupal) (X-29/07 mañana): «Mechero»</t>
         </is>
       </c>
+      <c r="L199" s="13" t="inlineStr"/>
+      <c r="M199" s="13" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Mechero/cerillas</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C200" s="6">
+        <f>SUM(D200:I200)</f>
+        <v/>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K200" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS ICARO - Línea de la vida (Volante noche): «Mechero/cerillas»</t>
+        </is>
+      </c>
       <c r="L200" s="8" t="inlineStr"/>
       <c r="M200" s="8" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>Mechero/cerillas</t>
+          <t>Medallas de goma eva (las hace el kraalete)</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
@@ -12218,10 +12218,10 @@
         <v>0</v>
       </c>
       <c r="G201" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" s="10" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="K201" s="12" t="inlineStr">
         <is>
-          <t>RUTAS ICARO - Línea de la vida (Volante noche): «Mechero/cerillas»</t>
+          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Medallas de goma eva (las hace el kraalete)»</t>
         </is>
       </c>
       <c r="L201" s="13" t="inlineStr"/>
@@ -12242,7 +12242,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Medallas de goma eva (las hace el kraalete)</t>
+          <t>Menaje</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -12261,10 +12261,10 @@
         <v>0</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
         <v>0</v>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="K202" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Gymkhana deportes (V-17/07 tarde): «Medallas de goma eva (las hace el kraalete)»</t>
+          <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Menaje»</t>
         </is>
       </c>
       <c r="L202" s="8" t="inlineStr"/>
@@ -12288,12 +12288,12 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>Menaje</t>
+          <t>Menaje de cocina (sartenes, cazuelas, boles, hornillos, bombonas)</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Cocina/menaje</t>
         </is>
       </c>
       <c r="C203" s="11">
@@ -12301,22 +12301,22 @@
         <v/>
       </c>
       <c r="D203" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E203" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G203" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H203" s="10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I203" s="10" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J203" s="10" t="inlineStr">
         <is>
@@ -12324,52 +12324,6 @@
         </is>
       </c>
       <c r="K203" s="12" t="inlineStr">
-        <is>
-          <t>EXPLORADORES - Volante (x3 días) (D-19 a M-21/07): «Menaje»</t>
-        </is>
-      </c>
-      <c r="L203" s="13" t="inlineStr"/>
-      <c r="M203" s="13" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Menaje de cocina (sartenes, cazuelas, boles, hornillos, bombonas)</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Cocina/menaje</t>
-        </is>
-      </c>
-      <c r="C204" s="6">
-        <f>SUM(D204:I204)</f>
-        <v/>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F204" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G204" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H204" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I204" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="J204" s="3" t="inlineStr">
-        <is>
-          <t>YA HAY (bases) - revisar</t>
-        </is>
-      </c>
-      <c r="K204" s="7" t="inlineStr">
         <is>
           <t>CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Cazuela y cuchara de madera»
 CASTORES - Acampada volante (x3 días) (D-19 a M-21/07): «Bolsas de basura»
@@ -12456,13 +12410,59 @@
 COMISIONES - GRAN JUEGO (S-18/07 mañana): «Gominolas de corazones( 3 bolsas)»</t>
         </is>
       </c>
+      <c r="L203" s="13" t="inlineStr"/>
+      <c r="M203" s="13" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Mini tronquitos</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C204" s="6">
+        <f>SUM(D204:I204)</f>
+        <v/>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>YA HAY (bases) - revisar</t>
+        </is>
+      </c>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mini tronquitos»</t>
+        </is>
+      </c>
       <c r="L204" s="8" t="inlineStr"/>
       <c r="M204" s="8" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>Mini tronquitos</t>
+          <t>Mismo material que la noche previa</t>
         </is>
       </c>
       <c r="B205" s="10" t="inlineStr">
@@ -12481,13 +12481,13 @@
         <v>0</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H205" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" s="10" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="K205" s="12" t="inlineStr">
         <is>
-          <t>RUTAS PANDORA - PPV (velada) (V-24/07 noche): «Mini tronquitos»</t>
+          <t>EXPLORADORES - Raids (L-27/07): «Mismo material que la noche previa»</t>
         </is>
       </c>
       <c r="L205" s="13" t="inlineStr"/>
@@ -12508,7 +12508,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Mismo material que la noche previa</t>
+          <t>Miss y Mister grupales</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -12527,10 +12527,10 @@
         <v>0</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" s="3" t="n">
         <v>0</v>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="K206" s="7" t="inlineStr">
         <is>
-          <t>EXPLORADORES - Raids (L-27/07): «Mismo material que la noche previa»</t>
+          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Miss y Mister grupales»</t>
         </is>
       </c>
       <c r="L206" s="8" t="inlineStr"/>
@@ -12554,7 +12554,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>Miss y Mister grupales</t>
+          <t>Miss y Mister plastificados</t>
         </is>
       </c>
       <c r="B207" s="10" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="K207" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Velada final conjunta (X-29/07 noche): «Miss y Mister grupales»</t>
+          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Miss y Mister plastificados»</t>
         </is>
       </c>
       <c r="L207" s="13" t="inlineStr"/>
@@ -12600,7 +12600,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Miss y Mister plastificados</t>
+          <t>Miss y Mister ya plastificados</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="K208" s="7" t="inlineStr">
         <is>
-          <t>PIONEROS - Evaluación + Miss y Mister + velada (X-29/07 tarde): «Miss y Mister plastificados»</t>
+          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Miss y Mister ya plastificados»</t>
         </is>
       </c>
       <c r="L208" s="8" t="inlineStr"/>
@@ -12646,7 +12646,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>Miss y Mister ya plastificados</t>
+          <t>MONITORES EN EL CAMPA: Hay que hacer dos triángulos que es el 5to objeto</t>
         </is>
       </c>
       <c r="B209" s="10" t="inlineStr">
@@ -12665,10 +12665,10 @@
         <v>0</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="10" t="n">
         <v>0</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="K209" s="12" t="inlineStr">
         <is>
-          <t>PIONEROS - Miss y Mister (S-25/07 mañana): «Miss y Mister ya plastificados»</t>
+          <t>EXPLORADORES - Velada de código morse (V-17/07 noche): «MONITORES EN EL CAMPA: Hay que hacer dos triángulos que es el 5to objeto»</t>
         </is>
       </c>
       <c r="L209" s="13" t="inlineStr"/>
@@ -19629,7 +19629,8 @@
           <t>Silbato o linterna x3
 Folios (unos 4)
 2 rotuladores
-5 objetos 'tesoro': 2 mazas, 2 telas/objetos amarillos, 2 pinceles, 2 botellines o latas</t>
+5 objetos 'tesoro': 2 mazas, 2 telas/objetos amarillos, 2 pinceles, 2 botellines o latas
+MONITORES EN EL CAMPA: Hay que hacer dos triángulos que es el 5to objeto</t>
         </is>
       </c>
     </row>
@@ -22220,8 +22221,7 @@
 pinturas de cara o varios elementos de maquillaje
 Pinturas o rotuladores para dibujar
 Cubos de plástico ( 2)
-Harina (alternativa para celíacos, para esconder las gominolas en los cubos cantidad en función del tamaño de cubos 
-))
+Harina (alternativa para celíacos, para esconder las gominolas en los cubos cantidad en función del tamaño de cubos)
 Gominolas de corazones( 3 bolsas)
 telas o algo para que se disfracen
 Pañoletas o tela para tapar los ojos.</t>
